--- a/research/traditional_assets/database/data/lithuania/lithuania_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_environmental_waste_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="wse_cts" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0475</v>
+        <v>-0.0917</v>
+      </c>
+      <c r="E2">
+        <v>-0.319</v>
       </c>
       <c r="G2">
-        <v>-0.006766975308641975</v>
+        <v>0.06717703349282296</v>
       </c>
       <c r="H2">
-        <v>-0.006766975308641975</v>
+        <v>0.06717703349282296</v>
       </c>
       <c r="I2">
-        <v>-0.01597222222222222</v>
+        <v>0.06555023923444976</v>
       </c>
       <c r="J2">
-        <v>-0.01597222222222222</v>
+        <v>0.04887240058864772</v>
       </c>
       <c r="K2">
-        <v>-15.4</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.1188271604938272</v>
+        <v>0.008985645933014354</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.62</v>
+        <v>4.77</v>
       </c>
       <c r="V2">
-        <v>0.07605042016806722</v>
+        <v>0.1050660792951542</v>
       </c>
       <c r="W2">
-        <v>-0.389873417721519</v>
+        <v>0.04347222222222222</v>
       </c>
       <c r="X2">
-        <v>0.1375376241149477</v>
+        <v>0.1029777156548457</v>
       </c>
       <c r="Y2">
-        <v>-0.5274110418364667</v>
+        <v>-0.05950549343262347</v>
       </c>
       <c r="Z2">
-        <v>2.368853957229025</v>
+        <v>2.877202643171806</v>
       </c>
       <c r="AA2">
-        <v>-0.03783586181685249</v>
+        <v>0.1406158001518086</v>
       </c>
       <c r="AB2">
-        <v>0.1088319420337814</v>
+        <v>0.08800754272343195</v>
       </c>
       <c r="AC2">
-        <v>-0.1466678038506339</v>
+        <v>0.0526082574283766</v>
       </c>
       <c r="AD2">
-        <v>27.3</v>
+        <v>19.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>27.3</v>
+        <v>19.6</v>
       </c>
       <c r="AG2">
-        <v>23.68</v>
+        <v>14.83</v>
       </c>
       <c r="AH2">
-        <v>0.3644859813084112</v>
+        <v>0.3015384615384615</v>
       </c>
       <c r="AI2">
-        <v>0.5560081466395111</v>
+        <v>0.4495412844036697</v>
       </c>
       <c r="AJ2">
-        <v>0.3322109988776655</v>
+        <v>0.2462228125518845</v>
       </c>
       <c r="AK2">
-        <v>0.5206684256816182</v>
+        <v>0.3819211949523565</v>
       </c>
       <c r="AL2">
-        <v>0.833</v>
+        <v>2.12</v>
       </c>
       <c r="AM2">
-        <v>0.6829999999999999</v>
+        <v>1.804</v>
       </c>
       <c r="AN2">
-        <v>24.59459459459459</v>
+        <v>1.940594059405941</v>
       </c>
       <c r="AO2">
-        <v>-2.48499399759904</v>
+        <v>3.231132075471698</v>
       </c>
       <c r="AP2">
-        <v>21.33333333333333</v>
+        <v>1.468316831683169</v>
       </c>
       <c r="AQ2">
-        <v>-3.030746705710103</v>
+        <v>3.797117516629712</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0475</v>
+        <v>-0.0917</v>
+      </c>
+      <c r="E3">
+        <v>-0.319</v>
       </c>
       <c r="G3">
-        <v>-0.006766975308641975</v>
+        <v>0.06717703349282296</v>
       </c>
       <c r="H3">
-        <v>-0.006766975308641975</v>
+        <v>0.06717703349282296</v>
       </c>
       <c r="I3">
-        <v>-0.01597222222222222</v>
+        <v>0.06555023923444976</v>
       </c>
       <c r="J3">
-        <v>-0.01597222222222222</v>
+        <v>0.04887240058864772</v>
       </c>
       <c r="K3">
-        <v>-15.4</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.1188271604938272</v>
+        <v>0.008985645933014354</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.62</v>
+        <v>4.77</v>
       </c>
       <c r="V3">
-        <v>0.07605042016806722</v>
+        <v>0.1050660792951542</v>
       </c>
       <c r="W3">
-        <v>-0.389873417721519</v>
+        <v>0.04347222222222222</v>
       </c>
       <c r="X3">
-        <v>0.1375376241149477</v>
+        <v>0.1029777156548457</v>
       </c>
       <c r="Y3">
-        <v>-0.5274110418364667</v>
+        <v>-0.05950549343262347</v>
       </c>
       <c r="Z3">
-        <v>2.368853957229025</v>
+        <v>2.877202643171806</v>
       </c>
       <c r="AA3">
-        <v>-0.03783586181685249</v>
+        <v>0.1406158001518086</v>
       </c>
       <c r="AB3">
-        <v>0.1088319420337814</v>
+        <v>0.08800754272343195</v>
       </c>
       <c r="AC3">
-        <v>-0.1466678038506339</v>
+        <v>0.0526082574283766</v>
       </c>
       <c r="AD3">
+        <v>19.6</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>19.6</v>
+      </c>
+      <c r="AG3">
+        <v>14.83</v>
+      </c>
+      <c r="AH3">
+        <v>0.3015384615384615</v>
+      </c>
+      <c r="AI3">
+        <v>0.4495412844036697</v>
+      </c>
+      <c r="AJ3">
+        <v>0.2462228125518845</v>
+      </c>
+      <c r="AK3">
+        <v>0.3819211949523565</v>
+      </c>
+      <c r="AL3">
+        <v>2.12</v>
+      </c>
+      <c r="AM3">
+        <v>1.804</v>
+      </c>
+      <c r="AN3">
+        <v>1.940594059405941</v>
+      </c>
+      <c r="AO3">
+        <v>3.231132075471698</v>
+      </c>
+      <c r="AP3">
+        <v>1.468316831683169</v>
+      </c>
+      <c r="AQ3">
+        <v>3.797117516629712</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>City Service SE (WSE:CTS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WSE:CTS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Waste Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3.2311320754717</v>
+      </c>
+      <c r="F2">
+        <v>10.1585272031814</v>
+      </c>
+      <c r="G2">
+        <v>1.94059405940594</v>
+      </c>
+      <c r="H2">
+        <v>1.9950495049505</v>
+      </c>
+      <c r="I2">
+        <v>0.301538461538462</v>
+      </c>
+      <c r="J2">
+        <v>0.31</v>
+      </c>
+      <c r="K2">
+        <v>45.4</v>
+      </c>
+      <c r="L2">
+        <v>50.7661720768576</v>
+      </c>
+      <c r="M2">
+        <v>60.23</v>
+      </c>
+      <c r="N2">
+        <v>66.1461720768576</v>
+      </c>
+      <c r="O2">
+        <v>19.6</v>
+      </c>
+      <c r="P2">
+        <v>20.15</v>
+      </c>
+      <c r="Q2">
+        <v>0.08800754272343191</v>
+      </c>
+      <c r="R2">
+        <v>0.08360637662280131</v>
+      </c>
+      <c r="S2">
+        <v>0.053331733994545</v>
+      </c>
+      <c r="T2">
+        <v>0.03893</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.102977715654846</v>
+      </c>
+      <c r="X2">
+        <v>0.103678371917103</v>
+      </c>
+      <c r="Y2">
+        <v>1.09938074805196</v>
+      </c>
+      <c r="Z2">
+        <v>1.11138316973164</v>
+      </c>
+      <c r="AA2">
+        <v>19.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.0627432164641706</v>
+      </c>
+      <c r="AC2">
+        <v>3.231132075471698</v>
+      </c>
+      <c r="AD2">
+        <v>19.6</v>
+      </c>
+      <c r="AE2">
+        <v>2.12</v>
+      </c>
+      <c r="AF2">
+        <v>3.25</v>
+      </c>
+      <c r="AG2">
+        <v>10.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>45.4</v>
+      </c>
+      <c r="AK2">
+        <v>0.0583762411417202</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.15</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>8.181000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>2.12</v>
+      </c>
+      <c r="AS2">
+        <v>19.6</v>
+      </c>
+      <c r="AT2">
+        <v>4.77</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08574921512616812</v>
+      </c>
+      <c r="C2">
+        <v>67.89715324990358</v>
+      </c>
+      <c r="D2">
+        <v>63.12715324990359</v>
+      </c>
+      <c r="E2">
+        <v>-19.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.77</v>
+      </c>
+      <c r="H2">
+        <v>45.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>12.625</v>
+      </c>
+      <c r="K2">
+        <v>3.25</v>
+      </c>
+      <c r="L2">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="O2">
+        <v>1.40625</v>
+      </c>
+      <c r="P2">
+        <v>7.968749999999998</v>
+      </c>
+      <c r="Q2">
+        <v>11.21875</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08574921512616812</v>
+      </c>
+      <c r="T2">
+        <v>0.8042521102410373</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.037995</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08567074130347888</v>
+      </c>
+      <c r="C3">
+        <v>67.35284453818372</v>
+      </c>
+      <c r="D3">
+        <v>63.23284453818373</v>
+      </c>
+      <c r="E3">
+        <v>-18.95</v>
+      </c>
+      <c r="F3">
+        <v>0.65</v>
+      </c>
+      <c r="G3">
+        <v>4.77</v>
+      </c>
+      <c r="H3">
+        <v>45.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>12.625</v>
+      </c>
+      <c r="K3">
+        <v>3.25</v>
+      </c>
+      <c r="L3">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M3">
+        <v>0.029055</v>
+      </c>
+      <c r="N3">
+        <v>9.345944999999999</v>
+      </c>
+      <c r="O3">
+        <v>1.40189175</v>
+      </c>
+      <c r="P3">
+        <v>7.944053249999999</v>
+      </c>
+      <c r="Q3">
+        <v>11.19405325</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08615231444795846</v>
+      </c>
+      <c r="T3">
+        <v>0.8111573051269451</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.037995</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>322.66391326794</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08559226748078962</v>
+      </c>
+      <c r="C4">
+        <v>66.80889032945606</v>
+      </c>
+      <c r="D4">
+        <v>63.33889032945606</v>
+      </c>
+      <c r="E4">
+        <v>-18.3</v>
+      </c>
+      <c r="F4">
+        <v>1.3</v>
+      </c>
+      <c r="G4">
+        <v>4.77</v>
+      </c>
+      <c r="H4">
+        <v>45.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>12.625</v>
+      </c>
+      <c r="K4">
+        <v>3.25</v>
+      </c>
+      <c r="L4">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M4">
+        <v>0.05811000000000001</v>
+      </c>
+      <c r="N4">
+        <v>9.316889999999999</v>
+      </c>
+      <c r="O4">
+        <v>1.3975335</v>
+      </c>
+      <c r="P4">
+        <v>7.919356499999999</v>
+      </c>
+      <c r="Q4">
+        <v>11.1693565</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08656364028652003</v>
+      </c>
+      <c r="T4">
+        <v>0.8182034223574635</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.037995</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>161.33195663397</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08551379365810037</v>
+      </c>
+      <c r="C5">
+        <v>66.2652924102938</v>
+      </c>
+      <c r="D5">
+        <v>63.4452924102938</v>
+      </c>
+      <c r="E5">
+        <v>-17.65</v>
+      </c>
+      <c r="F5">
+        <v>1.95</v>
+      </c>
+      <c r="G5">
+        <v>4.77</v>
+      </c>
+      <c r="H5">
+        <v>45.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>12.625</v>
+      </c>
+      <c r="K5">
+        <v>3.25</v>
+      </c>
+      <c r="L5">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M5">
+        <v>0.08716500000000001</v>
+      </c>
+      <c r="N5">
+        <v>9.287834999999998</v>
+      </c>
+      <c r="O5">
+        <v>1.39317525</v>
+      </c>
+      <c r="P5">
+        <v>7.894659749999998</v>
+      </c>
+      <c r="Q5">
+        <v>11.14465975</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08698344707020657</v>
+      </c>
+      <c r="T5">
+        <v>0.8253948203556212</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.037995</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>107.55463775598</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08543531983541111</v>
+      </c>
+      <c r="C6">
+        <v>65.72205257929544</v>
+      </c>
+      <c r="D6">
+        <v>63.55205257929543</v>
+      </c>
+      <c r="E6">
+        <v>-17</v>
+      </c>
+      <c r="F6">
+        <v>2.6</v>
+      </c>
+      <c r="G6">
+        <v>4.77</v>
+      </c>
+      <c r="H6">
+        <v>45.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>12.625</v>
+      </c>
+      <c r="K6">
+        <v>3.25</v>
+      </c>
+      <c r="L6">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M6">
+        <v>0.11622</v>
+      </c>
+      <c r="N6">
+        <v>9.258779999999998</v>
+      </c>
+      <c r="O6">
+        <v>1.388817</v>
+      </c>
+      <c r="P6">
+        <v>7.869962999999998</v>
+      </c>
+      <c r="Q6">
+        <v>11.119963</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08741199982855324</v>
+      </c>
+      <c r="T6">
+        <v>0.8327360391454073</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.037995</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>80.665978316985</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08535684601272188</v>
+      </c>
+      <c r="C7">
+        <v>65.17917264718581</v>
+      </c>
+      <c r="D7">
+        <v>63.65917264718581</v>
+      </c>
+      <c r="E7">
+        <v>-16.35</v>
+      </c>
+      <c r="F7">
+        <v>3.25</v>
+      </c>
+      <c r="G7">
+        <v>4.77</v>
+      </c>
+      <c r="H7">
+        <v>45.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>12.625</v>
+      </c>
+      <c r="K7">
+        <v>3.25</v>
+      </c>
+      <c r="L7">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M7">
+        <v>0.145275</v>
+      </c>
+      <c r="N7">
+        <v>9.229724999999998</v>
+      </c>
+      <c r="O7">
+        <v>1.38445875</v>
+      </c>
+      <c r="P7">
+        <v>7.845266249999999</v>
+      </c>
+      <c r="Q7">
+        <v>11.09526625</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08784957475023356</v>
+      </c>
+      <c r="T7">
+        <v>0.8402318099097152</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.037995</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>64.53278265358801</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08527837219003261</v>
+      </c>
+      <c r="C8">
+        <v>64.6366544369188</v>
+      </c>
+      <c r="D8">
+        <v>63.76665443691881</v>
+      </c>
+      <c r="E8">
+        <v>-15.7</v>
+      </c>
+      <c r="F8">
+        <v>3.9</v>
+      </c>
+      <c r="G8">
+        <v>4.77</v>
+      </c>
+      <c r="H8">
+        <v>45.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>12.625</v>
+      </c>
+      <c r="K8">
+        <v>3.25</v>
+      </c>
+      <c r="L8">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M8">
+        <v>0.17433</v>
+      </c>
+      <c r="N8">
+        <v>9.200669999999999</v>
+      </c>
+      <c r="O8">
+        <v>1.3801005</v>
+      </c>
+      <c r="P8">
+        <v>7.8205695</v>
+      </c>
+      <c r="Q8">
+        <v>11.0705695</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08829645977663045</v>
+      </c>
+      <c r="T8">
+        <v>0.8478870651583701</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.037995</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>53.77731887799001</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08519989836734337</v>
+      </c>
+      <c r="C9">
+        <v>64.09449978378039</v>
+      </c>
+      <c r="D9">
+        <v>63.87449978378039</v>
+      </c>
+      <c r="E9">
+        <v>-15.05</v>
+      </c>
+      <c r="F9">
+        <v>4.550000000000001</v>
+      </c>
+      <c r="G9">
+        <v>4.77</v>
+      </c>
+      <c r="H9">
+        <v>45.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>12.625</v>
+      </c>
+      <c r="K9">
+        <v>3.25</v>
+      </c>
+      <c r="L9">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M9">
+        <v>0.203385</v>
+      </c>
+      <c r="N9">
+        <v>9.171614999999997</v>
+      </c>
+      <c r="O9">
+        <v>1.37574225</v>
+      </c>
+      <c r="P9">
+        <v>7.795872749999997</v>
+      </c>
+      <c r="Q9">
+        <v>11.04587275</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08875295523370255</v>
+      </c>
+      <c r="T9">
+        <v>0.8557069495521574</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.037995</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>46.09484475256285</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08512142454465411</v>
+      </c>
+      <c r="C10">
+        <v>63.55271053549346</v>
+      </c>
+      <c r="D10">
+        <v>63.98271053549346</v>
+      </c>
+      <c r="E10">
+        <v>-14.4</v>
+      </c>
+      <c r="F10">
+        <v>5.2</v>
+      </c>
+      <c r="G10">
+        <v>4.77</v>
+      </c>
+      <c r="H10">
+        <v>45.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>12.625</v>
+      </c>
+      <c r="K10">
+        <v>3.25</v>
+      </c>
+      <c r="L10">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M10">
+        <v>0.23244</v>
+      </c>
+      <c r="N10">
+        <v>9.142559999999998</v>
+      </c>
+      <c r="O10">
+        <v>1.371384</v>
+      </c>
+      <c r="P10">
+        <v>7.771175999999998</v>
+      </c>
+      <c r="Q10">
+        <v>11.021176</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08921937450505882</v>
+      </c>
+      <c r="T10">
+        <v>0.8636968314327661</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.037995</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>40.3329891584925</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08504295072196484</v>
+      </c>
+      <c r="C11">
+        <v>63.01128855232309</v>
+      </c>
+      <c r="D11">
+        <v>64.09128855232309</v>
+      </c>
+      <c r="E11">
+        <v>-13.75</v>
+      </c>
+      <c r="F11">
+        <v>5.85</v>
+      </c>
+      <c r="G11">
+        <v>4.77</v>
+      </c>
+      <c r="H11">
+        <v>45.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>12.625</v>
+      </c>
+      <c r="K11">
+        <v>3.25</v>
+      </c>
+      <c r="L11">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M11">
+        <v>0.261495</v>
+      </c>
+      <c r="N11">
+        <v>9.113504999999998</v>
+      </c>
+      <c r="O11">
+        <v>1.36702575</v>
+      </c>
+      <c r="P11">
+        <v>7.746479249999998</v>
+      </c>
+      <c r="Q11">
+        <v>10.99647925</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08969604474941192</v>
+      </c>
+      <c r="T11">
+        <v>0.8718623151129485</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.037995</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>35.85154591866</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08496447689927562</v>
+      </c>
+      <c r="C12">
+        <v>62.47023570718315</v>
+      </c>
+      <c r="D12">
+        <v>64.20023570718315</v>
+      </c>
+      <c r="E12">
+        <v>-13.1</v>
+      </c>
+      <c r="F12">
+        <v>6.5</v>
+      </c>
+      <c r="G12">
+        <v>4.77</v>
+      </c>
+      <c r="H12">
+        <v>45.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>12.625</v>
+      </c>
+      <c r="K12">
+        <v>3.25</v>
+      </c>
+      <c r="L12">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M12">
+        <v>0.29055</v>
+      </c>
+      <c r="N12">
+        <v>9.084449999999999</v>
+      </c>
+      <c r="O12">
+        <v>1.3626675</v>
+      </c>
+      <c r="P12">
+        <v>7.721782499999999</v>
+      </c>
+      <c r="Q12">
+        <v>10.9717825</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0901833076658618</v>
+      </c>
+      <c r="T12">
+        <v>0.8802092539860242</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.037995</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>32.26639132679401</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08488600307658636</v>
+      </c>
+      <c r="C13">
+        <v>61.92955388574425</v>
+      </c>
+      <c r="D13">
+        <v>64.30955388574425</v>
+      </c>
+      <c r="E13">
+        <v>-12.45</v>
+      </c>
+      <c r="F13">
+        <v>7.15</v>
+      </c>
+      <c r="G13">
+        <v>4.77</v>
+      </c>
+      <c r="H13">
+        <v>45.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>12.625</v>
+      </c>
+      <c r="K13">
+        <v>3.25</v>
+      </c>
+      <c r="L13">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M13">
+        <v>0.319605</v>
+      </c>
+      <c r="N13">
+        <v>9.055394999999999</v>
+      </c>
+      <c r="O13">
+        <v>1.35830925</v>
+      </c>
+      <c r="P13">
+        <v>7.697085749999999</v>
+      </c>
+      <c r="Q13">
+        <v>10.94708575</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09068152031077119</v>
+      </c>
+      <c r="T13">
+        <v>0.8887437645191687</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.037995</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>29.33308302435819</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08480752925389712</v>
+      </c>
+      <c r="C14">
+        <v>61.38924498654222</v>
+      </c>
+      <c r="D14">
+        <v>64.41924498654222</v>
+      </c>
+      <c r="E14">
+        <v>-11.8</v>
+      </c>
+      <c r="F14">
+        <v>7.8</v>
+      </c>
+      <c r="G14">
+        <v>4.77</v>
+      </c>
+      <c r="H14">
+        <v>45.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>12.625</v>
+      </c>
+      <c r="K14">
+        <v>3.25</v>
+      </c>
+      <c r="L14">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M14">
+        <v>0.34866</v>
+      </c>
+      <c r="N14">
+        <v>9.026339999999998</v>
+      </c>
+      <c r="O14">
+        <v>1.353951</v>
+      </c>
+      <c r="P14">
+        <v>7.672388999999998</v>
+      </c>
+      <c r="Q14">
+        <v>10.922389</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09119105597033762</v>
+      </c>
+      <c r="T14">
+        <v>0.8974722412007939</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.037995</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>26.888659438995</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08472905543120784</v>
+      </c>
+      <c r="C15">
+        <v>60.8493109210882</v>
+      </c>
+      <c r="D15">
+        <v>64.52931092108821</v>
+      </c>
+      <c r="E15">
+        <v>-11.15</v>
+      </c>
+      <c r="F15">
+        <v>8.450000000000001</v>
+      </c>
+      <c r="G15">
+        <v>4.77</v>
+      </c>
+      <c r="H15">
+        <v>45.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>12.625</v>
+      </c>
+      <c r="K15">
+        <v>3.25</v>
+      </c>
+      <c r="L15">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M15">
+        <v>0.3777150000000001</v>
+      </c>
+      <c r="N15">
+        <v>8.997284999999998</v>
+      </c>
+      <c r="O15">
+        <v>1.34959275</v>
+      </c>
+      <c r="P15">
+        <v>7.647692249999999</v>
+      </c>
+      <c r="Q15">
+        <v>10.89769225</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09171230509334236</v>
+      </c>
+      <c r="T15">
+        <v>0.9064013725187782</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.037995</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>24.82030102061077</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08465058160851859</v>
+      </c>
+      <c r="C16">
+        <v>60.30975361397962</v>
+      </c>
+      <c r="D16">
+        <v>64.63975361397962</v>
+      </c>
+      <c r="E16">
+        <v>-10.5</v>
+      </c>
+      <c r="F16">
+        <v>9.100000000000001</v>
+      </c>
+      <c r="G16">
+        <v>4.77</v>
+      </c>
+      <c r="H16">
+        <v>45.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>12.625</v>
+      </c>
+      <c r="K16">
+        <v>3.25</v>
+      </c>
+      <c r="L16">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M16">
+        <v>0.4067700000000001</v>
+      </c>
+      <c r="N16">
+        <v>8.968229999999998</v>
+      </c>
+      <c r="O16">
+        <v>1.3452345</v>
+      </c>
+      <c r="P16">
+        <v>7.622995499999998</v>
+      </c>
+      <c r="Q16">
+        <v>10.8729955</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09224567628897511</v>
+      </c>
+      <c r="T16">
+        <v>0.9155381580534597</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.037995</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>23.04742237628143</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08457210778582935</v>
+      </c>
+      <c r="C17">
+        <v>59.77057500301228</v>
+      </c>
+      <c r="D17">
+        <v>64.75057500301229</v>
+      </c>
+      <c r="E17">
+        <v>-9.850000000000001</v>
+      </c>
+      <c r="F17">
+        <v>9.75</v>
+      </c>
+      <c r="G17">
+        <v>4.77</v>
+      </c>
+      <c r="H17">
+        <v>45.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>12.625</v>
+      </c>
+      <c r="K17">
+        <v>3.25</v>
+      </c>
+      <c r="L17">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M17">
+        <v>0.435825</v>
+      </c>
+      <c r="N17">
+        <v>8.939174999999999</v>
+      </c>
+      <c r="O17">
+        <v>1.34087625</v>
+      </c>
+      <c r="P17">
+        <v>7.598298749999999</v>
+      </c>
+      <c r="Q17">
+        <v>10.84829875</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09279159739509335</v>
+      </c>
+      <c r="T17">
+        <v>0.9248899267771928</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.037995</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>21.510927551196</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08449363396314011</v>
+      </c>
+      <c r="C18">
+        <v>59.23177703929402</v>
+      </c>
+      <c r="D18">
+        <v>64.86177703929403</v>
+      </c>
+      <c r="E18">
+        <v>-9.200000000000001</v>
+      </c>
+      <c r="F18">
+        <v>10.4</v>
+      </c>
+      <c r="G18">
+        <v>4.77</v>
+      </c>
+      <c r="H18">
+        <v>45.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>12.625</v>
+      </c>
+      <c r="K18">
+        <v>3.25</v>
+      </c>
+      <c r="L18">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M18">
+        <v>0.4648800000000001</v>
+      </c>
+      <c r="N18">
+        <v>8.910119999999997</v>
+      </c>
+      <c r="O18">
+        <v>1.336518</v>
+      </c>
+      <c r="P18">
+        <v>7.573601999999998</v>
+      </c>
+      <c r="Q18">
+        <v>10.823602</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09335051662278583</v>
+      </c>
+      <c r="T18">
+        <v>0.9344643566610148</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.037995</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>20.16649457924625</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08441516014045083</v>
+      </c>
+      <c r="C19">
+        <v>58.69336168735884</v>
+      </c>
+      <c r="D19">
+        <v>64.97336168735885</v>
+      </c>
+      <c r="E19">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="F19">
+        <v>11.05</v>
+      </c>
+      <c r="G19">
+        <v>4.77</v>
+      </c>
+      <c r="H19">
+        <v>45.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>12.625</v>
+      </c>
+      <c r="K19">
+        <v>3.25</v>
+      </c>
+      <c r="L19">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M19">
+        <v>0.4939350000000001</v>
+      </c>
+      <c r="N19">
+        <v>8.881064999999998</v>
+      </c>
+      <c r="O19">
+        <v>1.33215975</v>
+      </c>
+      <c r="P19">
+        <v>7.548905249999998</v>
+      </c>
+      <c r="Q19">
+        <v>10.79890525</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09392290378367571</v>
+      </c>
+      <c r="T19">
+        <v>0.9442694956986636</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.037995</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>18.98023019223177</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.0843366863177616</v>
+      </c>
+      <c r="C20">
+        <v>58.15533092528268</v>
+      </c>
+      <c r="D20">
+        <v>65.08533092528269</v>
+      </c>
+      <c r="E20">
+        <v>-7.900000000000002</v>
+      </c>
+      <c r="F20">
+        <v>11.7</v>
+      </c>
+      <c r="G20">
+        <v>4.77</v>
+      </c>
+      <c r="H20">
+        <v>45.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>12.625</v>
+      </c>
+      <c r="K20">
+        <v>3.25</v>
+      </c>
+      <c r="L20">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M20">
+        <v>0.5229900000000001</v>
+      </c>
+      <c r="N20">
+        <v>8.852009999999998</v>
+      </c>
+      <c r="O20">
+        <v>1.3278015</v>
+      </c>
+      <c r="P20">
+        <v>7.524208499999999</v>
+      </c>
+      <c r="Q20">
+        <v>10.7742085</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09450925160702633</v>
+      </c>
+      <c r="T20">
+        <v>0.9543137844689381</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.037995</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>17.92577295933</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08425821249507234</v>
+      </c>
+      <c r="C21">
+        <v>57.61768674480059</v>
+      </c>
+      <c r="D21">
+        <v>65.19768674480059</v>
+      </c>
+      <c r="E21">
+        <v>-7.250000000000002</v>
+      </c>
+      <c r="F21">
+        <v>12.35</v>
+      </c>
+      <c r="G21">
+        <v>4.77</v>
+      </c>
+      <c r="H21">
+        <v>45.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>12.625</v>
+      </c>
+      <c r="K21">
+        <v>3.25</v>
+      </c>
+      <c r="L21">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M21">
+        <v>0.552045</v>
+      </c>
+      <c r="N21">
+        <v>8.822954999999999</v>
+      </c>
+      <c r="O21">
+        <v>1.32344325</v>
+      </c>
+      <c r="P21">
+        <v>7.499511749999999</v>
+      </c>
+      <c r="Q21">
+        <v>10.74951175</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09511007715441029</v>
+      </c>
+      <c r="T21">
+        <v>0.9646060803693428</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.037995</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>16.98231122462843</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08417973867238308</v>
+      </c>
+      <c r="C22">
+        <v>57.08043115142438</v>
+      </c>
+      <c r="D22">
+        <v>65.31043115142438</v>
+      </c>
+      <c r="E22">
+        <v>-6.600000000000001</v>
+      </c>
+      <c r="F22">
+        <v>13</v>
+      </c>
+      <c r="G22">
+        <v>4.77</v>
+      </c>
+      <c r="H22">
+        <v>45.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>12.625</v>
+      </c>
+      <c r="K22">
+        <v>3.25</v>
+      </c>
+      <c r="L22">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M22">
+        <v>0.5811000000000001</v>
+      </c>
+      <c r="N22">
+        <v>8.793899999999999</v>
+      </c>
+      <c r="O22">
+        <v>1.319085</v>
+      </c>
+      <c r="P22">
+        <v>7.474815</v>
+      </c>
+      <c r="Q22">
+        <v>10.724815</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09572592334047886</v>
+      </c>
+      <c r="T22">
+        <v>0.9751556836672576</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.037995</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>16.133195663397</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08410126484969382</v>
+      </c>
+      <c r="C23">
+        <v>56.54356616456234</v>
+      </c>
+      <c r="D23">
+        <v>65.42356616456235</v>
+      </c>
+      <c r="E23">
+        <v>-5.950000000000001</v>
+      </c>
+      <c r="F23">
+        <v>13.65</v>
+      </c>
+      <c r="G23">
+        <v>4.77</v>
+      </c>
+      <c r="H23">
+        <v>45.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>12.625</v>
+      </c>
+      <c r="K23">
+        <v>3.25</v>
+      </c>
+      <c r="L23">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M23">
+        <v>0.6101550000000001</v>
+      </c>
+      <c r="N23">
+        <v>8.764844999999998</v>
+      </c>
+      <c r="O23">
+        <v>1.314726749999999</v>
+      </c>
+      <c r="P23">
+        <v>7.450118249999998</v>
+      </c>
+      <c r="Q23">
+        <v>10.70011825</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09635736056923269</v>
+      </c>
+      <c r="T23">
+        <v>0.9859723655296766</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.037995</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>15.36494825085428</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08402279102700459</v>
+      </c>
+      <c r="C24">
+        <v>56.00709381763951</v>
+      </c>
+      <c r="D24">
+        <v>65.53709381763952</v>
+      </c>
+      <c r="E24">
+        <v>-5.300000000000001</v>
+      </c>
+      <c r="F24">
+        <v>14.3</v>
+      </c>
+      <c r="G24">
+        <v>4.77</v>
+      </c>
+      <c r="H24">
+        <v>45.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>12.625</v>
+      </c>
+      <c r="K24">
+        <v>3.25</v>
+      </c>
+      <c r="L24">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M24">
+        <v>0.6392100000000001</v>
+      </c>
+      <c r="N24">
+        <v>8.735789999999998</v>
+      </c>
+      <c r="O24">
+        <v>1.3103685</v>
+      </c>
+      <c r="P24">
+        <v>7.425421499999999</v>
+      </c>
+      <c r="Q24">
+        <v>10.6754215</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09700498849615972</v>
+      </c>
+      <c r="T24">
+        <v>0.9970663982090808</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.037995</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>14.66654151217909</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08394431720431533</v>
+      </c>
+      <c r="C25">
+        <v>55.4710161582198</v>
+      </c>
+      <c r="D25">
+        <v>65.6510161582198</v>
+      </c>
+      <c r="E25">
+        <v>-4.65</v>
+      </c>
+      <c r="F25">
+        <v>14.95</v>
+      </c>
+      <c r="G25">
+        <v>4.77</v>
+      </c>
+      <c r="H25">
+        <v>45.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>12.625</v>
+      </c>
+      <c r="K25">
+        <v>3.25</v>
+      </c>
+      <c r="L25">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M25">
+        <v>0.6682650000000001</v>
+      </c>
+      <c r="N25">
+        <v>8.706734999999998</v>
+      </c>
+      <c r="O25">
+        <v>1.30601025</v>
+      </c>
+      <c r="P25">
+        <v>7.400724749999998</v>
+      </c>
+      <c r="Q25">
+        <v>10.65072475</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09766943792768223</v>
+      </c>
+      <c r="T25">
+        <v>1.008448587581456</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.037995</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>14.02886579425826</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08386584338162606</v>
+      </c>
+      <c r="C26">
+        <v>54.93533524812884</v>
+      </c>
+      <c r="D26">
+        <v>65.76533524812885</v>
+      </c>
+      <c r="E26">
+        <v>-4.000000000000002</v>
+      </c>
+      <c r="F26">
+        <v>15.6</v>
+      </c>
+      <c r="G26">
+        <v>4.77</v>
+      </c>
+      <c r="H26">
+        <v>45.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>12.625</v>
+      </c>
+      <c r="K26">
+        <v>3.25</v>
+      </c>
+      <c r="L26">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M26">
+        <v>0.6973200000000001</v>
+      </c>
+      <c r="N26">
+        <v>8.677679999999999</v>
+      </c>
+      <c r="O26">
+        <v>1.301652</v>
+      </c>
+      <c r="P26">
+        <v>7.376027999999999</v>
+      </c>
+      <c r="Q26">
+        <v>10.626028</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09835137287056062</v>
+      </c>
+      <c r="T26">
+        <v>1.020130308253105</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.037995</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>13.4443297194975</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08378736955893683</v>
+      </c>
+      <c r="C27">
+        <v>54.40005316357839</v>
+      </c>
+      <c r="D27">
+        <v>65.8800531635784</v>
+      </c>
+      <c r="E27">
+        <v>-3.350000000000001</v>
+      </c>
+      <c r="F27">
+        <v>16.25</v>
+      </c>
+      <c r="G27">
+        <v>4.77</v>
+      </c>
+      <c r="H27">
+        <v>45.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>12.625</v>
+      </c>
+      <c r="K27">
+        <v>3.25</v>
+      </c>
+      <c r="L27">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M27">
+        <v>0.7263750000000001</v>
+      </c>
+      <c r="N27">
+        <v>8.648624999999997</v>
+      </c>
+      <c r="O27">
+        <v>1.297293749999999</v>
+      </c>
+      <c r="P27">
+        <v>7.351331249999998</v>
+      </c>
+      <c r="Q27">
+        <v>10.60133125</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.0990514927452491</v>
+      </c>
+      <c r="T27">
+        <v>1.032123541475998</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.037995</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>12.9065565307176</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08395199573624756</v>
+      </c>
+      <c r="C28">
+        <v>53.50985157034866</v>
+      </c>
+      <c r="D28">
+        <v>65.63985157034867</v>
+      </c>
+      <c r="E28">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="F28">
+        <v>16.9</v>
+      </c>
+      <c r="G28">
+        <v>4.77</v>
+      </c>
+      <c r="H28">
+        <v>45.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>12.625</v>
+      </c>
+      <c r="K28">
+        <v>3.25</v>
+      </c>
+      <c r="L28">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M28">
+        <v>0.7740200000000002</v>
+      </c>
+      <c r="N28">
+        <v>8.600979999999998</v>
+      </c>
+      <c r="O28">
+        <v>1.290147</v>
+      </c>
+      <c r="P28">
+        <v>7.310832999999999</v>
+      </c>
+      <c r="Q28">
+        <v>10.560833</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09977053477871292</v>
+      </c>
+      <c r="T28">
+        <v>1.044440916137347</v>
+      </c>
+      <c r="U28">
+        <v>0.0458</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.03893</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>12.1120901268701</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08388287191355832</v>
+      </c>
+      <c r="C29">
+        <v>52.960494614341</v>
+      </c>
+      <c r="D29">
+        <v>65.740494614341</v>
+      </c>
+      <c r="E29">
+        <v>-2.050000000000001</v>
+      </c>
+      <c r="F29">
+        <v>17.55</v>
+      </c>
+      <c r="G29">
+        <v>4.77</v>
+      </c>
+      <c r="H29">
+        <v>45.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>12.625</v>
+      </c>
+      <c r="K29">
+        <v>3.25</v>
+      </c>
+      <c r="L29">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M29">
+        <v>0.80379</v>
+      </c>
+      <c r="N29">
+        <v>8.571209999999999</v>
+      </c>
+      <c r="O29">
+        <v>1.2856815</v>
+      </c>
+      <c r="P29">
+        <v>7.285528499999999</v>
+      </c>
+      <c r="Q29">
+        <v>10.5355285</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1005092765939155</v>
+      </c>
+      <c r="T29">
+        <v>1.057095753118185</v>
+      </c>
+      <c r="U29">
+        <v>0.0458</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.03893</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>11.66349419624529</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08381374809086908</v>
+      </c>
+      <c r="C30">
+        <v>52.41144675642994</v>
+      </c>
+      <c r="D30">
+        <v>65.84144675642995</v>
+      </c>
+      <c r="E30">
+        <v>-1.399999999999999</v>
+      </c>
+      <c r="F30">
+        <v>18.2</v>
+      </c>
+      <c r="G30">
+        <v>4.77</v>
+      </c>
+      <c r="H30">
+        <v>45.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>12.625</v>
+      </c>
+      <c r="K30">
+        <v>3.25</v>
+      </c>
+      <c r="L30">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M30">
+        <v>0.8335600000000002</v>
+      </c>
+      <c r="N30">
+        <v>8.541439999999998</v>
+      </c>
+      <c r="O30">
+        <v>1.281216</v>
+      </c>
+      <c r="P30">
+        <v>7.260223999999998</v>
+      </c>
+      <c r="Q30">
+        <v>10.510224</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1012685390150959</v>
+      </c>
+      <c r="T30">
+        <v>1.070102113348491</v>
+      </c>
+      <c r="U30">
+        <v>0.0458</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.03893</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>11.24694083209367</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08374462426817982</v>
+      </c>
+      <c r="C31">
+        <v>51.86270942277331</v>
+      </c>
+      <c r="D31">
+        <v>65.94270942277331</v>
+      </c>
+      <c r="E31">
+        <v>-0.7500000000000036</v>
+      </c>
+      <c r="F31">
+        <v>18.85</v>
+      </c>
+      <c r="G31">
+        <v>4.77</v>
+      </c>
+      <c r="H31">
+        <v>45.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>12.625</v>
+      </c>
+      <c r="K31">
+        <v>3.25</v>
+      </c>
+      <c r="L31">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M31">
+        <v>0.8633299999999999</v>
+      </c>
+      <c r="N31">
+        <v>8.511669999999999</v>
+      </c>
+      <c r="O31">
+        <v>1.2767505</v>
+      </c>
+      <c r="P31">
+        <v>7.234919499999999</v>
+      </c>
+      <c r="Q31">
+        <v>10.4849195</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1020491891101124</v>
+      </c>
+      <c r="T31">
+        <v>1.083474849923313</v>
+      </c>
+      <c r="U31">
+        <v>0.0458</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.03893</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>10.8591152861594</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08367550044549056</v>
+      </c>
+      <c r="C32">
+        <v>51.31428404831593</v>
+      </c>
+      <c r="D32">
+        <v>66.04428404831593</v>
+      </c>
+      <c r="E32">
+        <v>-0.1000000000000014</v>
+      </c>
+      <c r="F32">
+        <v>19.5</v>
+      </c>
+      <c r="G32">
+        <v>4.77</v>
+      </c>
+      <c r="H32">
+        <v>45.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>12.625</v>
+      </c>
+      <c r="K32">
+        <v>3.25</v>
+      </c>
+      <c r="L32">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M32">
+        <v>0.8931</v>
+      </c>
+      <c r="N32">
+        <v>8.481899999999998</v>
+      </c>
+      <c r="O32">
+        <v>1.272285</v>
+      </c>
+      <c r="P32">
+        <v>7.209614999999998</v>
+      </c>
+      <c r="Q32">
+        <v>10.459615</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.102852143493558</v>
+      </c>
+      <c r="T32">
+        <v>1.097229664685986</v>
+      </c>
+      <c r="U32">
+        <v>0.0458</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.03893</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>10.49714477662076</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08360637662280132</v>
+      </c>
+      <c r="C33">
+        <v>50.76617207685761</v>
+      </c>
+      <c r="D33">
+        <v>66.14617207685761</v>
+      </c>
+      <c r="E33">
+        <v>0.5499999999999972</v>
+      </c>
+      <c r="F33">
+        <v>20.15</v>
+      </c>
+      <c r="G33">
+        <v>4.77</v>
+      </c>
+      <c r="H33">
+        <v>45.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>12.625</v>
+      </c>
+      <c r="K33">
+        <v>3.25</v>
+      </c>
+      <c r="L33">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M33">
+        <v>0.92287</v>
+      </c>
+      <c r="N33">
+        <v>8.452129999999999</v>
+      </c>
+      <c r="O33">
+        <v>1.2678195</v>
+      </c>
+      <c r="P33">
+        <v>7.184310499999999</v>
+      </c>
+      <c r="Q33">
+        <v>10.4343105</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1036783719171034</v>
+      </c>
+      <c r="T33">
+        <v>1.111383169731636</v>
+      </c>
+      <c r="U33">
+        <v>0.0458</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.03893</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>10.15852720318138</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08413565280011205</v>
+      </c>
+      <c r="C34">
+        <v>49.34394115178553</v>
+      </c>
+      <c r="D34">
+        <v>65.37394115178553</v>
+      </c>
+      <c r="E34">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="F34">
+        <v>20.8</v>
+      </c>
+      <c r="G34">
+        <v>4.77</v>
+      </c>
+      <c r="H34">
+        <v>45.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>12.625</v>
+      </c>
+      <c r="K34">
+        <v>3.25</v>
+      </c>
+      <c r="L34">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M34">
+        <v>0.9984000000000001</v>
+      </c>
+      <c r="N34">
+        <v>8.376599999999998</v>
+      </c>
+      <c r="O34">
+        <v>1.25649</v>
+      </c>
+      <c r="P34">
+        <v>7.120109999999999</v>
+      </c>
+      <c r="Q34">
+        <v>10.37011</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1045289011766354</v>
+      </c>
+      <c r="T34">
+        <v>1.125952954337452</v>
+      </c>
+      <c r="U34">
+        <v>0.048</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.0408</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>9.390024038461537</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08408522897742281</v>
+      </c>
+      <c r="C35">
+        <v>48.76673318776658</v>
+      </c>
+      <c r="D35">
+        <v>65.44673318776658</v>
+      </c>
+      <c r="E35">
+        <v>1.849999999999998</v>
+      </c>
+      <c r="F35">
+        <v>21.45</v>
+      </c>
+      <c r="G35">
+        <v>4.77</v>
+      </c>
+      <c r="H35">
+        <v>45.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>12.625</v>
+      </c>
+      <c r="K35">
+        <v>3.25</v>
+      </c>
+      <c r="L35">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M35">
+        <v>1.0296</v>
+      </c>
+      <c r="N35">
+        <v>8.345399999999998</v>
+      </c>
+      <c r="O35">
+        <v>1.25181</v>
+      </c>
+      <c r="P35">
+        <v>7.093589999999998</v>
+      </c>
+      <c r="Q35">
+        <v>10.34359</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1054048193692878</v>
+      </c>
+      <c r="T35">
+        <v>1.140957657886725</v>
+      </c>
+      <c r="U35">
+        <v>0.048</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.0408</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>9.105477855477853</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08403480515473355</v>
+      </c>
+      <c r="C36">
+        <v>48.18968750819666</v>
+      </c>
+      <c r="D36">
+        <v>65.51968750819667</v>
+      </c>
+      <c r="E36">
+        <v>2.5</v>
+      </c>
+      <c r="F36">
+        <v>22.1</v>
+      </c>
+      <c r="G36">
+        <v>4.77</v>
+      </c>
+      <c r="H36">
+        <v>45.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>12.625</v>
+      </c>
+      <c r="K36">
+        <v>3.25</v>
+      </c>
+      <c r="L36">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M36">
+        <v>1.0608</v>
+      </c>
+      <c r="N36">
+        <v>8.314199999999998</v>
+      </c>
+      <c r="O36">
+        <v>1.24713</v>
+      </c>
+      <c r="P36">
+        <v>7.067069999999998</v>
+      </c>
+      <c r="Q36">
+        <v>10.31707</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1063072805374751</v>
+      </c>
+      <c r="T36">
+        <v>1.15641704942234</v>
+      </c>
+      <c r="U36">
+        <v>0.048</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.0408</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>8.837669683257914</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08398438133204431</v>
+      </c>
+      <c r="C37">
+        <v>47.61280465638312</v>
+      </c>
+      <c r="D37">
+        <v>65.59280465638312</v>
+      </c>
+      <c r="E37">
+        <v>3.150000000000002</v>
+      </c>
+      <c r="F37">
+        <v>22.75</v>
+      </c>
+      <c r="G37">
+        <v>4.77</v>
+      </c>
+      <c r="H37">
+        <v>45.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>12.625</v>
+      </c>
+      <c r="K37">
+        <v>3.25</v>
+      </c>
+      <c r="L37">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M37">
+        <v>1.092</v>
+      </c>
+      <c r="N37">
+        <v>8.282999999999998</v>
+      </c>
+      <c r="O37">
+        <v>1.24245</v>
+      </c>
+      <c r="P37">
+        <v>7.040549999999998</v>
+      </c>
+      <c r="Q37">
+        <v>10.29055</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1072375097416066</v>
+      </c>
+      <c r="T37">
+        <v>1.172352114543666</v>
+      </c>
+      <c r="U37">
+        <v>0.048</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.0408</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>8.585164835164832</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08393395750935506</v>
+      </c>
+      <c r="C38">
+        <v>47.03608517806124</v>
+      </c>
+      <c r="D38">
+        <v>65.66608517806124</v>
+      </c>
+      <c r="E38">
+        <v>3.799999999999997</v>
+      </c>
+      <c r="F38">
+        <v>23.4</v>
+      </c>
+      <c r="G38">
+        <v>4.77</v>
+      </c>
+      <c r="H38">
+        <v>45.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>12.625</v>
+      </c>
+      <c r="K38">
+        <v>3.25</v>
+      </c>
+      <c r="L38">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M38">
+        <v>1.1232</v>
+      </c>
+      <c r="N38">
+        <v>8.251799999999998</v>
+      </c>
+      <c r="O38">
+        <v>1.23777</v>
+      </c>
+      <c r="P38">
+        <v>7.014029999999998</v>
+      </c>
+      <c r="Q38">
+        <v>10.26403</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1081968086083673</v>
+      </c>
+      <c r="T38">
+        <v>1.188785150450033</v>
+      </c>
+      <c r="U38">
+        <v>0.048</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.0408</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>8.346688034188032</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.0838835336866658</v>
+      </c>
+      <c r="C39">
+        <v>46.45952962140788</v>
+      </c>
+      <c r="D39">
+        <v>65.73952962140788</v>
+      </c>
+      <c r="E39">
+        <v>4.449999999999999</v>
+      </c>
+      <c r="F39">
+        <v>24.05</v>
+      </c>
+      <c r="G39">
+        <v>4.77</v>
+      </c>
+      <c r="H39">
+        <v>45.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>12.625</v>
+      </c>
+      <c r="K39">
+        <v>3.25</v>
+      </c>
+      <c r="L39">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M39">
+        <v>1.1544</v>
+      </c>
+      <c r="N39">
+        <v>8.220599999999997</v>
+      </c>
+      <c r="O39">
+        <v>1.23309</v>
+      </c>
+      <c r="P39">
+        <v>6.987509999999998</v>
+      </c>
+      <c r="Q39">
+        <v>10.23751</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.109186561407406</v>
+      </c>
+      <c r="T39">
+        <v>1.205739870035968</v>
+      </c>
+      <c r="U39">
+        <v>0.048</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.0408</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>8.121101871101867</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08383310986397656</v>
+      </c>
+      <c r="C40">
+        <v>45.88313853705498</v>
+      </c>
+      <c r="D40">
+        <v>65.81313853705498</v>
+      </c>
+      <c r="E40">
+        <v>5.099999999999998</v>
+      </c>
+      <c r="F40">
+        <v>24.7</v>
+      </c>
+      <c r="G40">
+        <v>4.77</v>
+      </c>
+      <c r="H40">
+        <v>45.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>12.625</v>
+      </c>
+      <c r="K40">
+        <v>3.25</v>
+      </c>
+      <c r="L40">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M40">
+        <v>1.1856</v>
+      </c>
+      <c r="N40">
+        <v>8.189399999999999</v>
+      </c>
+      <c r="O40">
+        <v>1.22841</v>
+      </c>
+      <c r="P40">
+        <v>6.960989999999999</v>
+      </c>
+      <c r="Q40">
+        <v>10.21099</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1102082417160912</v>
+      </c>
+      <c r="T40">
+        <v>1.223241516060158</v>
+      </c>
+      <c r="U40">
+        <v>0.048</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.0408</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>7.907388663967611</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08427993604128729</v>
+      </c>
+      <c r="C41">
+        <v>44.58654499121889</v>
+      </c>
+      <c r="D41">
+        <v>65.1665449912189</v>
+      </c>
+      <c r="E41">
+        <v>5.75</v>
+      </c>
+      <c r="F41">
+        <v>25.35</v>
+      </c>
+      <c r="G41">
+        <v>4.77</v>
+      </c>
+      <c r="H41">
+        <v>45.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>12.625</v>
+      </c>
+      <c r="K41">
+        <v>3.25</v>
+      </c>
+      <c r="L41">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M41">
+        <v>1.254825</v>
+      </c>
+      <c r="N41">
+        <v>8.120174999999998</v>
+      </c>
+      <c r="O41">
+        <v>1.21802625</v>
+      </c>
+      <c r="P41">
+        <v>6.902148749999999</v>
+      </c>
+      <c r="Q41">
+        <v>10.15214875</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1112634197398152</v>
+      </c>
+      <c r="T41">
+        <v>1.241316986544158</v>
+      </c>
+      <c r="U41">
+        <v>0.0495</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.042075</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>7.471161317315161</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08424226221859804</v>
+      </c>
+      <c r="C42">
+        <v>43.99057119373188</v>
+      </c>
+      <c r="D42">
+        <v>65.22057119373189</v>
+      </c>
+      <c r="E42">
+        <v>6.399999999999999</v>
+      </c>
+      <c r="F42">
+        <v>26</v>
+      </c>
+      <c r="G42">
+        <v>4.77</v>
+      </c>
+      <c r="H42">
+        <v>45.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>12.625</v>
+      </c>
+      <c r="K42">
+        <v>3.25</v>
+      </c>
+      <c r="L42">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M42">
+        <v>1.287</v>
+      </c>
+      <c r="N42">
+        <v>8.087999999999997</v>
+      </c>
+      <c r="O42">
+        <v>1.2132</v>
+      </c>
+      <c r="P42">
+        <v>6.874799999999998</v>
+      </c>
+      <c r="Q42">
+        <v>10.1248</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1123537703643301</v>
+      </c>
+      <c r="T42">
+        <v>1.259994972710959</v>
+      </c>
+      <c r="U42">
+        <v>0.0495</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.042075</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>7.284382284382282</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.0842045883959088</v>
+      </c>
+      <c r="C43">
+        <v>43.39468705121789</v>
+      </c>
+      <c r="D43">
+        <v>65.2746870512179</v>
+      </c>
+      <c r="E43">
+        <v>7.050000000000001</v>
+      </c>
+      <c r="F43">
+        <v>26.65</v>
+      </c>
+      <c r="G43">
+        <v>4.77</v>
+      </c>
+      <c r="H43">
+        <v>45.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>12.625</v>
+      </c>
+      <c r="K43">
+        <v>3.25</v>
+      </c>
+      <c r="L43">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M43">
+        <v>1.319175</v>
+      </c>
+      <c r="N43">
+        <v>8.055824999999999</v>
+      </c>
+      <c r="O43">
+        <v>1.20837375</v>
+      </c>
+      <c r="P43">
+        <v>6.847451249999999</v>
+      </c>
+      <c r="Q43">
+        <v>10.09745125</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1134810820269641</v>
+      </c>
+      <c r="T43">
+        <v>1.279306110951209</v>
+      </c>
+      <c r="U43">
+        <v>0.0495</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.042075</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>7.106714423787593</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08416691457321954</v>
+      </c>
+      <c r="C44">
+        <v>42.79889278703216</v>
+      </c>
+      <c r="D44">
+        <v>65.32889278703216</v>
+      </c>
+      <c r="E44">
+        <v>7.699999999999999</v>
+      </c>
+      <c r="F44">
         <v>27.3</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>27.3</v>
-      </c>
-      <c r="AG3">
-        <v>23.68</v>
-      </c>
-      <c r="AH3">
-        <v>0.3644859813084112</v>
-      </c>
-      <c r="AI3">
-        <v>0.5560081466395111</v>
-      </c>
-      <c r="AJ3">
-        <v>0.3322109988776655</v>
-      </c>
-      <c r="AK3">
-        <v>0.5206684256816182</v>
-      </c>
-      <c r="AL3">
-        <v>0.833</v>
-      </c>
-      <c r="AM3">
-        <v>0.6829999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>24.59459459459459</v>
-      </c>
-      <c r="AO3">
-        <v>-2.48499399759904</v>
-      </c>
-      <c r="AP3">
-        <v>21.33333333333333</v>
-      </c>
-      <c r="AQ3">
-        <v>-3.030746705710103</v>
+      <c r="G44">
+        <v>4.77</v>
+      </c>
+      <c r="H44">
+        <v>45.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>12.625</v>
+      </c>
+      <c r="K44">
+        <v>3.25</v>
+      </c>
+      <c r="L44">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M44">
+        <v>1.35135</v>
+      </c>
+      <c r="N44">
+        <v>8.023649999999998</v>
+      </c>
+      <c r="O44">
+        <v>1.2035475</v>
+      </c>
+      <c r="P44">
+        <v>6.820102499999998</v>
+      </c>
+      <c r="Q44">
+        <v>10.0701025</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1146472665055509</v>
+      </c>
+      <c r="T44">
+        <v>1.299283150510089</v>
+      </c>
+      <c r="U44">
+        <v>0.0495</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.042075</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>6.937506937506936</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.0841292407505303</v>
+      </c>
+      <c r="C45">
+        <v>42.20318862527239</v>
+      </c>
+      <c r="D45">
+        <v>65.3831886252724</v>
+      </c>
+      <c r="E45">
+        <v>8.349999999999998</v>
+      </c>
+      <c r="F45">
+        <v>27.95</v>
+      </c>
+      <c r="G45">
+        <v>4.77</v>
+      </c>
+      <c r="H45">
+        <v>45.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>12.625</v>
+      </c>
+      <c r="K45">
+        <v>3.25</v>
+      </c>
+      <c r="L45">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M45">
+        <v>1.383525</v>
+      </c>
+      <c r="N45">
+        <v>7.991474999999998</v>
+      </c>
+      <c r="O45">
+        <v>1.19872125</v>
+      </c>
+      <c r="P45">
+        <v>6.792753749999998</v>
+      </c>
+      <c r="Q45">
+        <v>10.04275375</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1158543697377724</v>
+      </c>
+      <c r="T45">
+        <v>1.319961138825422</v>
+      </c>
+      <c r="U45">
+        <v>0.0495</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.042075</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>6.776169566867239</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08409156692784103</v>
+      </c>
+      <c r="C46">
+        <v>41.607574790782</v>
+      </c>
+      <c r="D46">
+        <v>65.43757479078201</v>
+      </c>
+      <c r="E46">
+        <v>9</v>
+      </c>
+      <c r="F46">
+        <v>28.6</v>
+      </c>
+      <c r="G46">
+        <v>4.77</v>
+      </c>
+      <c r="H46">
+        <v>45.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>12.625</v>
+      </c>
+      <c r="K46">
+        <v>3.25</v>
+      </c>
+      <c r="L46">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M46">
+        <v>1.4157</v>
+      </c>
+      <c r="N46">
+        <v>7.959299999999998</v>
+      </c>
+      <c r="O46">
+        <v>1.193895</v>
+      </c>
+      <c r="P46">
+        <v>6.765404999999999</v>
+      </c>
+      <c r="Q46">
+        <v>10.015405</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1171045837997161</v>
+      </c>
+      <c r="T46">
+        <v>1.341377626723444</v>
+      </c>
+      <c r="U46">
+        <v>0.0495</v>
+      </c>
+      <c r="V46">
+        <v>0.15</v>
+      </c>
+      <c r="W46">
+        <v>0.042075</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>6.622165713074802</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08405389310515179</v>
+      </c>
+      <c r="C47">
+        <v>41.01205150915303</v>
+      </c>
+      <c r="D47">
+        <v>65.49205150915303</v>
+      </c>
+      <c r="E47">
+        <v>9.649999999999999</v>
+      </c>
+      <c r="F47">
+        <v>29.25</v>
+      </c>
+      <c r="G47">
+        <v>4.77</v>
+      </c>
+      <c r="H47">
+        <v>45.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>12.625</v>
+      </c>
+      <c r="K47">
+        <v>3.25</v>
+      </c>
+      <c r="L47">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M47">
+        <v>1.447875</v>
+      </c>
+      <c r="N47">
+        <v>7.927124999999998</v>
+      </c>
+      <c r="O47">
+        <v>1.18906875</v>
+      </c>
+      <c r="P47">
+        <v>6.738056249999999</v>
+      </c>
+      <c r="Q47">
+        <v>9.98805625</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1184002601911851</v>
+      </c>
+      <c r="T47">
+        <v>1.363572895999577</v>
+      </c>
+      <c r="U47">
+        <v>0.0495</v>
+      </c>
+      <c r="V47">
+        <v>0.15</v>
+      </c>
+      <c r="W47">
+        <v>0.042075</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>6.475006475006474</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08401621928246254</v>
+      </c>
+      <c r="C48">
+        <v>40.41661900672945</v>
+      </c>
+      <c r="D48">
+        <v>65.54661900672946</v>
+      </c>
+      <c r="E48">
+        <v>10.3</v>
+      </c>
+      <c r="F48">
+        <v>29.9</v>
+      </c>
+      <c r="G48">
+        <v>4.77</v>
+      </c>
+      <c r="H48">
+        <v>45.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>12.625</v>
+      </c>
+      <c r="K48">
+        <v>3.25</v>
+      </c>
+      <c r="L48">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M48">
+        <v>1.48005</v>
+      </c>
+      <c r="N48">
+        <v>7.894949999999998</v>
+      </c>
+      <c r="O48">
+        <v>1.1842425</v>
+      </c>
+      <c r="P48">
+        <v>6.710707499999998</v>
+      </c>
+      <c r="Q48">
+        <v>9.960707499999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1197439245971528</v>
+      </c>
+      <c r="T48">
+        <v>1.386590212285937</v>
+      </c>
+      <c r="U48">
+        <v>0.0495</v>
+      </c>
+      <c r="V48">
+        <v>0.15</v>
+      </c>
+      <c r="W48">
+        <v>0.042075</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>6.334245464680246</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08397854545977329</v>
+      </c>
+      <c r="C49">
+        <v>39.8212775106102</v>
+      </c>
+      <c r="D49">
+        <v>65.6012775106102</v>
+      </c>
+      <c r="E49">
+        <v>10.95</v>
+      </c>
+      <c r="F49">
+        <v>30.55</v>
+      </c>
+      <c r="G49">
+        <v>4.77</v>
+      </c>
+      <c r="H49">
+        <v>45.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>12.625</v>
+      </c>
+      <c r="K49">
+        <v>3.25</v>
+      </c>
+      <c r="L49">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M49">
+        <v>1.512225</v>
+      </c>
+      <c r="N49">
+        <v>7.862774999999998</v>
+      </c>
+      <c r="O49">
+        <v>1.17941625</v>
+      </c>
+      <c r="P49">
+        <v>6.683358749999998</v>
+      </c>
+      <c r="Q49">
+        <v>9.933358749999998</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1211382933203269</v>
+      </c>
+      <c r="T49">
+        <v>1.410476106545366</v>
+      </c>
+      <c r="U49">
+        <v>0.0495</v>
+      </c>
+      <c r="V49">
+        <v>0.15</v>
+      </c>
+      <c r="W49">
+        <v>0.042075</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>6.199474284580666</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08451207163708402</v>
+      </c>
+      <c r="C50">
+        <v>38.40561545322616</v>
+      </c>
+      <c r="D50">
+        <v>64.83561545322617</v>
+      </c>
+      <c r="E50">
+        <v>11.6</v>
+      </c>
+      <c r="F50">
+        <v>31.2</v>
+      </c>
+      <c r="G50">
+        <v>4.77</v>
+      </c>
+      <c r="H50">
+        <v>45.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>12.625</v>
+      </c>
+      <c r="K50">
+        <v>3.25</v>
+      </c>
+      <c r="L50">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M50">
+        <v>1.58808</v>
+      </c>
+      <c r="N50">
+        <v>7.786919999999999</v>
+      </c>
+      <c r="O50">
+        <v>1.168038</v>
+      </c>
+      <c r="P50">
+        <v>6.618881999999999</v>
+      </c>
+      <c r="Q50">
+        <v>9.868881999999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.122586291609777</v>
+      </c>
+      <c r="T50">
+        <v>1.435280689045543</v>
+      </c>
+      <c r="U50">
+        <v>0.0509</v>
+      </c>
+      <c r="V50">
+        <v>0.15</v>
+      </c>
+      <c r="W50">
+        <v>0.043265</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>5.903354994710593</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08448629781439476</v>
+      </c>
+      <c r="C51">
+        <v>37.79219232061493</v>
+      </c>
+      <c r="D51">
+        <v>64.87219232061493</v>
+      </c>
+      <c r="E51">
+        <v>12.25</v>
+      </c>
+      <c r="F51">
+        <v>31.85</v>
+      </c>
+      <c r="G51">
+        <v>4.77</v>
+      </c>
+      <c r="H51">
+        <v>45.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>12.625</v>
+      </c>
+      <c r="K51">
+        <v>3.25</v>
+      </c>
+      <c r="L51">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M51">
+        <v>1.621165</v>
+      </c>
+      <c r="N51">
+        <v>7.753834999999999</v>
+      </c>
+      <c r="O51">
+        <v>1.16307525</v>
+      </c>
+      <c r="P51">
+        <v>6.590759749999999</v>
+      </c>
+      <c r="Q51">
+        <v>9.84075975</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1240910741458721</v>
+      </c>
+      <c r="T51">
+        <v>1.461058000271217</v>
+      </c>
+      <c r="U51">
+        <v>0.0509</v>
+      </c>
+      <c r="V51">
+        <v>0.15</v>
+      </c>
+      <c r="W51">
+        <v>0.043265</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>5.782878362165479</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08446052399170553</v>
+      </c>
+      <c r="C52">
+        <v>37.17881048081468</v>
+      </c>
+      <c r="D52">
+        <v>64.90881048081468</v>
+      </c>
+      <c r="E52">
+        <v>12.9</v>
+      </c>
+      <c r="F52">
+        <v>32.5</v>
+      </c>
+      <c r="G52">
+        <v>4.77</v>
+      </c>
+      <c r="H52">
+        <v>45.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>12.625</v>
+      </c>
+      <c r="K52">
+        <v>3.25</v>
+      </c>
+      <c r="L52">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M52">
+        <v>1.65425</v>
+      </c>
+      <c r="N52">
+        <v>7.720749999999998</v>
+      </c>
+      <c r="O52">
+        <v>1.1581125</v>
+      </c>
+      <c r="P52">
+        <v>6.562637499999998</v>
+      </c>
+      <c r="Q52">
+        <v>9.812637499999997</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1256560479834111</v>
+      </c>
+      <c r="T52">
+        <v>1.487866403945919</v>
+      </c>
+      <c r="U52">
+        <v>0.0509</v>
+      </c>
+      <c r="V52">
+        <v>0.15</v>
+      </c>
+      <c r="W52">
+        <v>0.043265</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>5.667220794922169</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08443475016901626</v>
+      </c>
+      <c r="C53">
+        <v>36.56547000379022</v>
+      </c>
+      <c r="D53">
+        <v>64.94547000379022</v>
+      </c>
+      <c r="E53">
+        <v>13.55</v>
+      </c>
+      <c r="F53">
+        <v>33.15</v>
+      </c>
+      <c r="G53">
+        <v>4.77</v>
+      </c>
+      <c r="H53">
+        <v>45.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>12.625</v>
+      </c>
+      <c r="K53">
+        <v>3.25</v>
+      </c>
+      <c r="L53">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M53">
+        <v>1.687335</v>
+      </c>
+      <c r="N53">
+        <v>7.687664999999998</v>
+      </c>
+      <c r="O53">
+        <v>1.15314975</v>
+      </c>
+      <c r="P53">
+        <v>6.534515249999998</v>
+      </c>
+      <c r="Q53">
+        <v>9.784515249999998</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1272848983041148</v>
+      </c>
+      <c r="T53">
+        <v>1.515769028178771</v>
+      </c>
+      <c r="U53">
+        <v>0.0509</v>
+      </c>
+      <c r="V53">
+        <v>0.15</v>
+      </c>
+      <c r="W53">
+        <v>0.043265</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>5.556098818551146</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08440897634632702</v>
+      </c>
+      <c r="C54">
+        <v>35.95217095966427</v>
+      </c>
+      <c r="D54">
+        <v>64.98217095966427</v>
+      </c>
+      <c r="E54">
+        <v>14.2</v>
+      </c>
+      <c r="F54">
+        <v>33.8</v>
+      </c>
+      <c r="G54">
+        <v>4.77</v>
+      </c>
+      <c r="H54">
+        <v>45.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>12.625</v>
+      </c>
+      <c r="K54">
+        <v>3.25</v>
+      </c>
+      <c r="L54">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M54">
+        <v>1.72042</v>
+      </c>
+      <c r="N54">
+        <v>7.654579999999997</v>
+      </c>
+      <c r="O54">
+        <v>1.148187</v>
+      </c>
+      <c r="P54">
+        <v>6.506392999999997</v>
+      </c>
+      <c r="Q54">
+        <v>9.756392999999997</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1289816173881813</v>
+      </c>
+      <c r="T54">
+        <v>1.544834261754659</v>
+      </c>
+      <c r="U54">
+        <v>0.0509</v>
+      </c>
+      <c r="V54">
+        <v>0.15</v>
+      </c>
+      <c r="W54">
+        <v>0.043265</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>5.449250764348238</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08438320252363776</v>
+      </c>
+      <c r="C55">
+        <v>35.33891341871832</v>
+      </c>
+      <c r="D55">
+        <v>65.01891341871833</v>
+      </c>
+      <c r="E55">
+        <v>14.85</v>
+      </c>
+      <c r="F55">
+        <v>34.45</v>
+      </c>
+      <c r="G55">
+        <v>4.77</v>
+      </c>
+      <c r="H55">
+        <v>45.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>12.625</v>
+      </c>
+      <c r="K55">
+        <v>3.25</v>
+      </c>
+      <c r="L55">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M55">
+        <v>1.753505</v>
+      </c>
+      <c r="N55">
+        <v>7.621494999999998</v>
+      </c>
+      <c r="O55">
+        <v>1.14322425</v>
+      </c>
+      <c r="P55">
+        <v>6.478270749999998</v>
+      </c>
+      <c r="Q55">
+        <v>9.728270749999998</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1307505372843357</v>
+      </c>
+      <c r="T55">
+        <v>1.575136313780585</v>
+      </c>
+      <c r="U55">
+        <v>0.0509</v>
+      </c>
+      <c r="V55">
+        <v>0.15</v>
+      </c>
+      <c r="W55">
+        <v>0.043265</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>5.346434712190725</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08435742870094851</v>
+      </c>
+      <c r="C56">
+        <v>34.72569745139283</v>
+      </c>
+      <c r="D56">
+        <v>65.05569745139283</v>
+      </c>
+      <c r="E56">
+        <v>15.5</v>
+      </c>
+      <c r="F56">
+        <v>35.1</v>
+      </c>
+      <c r="G56">
+        <v>4.77</v>
+      </c>
+      <c r="H56">
+        <v>45.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>12.625</v>
+      </c>
+      <c r="K56">
+        <v>3.25</v>
+      </c>
+      <c r="L56">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M56">
+        <v>1.78659</v>
+      </c>
+      <c r="N56">
+        <v>7.588409999999998</v>
+      </c>
+      <c r="O56">
+        <v>1.1382615</v>
+      </c>
+      <c r="P56">
+        <v>6.450148499999998</v>
+      </c>
+      <c r="Q56">
+        <v>9.700148499999997</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1325963667411924</v>
+      </c>
+      <c r="T56">
+        <v>1.606755846329377</v>
+      </c>
+      <c r="U56">
+        <v>0.0509</v>
+      </c>
+      <c r="V56">
+        <v>0.15</v>
+      </c>
+      <c r="W56">
+        <v>0.043265</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>5.247426661964971</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08433165487825926</v>
+      </c>
+      <c r="C57">
+        <v>34.11252312828775</v>
+      </c>
+      <c r="D57">
+        <v>65.09252312828775</v>
+      </c>
+      <c r="E57">
+        <v>16.15</v>
+      </c>
+      <c r="F57">
+        <v>35.75</v>
+      </c>
+      <c r="G57">
+        <v>4.77</v>
+      </c>
+      <c r="H57">
+        <v>45.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>12.625</v>
+      </c>
+      <c r="K57">
+        <v>3.25</v>
+      </c>
+      <c r="L57">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M57">
+        <v>1.819675</v>
+      </c>
+      <c r="N57">
+        <v>7.555324999999998</v>
+      </c>
+      <c r="O57">
+        <v>1.13329875</v>
+      </c>
+      <c r="P57">
+        <v>6.422026249999998</v>
+      </c>
+      <c r="Q57">
+        <v>9.672026249999998</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1345242330627984</v>
+      </c>
+      <c r="T57">
+        <v>1.639780691435893</v>
+      </c>
+      <c r="U57">
+        <v>0.0509</v>
+      </c>
+      <c r="V57">
+        <v>0.15</v>
+      </c>
+      <c r="W57">
+        <v>0.043265</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>5.1520189044747</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.08430588105557001</v>
+      </c>
+      <c r="C58">
+        <v>33.49939052016299</v>
+      </c>
+      <c r="D58">
+        <v>65.129390520163</v>
+      </c>
+      <c r="E58">
+        <v>16.8</v>
+      </c>
+      <c r="F58">
+        <v>36.40000000000001</v>
+      </c>
+      <c r="G58">
+        <v>4.77</v>
+      </c>
+      <c r="H58">
+        <v>45.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>12.625</v>
+      </c>
+      <c r="K58">
+        <v>3.25</v>
+      </c>
+      <c r="L58">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M58">
+        <v>1.85276</v>
+      </c>
+      <c r="N58">
+        <v>7.522239999999998</v>
+      </c>
+      <c r="O58">
+        <v>1.128336</v>
+      </c>
+      <c r="P58">
+        <v>6.393903999999998</v>
+      </c>
+      <c r="Q58">
+        <v>9.643903999999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.13653972967175</v>
+      </c>
+      <c r="T58">
+        <v>1.674306665865432</v>
+      </c>
+      <c r="U58">
+        <v>0.0509</v>
+      </c>
+      <c r="V58">
+        <v>0.15</v>
+      </c>
+      <c r="W58">
+        <v>0.043265</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>5.060018566894793</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08428010723288075</v>
+      </c>
+      <c r="C59">
+        <v>32.88629969793892</v>
+      </c>
+      <c r="D59">
+        <v>65.16629969793892</v>
+      </c>
+      <c r="E59">
+        <v>17.45</v>
+      </c>
+      <c r="F59">
+        <v>37.05</v>
+      </c>
+      <c r="G59">
+        <v>4.77</v>
+      </c>
+      <c r="H59">
+        <v>45.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>12.625</v>
+      </c>
+      <c r="K59">
+        <v>3.25</v>
+      </c>
+      <c r="L59">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M59">
+        <v>1.885845</v>
+      </c>
+      <c r="N59">
+        <v>7.489154999999998</v>
+      </c>
+      <c r="O59">
+        <v>1.12337325</v>
+      </c>
+      <c r="P59">
+        <v>6.365781749999998</v>
+      </c>
+      <c r="Q59">
+        <v>9.615781749999998</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.138648970309025</v>
+      </c>
+      <c r="T59">
+        <v>1.710438499570764</v>
+      </c>
+      <c r="U59">
+        <v>0.0509</v>
+      </c>
+      <c r="V59">
+        <v>0.15</v>
+      </c>
+      <c r="W59">
+        <v>0.043265</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>4.971246311335236</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.08425433341019149</v>
+      </c>
+      <c r="C60">
+        <v>32.27325073269665</v>
+      </c>
+      <c r="D60">
+        <v>65.20325073269665</v>
+      </c>
+      <c r="E60">
+        <v>18.09999999999999</v>
+      </c>
+      <c r="F60">
+        <v>37.7</v>
+      </c>
+      <c r="G60">
+        <v>4.77</v>
+      </c>
+      <c r="H60">
+        <v>45.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>12.625</v>
+      </c>
+      <c r="K60">
+        <v>3.25</v>
+      </c>
+      <c r="L60">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M60">
+        <v>1.91893</v>
+      </c>
+      <c r="N60">
+        <v>7.456069999999999</v>
+      </c>
+      <c r="O60">
+        <v>1.1184105</v>
+      </c>
+      <c r="P60">
+        <v>6.337659499999999</v>
+      </c>
+      <c r="Q60">
+        <v>9.587659499999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1408586509766464</v>
+      </c>
+      <c r="T60">
+        <v>1.748290896785874</v>
+      </c>
+      <c r="U60">
+        <v>0.0509</v>
+      </c>
+      <c r="V60">
+        <v>0.15</v>
+      </c>
+      <c r="W60">
+        <v>0.043265</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>4.885535168036354</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.08422855958750225</v>
+      </c>
+      <c r="C61">
+        <v>31.66024369567867</v>
+      </c>
+      <c r="D61">
+        <v>65.24024369567867</v>
+      </c>
+      <c r="E61">
+        <v>18.75</v>
+      </c>
+      <c r="F61">
+        <v>38.35</v>
+      </c>
+      <c r="G61">
+        <v>4.77</v>
+      </c>
+      <c r="H61">
+        <v>45.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>12.625</v>
+      </c>
+      <c r="K61">
+        <v>3.25</v>
+      </c>
+      <c r="L61">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M61">
+        <v>1.952015</v>
+      </c>
+      <c r="N61">
+        <v>7.422984999999998</v>
+      </c>
+      <c r="O61">
+        <v>1.11344775</v>
+      </c>
+      <c r="P61">
+        <v>6.309537249999998</v>
+      </c>
+      <c r="Q61">
+        <v>9.559537249999998</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1431761209451274</v>
+      </c>
+      <c r="T61">
+        <v>1.78798975240172</v>
+      </c>
+      <c r="U61">
+        <v>0.0509</v>
+      </c>
+      <c r="V61">
+        <v>0.15</v>
+      </c>
+      <c r="W61">
+        <v>0.043265</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>4.802729487222177</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08420278576481299</v>
+      </c>
+      <c r="C62">
+        <v>31.04727865828926</v>
+      </c>
+      <c r="D62">
+        <v>65.27727865828926</v>
+      </c>
+      <c r="E62">
+        <v>19.4</v>
+      </c>
+      <c r="F62">
+        <v>39</v>
+      </c>
+      <c r="G62">
+        <v>4.77</v>
+      </c>
+      <c r="H62">
+        <v>45.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>12.625</v>
+      </c>
+      <c r="K62">
+        <v>3.25</v>
+      </c>
+      <c r="L62">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M62">
+        <v>1.9851</v>
+      </c>
+      <c r="N62">
+        <v>7.389899999999998</v>
+      </c>
+      <c r="O62">
+        <v>1.108485</v>
+      </c>
+      <c r="P62">
+        <v>6.281414999999998</v>
+      </c>
+      <c r="Q62">
+        <v>9.531414999999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1456094644120325</v>
+      </c>
+      <c r="T62">
+        <v>1.829673550798359</v>
+      </c>
+      <c r="U62">
+        <v>0.0509</v>
+      </c>
+      <c r="V62">
+        <v>0.15</v>
+      </c>
+      <c r="W62">
+        <v>0.043265</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>4.722683995768474</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.08417701194212374</v>
+      </c>
+      <c r="C63">
+        <v>30.43435569209486</v>
+      </c>
+      <c r="D63">
+        <v>65.31435569209486</v>
+      </c>
+      <c r="E63">
+        <v>20.05</v>
+      </c>
+      <c r="F63">
+        <v>39.65</v>
+      </c>
+      <c r="G63">
+        <v>4.77</v>
+      </c>
+      <c r="H63">
+        <v>45.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>12.625</v>
+      </c>
+      <c r="K63">
+        <v>3.25</v>
+      </c>
+      <c r="L63">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M63">
+        <v>2.018185</v>
+      </c>
+      <c r="N63">
+        <v>7.356814999999998</v>
+      </c>
+      <c r="O63">
+        <v>1.10352225</v>
+      </c>
+      <c r="P63">
+        <v>6.253292749999998</v>
+      </c>
+      <c r="Q63">
+        <v>9.503292749999998</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1481675947233942</v>
+      </c>
+      <c r="T63">
+        <v>1.873494979882006</v>
+      </c>
+      <c r="U63">
+        <v>0.0509</v>
+      </c>
+      <c r="V63">
+        <v>0.15</v>
+      </c>
+      <c r="W63">
+        <v>0.043265</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>4.645262946657516</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.08415123811943451</v>
+      </c>
+      <c r="C64">
+        <v>29.82147486882465</v>
+      </c>
+      <c r="D64">
+        <v>65.35147486882465</v>
+      </c>
+      <c r="E64">
+        <v>20.7</v>
+      </c>
+      <c r="F64">
+        <v>40.3</v>
+      </c>
+      <c r="G64">
+        <v>4.77</v>
+      </c>
+      <c r="H64">
+        <v>45.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>12.625</v>
+      </c>
+      <c r="K64">
+        <v>3.25</v>
+      </c>
+      <c r="L64">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M64">
+        <v>2.05127</v>
+      </c>
+      <c r="N64">
+        <v>7.323729999999999</v>
+      </c>
+      <c r="O64">
+        <v>1.0985595</v>
+      </c>
+      <c r="P64">
+        <v>6.225170499999999</v>
+      </c>
+      <c r="Q64">
+        <v>9.475170499999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1508603634721961</v>
+      </c>
+      <c r="T64">
+        <v>1.919622799970055</v>
+      </c>
+      <c r="U64">
+        <v>0.0509</v>
+      </c>
+      <c r="V64">
+        <v>0.15</v>
+      </c>
+      <c r="W64">
+        <v>0.043265</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>4.570339350743685</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.08551776429674525</v>
+      </c>
+      <c r="C65">
+        <v>27.25990006471237</v>
+      </c>
+      <c r="D65">
+        <v>63.43990006471238</v>
+      </c>
+      <c r="E65">
+        <v>21.35</v>
+      </c>
+      <c r="F65">
+        <v>40.95</v>
+      </c>
+      <c r="G65">
+        <v>4.77</v>
+      </c>
+      <c r="H65">
+        <v>45.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>12.625</v>
+      </c>
+      <c r="K65">
+        <v>3.25</v>
+      </c>
+      <c r="L65">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M65">
+        <v>2.190825</v>
+      </c>
+      <c r="N65">
+        <v>7.184174999999998</v>
+      </c>
+      <c r="O65">
+        <v>1.07762625</v>
+      </c>
+      <c r="P65">
+        <v>6.106548749999998</v>
+      </c>
+      <c r="Q65">
+        <v>9.356548749999998</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1536986872885007</v>
+      </c>
+      <c r="T65">
+        <v>1.968244015738539</v>
+      </c>
+      <c r="U65">
+        <v>0.0535</v>
+      </c>
+      <c r="V65">
+        <v>0.15</v>
+      </c>
+      <c r="W65">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>4.279209886686521</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.08551409047405598</v>
+      </c>
+      <c r="C66">
+        <v>26.61488928620631</v>
+      </c>
+      <c r="D66">
+        <v>63.44488928620632</v>
+      </c>
+      <c r="E66">
+        <v>22</v>
+      </c>
+      <c r="F66">
+        <v>41.6</v>
+      </c>
+      <c r="G66">
+        <v>4.77</v>
+      </c>
+      <c r="H66">
+        <v>45.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>12.625</v>
+      </c>
+      <c r="K66">
+        <v>3.25</v>
+      </c>
+      <c r="L66">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M66">
+        <v>2.2256</v>
+      </c>
+      <c r="N66">
+        <v>7.149399999999998</v>
+      </c>
+      <c r="O66">
+        <v>1.07241</v>
+      </c>
+      <c r="P66">
+        <v>6.076989999999999</v>
+      </c>
+      <c r="Q66">
+        <v>9.326989999999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1566946957612666</v>
+      </c>
+      <c r="T66">
+        <v>2.019566410160827</v>
+      </c>
+      <c r="U66">
+        <v>0.0535</v>
+      </c>
+      <c r="V66">
+        <v>0.15</v>
+      </c>
+      <c r="W66">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>4.212347232207044</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.08551041665136673</v>
+      </c>
+      <c r="C67">
+        <v>25.9698792925151</v>
+      </c>
+      <c r="D67">
+        <v>63.4498792925151</v>
+      </c>
+      <c r="E67">
+        <v>22.65</v>
+      </c>
+      <c r="F67">
+        <v>42.25</v>
+      </c>
+      <c r="G67">
+        <v>4.77</v>
+      </c>
+      <c r="H67">
+        <v>45.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>12.625</v>
+      </c>
+      <c r="K67">
+        <v>3.25</v>
+      </c>
+      <c r="L67">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M67">
+        <v>2.260375</v>
+      </c>
+      <c r="N67">
+        <v>7.114624999999998</v>
+      </c>
+      <c r="O67">
+        <v>1.06719375</v>
+      </c>
+      <c r="P67">
+        <v>6.047431249999999</v>
+      </c>
+      <c r="Q67">
+        <v>9.297431249999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1598619047181907</v>
+      </c>
+      <c r="T67">
+        <v>2.073821512835818</v>
+      </c>
+      <c r="U67">
+        <v>0.0535</v>
+      </c>
+      <c r="V67">
+        <v>0.15</v>
+      </c>
+      <c r="W67">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>4.14754189017309</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.08550674282867748</v>
+      </c>
+      <c r="C68">
+        <v>25.32487008382397</v>
+      </c>
+      <c r="D68">
+        <v>63.45487008382397</v>
+      </c>
+      <c r="E68">
+        <v>23.3</v>
+      </c>
+      <c r="F68">
+        <v>42.9</v>
+      </c>
+      <c r="G68">
+        <v>4.77</v>
+      </c>
+      <c r="H68">
+        <v>45.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>12.625</v>
+      </c>
+      <c r="K68">
+        <v>3.25</v>
+      </c>
+      <c r="L68">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M68">
+        <v>2.29515</v>
+      </c>
+      <c r="N68">
+        <v>7.079849999999999</v>
+      </c>
+      <c r="O68">
+        <v>1.0619775</v>
+      </c>
+      <c r="P68">
+        <v>6.017872499999999</v>
+      </c>
+      <c r="Q68">
+        <v>9.267872499999999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1632154200843456</v>
+      </c>
+      <c r="T68">
+        <v>2.131268092138749</v>
+      </c>
+      <c r="U68">
+        <v>0.0535</v>
+      </c>
+      <c r="V68">
+        <v>0.15</v>
+      </c>
+      <c r="W68">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>4.084700346382588</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.08550306900598822</v>
+      </c>
+      <c r="C69">
+        <v>24.67986166031817</v>
+      </c>
+      <c r="D69">
+        <v>63.45986166031818</v>
+      </c>
+      <c r="E69">
+        <v>23.95</v>
+      </c>
+      <c r="F69">
+        <v>43.55</v>
+      </c>
+      <c r="G69">
+        <v>4.77</v>
+      </c>
+      <c r="H69">
+        <v>45.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>12.625</v>
+      </c>
+      <c r="K69">
+        <v>3.25</v>
+      </c>
+      <c r="L69">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M69">
+        <v>2.329925</v>
+      </c>
+      <c r="N69">
+        <v>7.045074999999998</v>
+      </c>
+      <c r="O69">
+        <v>1.05676125</v>
+      </c>
+      <c r="P69">
+        <v>5.988313749999998</v>
+      </c>
+      <c r="Q69">
+        <v>9.238313749999998</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.166772178806025</v>
+      </c>
+      <c r="T69">
+        <v>2.192196282308525</v>
+      </c>
+      <c r="U69">
+        <v>0.0535</v>
+      </c>
+      <c r="V69">
+        <v>0.15</v>
+      </c>
+      <c r="W69">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>4.023734669570908</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.08705999518329897</v>
+      </c>
+      <c r="C70">
+        <v>21.98256929213203</v>
+      </c>
+      <c r="D70">
+        <v>61.41256929213203</v>
+      </c>
+      <c r="E70">
+        <v>24.6</v>
+      </c>
+      <c r="F70">
+        <v>44.2</v>
+      </c>
+      <c r="G70">
+        <v>4.77</v>
+      </c>
+      <c r="H70">
+        <v>45.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>12.625</v>
+      </c>
+      <c r="K70">
+        <v>3.25</v>
+      </c>
+      <c r="L70">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M70">
+        <v>2.48404</v>
+      </c>
+      <c r="N70">
+        <v>6.890959999999998</v>
+      </c>
+      <c r="O70">
+        <v>1.033644</v>
+      </c>
+      <c r="P70">
+        <v>5.857315999999998</v>
+      </c>
+      <c r="Q70">
+        <v>9.107315999999997</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1705512349478093</v>
+      </c>
+      <c r="T70">
+        <v>2.256932484363911</v>
+      </c>
+      <c r="U70">
+        <v>0.0562</v>
+      </c>
+      <c r="V70">
+        <v>0.15</v>
+      </c>
+      <c r="W70">
+        <v>0.04777</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>3.774093814914413</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.08707927136060974</v>
+      </c>
+      <c r="C71">
+        <v>21.30804946112749</v>
+      </c>
+      <c r="D71">
+        <v>61.38804946112749</v>
+      </c>
+      <c r="E71">
+        <v>25.25</v>
+      </c>
+      <c r="F71">
+        <v>44.85</v>
+      </c>
+      <c r="G71">
+        <v>4.77</v>
+      </c>
+      <c r="H71">
+        <v>45.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>12.625</v>
+      </c>
+      <c r="K71">
+        <v>3.25</v>
+      </c>
+      <c r="L71">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M71">
+        <v>2.52057</v>
+      </c>
+      <c r="N71">
+        <v>6.854429999999998</v>
+      </c>
+      <c r="O71">
+        <v>1.0281645</v>
+      </c>
+      <c r="P71">
+        <v>5.826265499999998</v>
+      </c>
+      <c r="Q71">
+        <v>9.076265499999998</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1745741011632572</v>
+      </c>
+      <c r="T71">
+        <v>2.325845215584161</v>
+      </c>
+      <c r="U71">
+        <v>0.0562</v>
+      </c>
+      <c r="V71">
+        <v>0.15</v>
+      </c>
+      <c r="W71">
+        <v>0.04777</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>3.719396803104059</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.08709854753792047</v>
+      </c>
+      <c r="C72">
+        <v>20.63354920208254</v>
+      </c>
+      <c r="D72">
+        <v>61.36354920208255</v>
+      </c>
+      <c r="E72">
+        <v>25.90000000000001</v>
+      </c>
+      <c r="F72">
+        <v>45.50000000000001</v>
+      </c>
+      <c r="G72">
+        <v>4.77</v>
+      </c>
+      <c r="H72">
+        <v>45.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>12.625</v>
+      </c>
+      <c r="K72">
+        <v>3.25</v>
+      </c>
+      <c r="L72">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M72">
+        <v>2.557100000000001</v>
+      </c>
+      <c r="N72">
+        <v>6.817899999999998</v>
+      </c>
+      <c r="O72">
+        <v>1.022685</v>
+      </c>
+      <c r="P72">
+        <v>5.795214999999999</v>
+      </c>
+      <c r="Q72">
+        <v>9.045214999999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1788651584597349</v>
+      </c>
+      <c r="T72">
+        <v>2.399352128885762</v>
+      </c>
+      <c r="U72">
+        <v>0.0562</v>
+      </c>
+      <c r="V72">
+        <v>0.15</v>
+      </c>
+      <c r="W72">
+        <v>0.04777</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>3.666262563059715</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.08711782371523123</v>
+      </c>
+      <c r="C73">
+        <v>19.95906849157274</v>
+      </c>
+      <c r="D73">
+        <v>61.33906849157274</v>
+      </c>
+      <c r="E73">
+        <v>26.55</v>
+      </c>
+      <c r="F73">
+        <v>46.15</v>
+      </c>
+      <c r="G73">
+        <v>4.77</v>
+      </c>
+      <c r="H73">
+        <v>45.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>12.625</v>
+      </c>
+      <c r="K73">
+        <v>3.25</v>
+      </c>
+      <c r="L73">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M73">
+        <v>2.59363</v>
+      </c>
+      <c r="N73">
+        <v>6.781369999999998</v>
+      </c>
+      <c r="O73">
+        <v>1.0172055</v>
+      </c>
+      <c r="P73">
+        <v>5.764164499999998</v>
+      </c>
+      <c r="Q73">
+        <v>9.014164499999998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1834521507421766</v>
+      </c>
+      <c r="T73">
+        <v>2.477928484484023</v>
+      </c>
+      <c r="U73">
+        <v>0.0562</v>
+      </c>
+      <c r="V73">
+        <v>0.15</v>
+      </c>
+      <c r="W73">
+        <v>0.04777</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>3.61462506217155</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.08713709989254197</v>
+      </c>
+      <c r="C74">
+        <v>19.28460730621104</v>
+      </c>
+      <c r="D74">
+        <v>61.31460730621104</v>
+      </c>
+      <c r="E74">
+        <v>27.2</v>
+      </c>
+      <c r="F74">
+        <v>46.8</v>
+      </c>
+      <c r="G74">
+        <v>4.77</v>
+      </c>
+      <c r="H74">
+        <v>45.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>12.625</v>
+      </c>
+      <c r="K74">
+        <v>3.25</v>
+      </c>
+      <c r="L74">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M74">
+        <v>2.63016</v>
+      </c>
+      <c r="N74">
+        <v>6.744839999999998</v>
+      </c>
+      <c r="O74">
+        <v>1.011726</v>
+      </c>
+      <c r="P74">
+        <v>5.733113999999999</v>
+      </c>
+      <c r="Q74">
+        <v>8.983113999999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.188366785330507</v>
+      </c>
+      <c r="T74">
+        <v>2.562117436910733</v>
+      </c>
+      <c r="U74">
+        <v>0.0562</v>
+      </c>
+      <c r="V74">
+        <v>0.15</v>
+      </c>
+      <c r="W74">
+        <v>0.04777</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>3.564421936308057</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.08715637606985271</v>
+      </c>
+      <c r="C75">
+        <v>18.61016562264761</v>
+      </c>
+      <c r="D75">
+        <v>61.29016562264761</v>
+      </c>
+      <c r="E75">
+        <v>27.84999999999999</v>
+      </c>
+      <c r="F75">
+        <v>47.45</v>
+      </c>
+      <c r="G75">
+        <v>4.77</v>
+      </c>
+      <c r="H75">
+        <v>45.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>12.625</v>
+      </c>
+      <c r="K75">
+        <v>3.25</v>
+      </c>
+      <c r="L75">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M75">
+        <v>2.66669</v>
+      </c>
+      <c r="N75">
+        <v>6.708309999999999</v>
+      </c>
+      <c r="O75">
+        <v>1.0062465</v>
+      </c>
+      <c r="P75">
+        <v>5.7020635</v>
+      </c>
+      <c r="Q75">
+        <v>8.9520635</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1936454669253804</v>
+      </c>
+      <c r="T75">
+        <v>2.652542608035717</v>
+      </c>
+      <c r="U75">
+        <v>0.0562</v>
+      </c>
+      <c r="V75">
+        <v>0.15</v>
+      </c>
+      <c r="W75">
+        <v>0.04777</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>3.515594238550413</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.09013195224716347</v>
+      </c>
+      <c r="C76">
+        <v>14.4073384117897</v>
+      </c>
+      <c r="D76">
+        <v>57.7373384117897</v>
+      </c>
+      <c r="E76">
+        <v>28.5</v>
+      </c>
+      <c r="F76">
+        <v>48.1</v>
+      </c>
+      <c r="G76">
+        <v>4.77</v>
+      </c>
+      <c r="H76">
+        <v>45.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>12.625</v>
+      </c>
+      <c r="K76">
+        <v>3.25</v>
+      </c>
+      <c r="L76">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M76">
+        <v>2.92929</v>
+      </c>
+      <c r="N76">
+        <v>6.445709999999998</v>
+      </c>
+      <c r="O76">
+        <v>0.9668564999999997</v>
+      </c>
+      <c r="P76">
+        <v>5.478853499999999</v>
+      </c>
+      <c r="Q76">
+        <v>8.7288535</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1993302009506287</v>
+      </c>
+      <c r="T76">
+        <v>2.749923561554931</v>
+      </c>
+      <c r="U76">
+        <v>0.0609</v>
+      </c>
+      <c r="V76">
+        <v>0.15</v>
+      </c>
+      <c r="W76">
+        <v>0.051765</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>3.200434234916993</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09019117842447422</v>
+      </c>
+      <c r="C77">
+        <v>13.69079855131048</v>
+      </c>
+      <c r="D77">
+        <v>57.67079855131048</v>
+      </c>
+      <c r="E77">
+        <v>29.15</v>
+      </c>
+      <c r="F77">
+        <v>48.75</v>
+      </c>
+      <c r="G77">
+        <v>4.77</v>
+      </c>
+      <c r="H77">
+        <v>45.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>12.625</v>
+      </c>
+      <c r="K77">
+        <v>3.25</v>
+      </c>
+      <c r="L77">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M77">
+        <v>2.968875</v>
+      </c>
+      <c r="N77">
+        <v>6.406124999999998</v>
+      </c>
+      <c r="O77">
+        <v>0.9609187499999996</v>
+      </c>
+      <c r="P77">
+        <v>5.445206249999998</v>
+      </c>
+      <c r="Q77">
+        <v>8.695206249999998</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2054697136978968</v>
+      </c>
+      <c r="T77">
+        <v>2.855094991355682</v>
+      </c>
+      <c r="U77">
+        <v>0.0609</v>
+      </c>
+      <c r="V77">
+        <v>0.15</v>
+      </c>
+      <c r="W77">
+        <v>0.051765</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>3.157761778451433</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.09025040460178496</v>
+      </c>
+      <c r="C78">
+        <v>12.97441188307943</v>
+      </c>
+      <c r="D78">
+        <v>57.60441188307944</v>
+      </c>
+      <c r="E78">
+        <v>29.8</v>
+      </c>
+      <c r="F78">
+        <v>49.4</v>
+      </c>
+      <c r="G78">
+        <v>4.77</v>
+      </c>
+      <c r="H78">
+        <v>45.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>12.625</v>
+      </c>
+      <c r="K78">
+        <v>3.25</v>
+      </c>
+      <c r="L78">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M78">
+        <v>3.00846</v>
+      </c>
+      <c r="N78">
+        <v>6.366539999999999</v>
+      </c>
+      <c r="O78">
+        <v>0.9549809999999997</v>
+      </c>
+      <c r="P78">
+        <v>5.411558999999999</v>
+      </c>
+      <c r="Q78">
+        <v>8.661558999999999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2121208525074374</v>
+      </c>
+      <c r="T78">
+        <v>2.969030706973163</v>
+      </c>
+      <c r="U78">
+        <v>0.0609</v>
+      </c>
+      <c r="V78">
+        <v>0.15</v>
+      </c>
+      <c r="W78">
+        <v>0.051765</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>3.116212281366546</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.09030963077909571</v>
+      </c>
+      <c r="C79">
+        <v>12.2581778786716</v>
+      </c>
+      <c r="D79">
+        <v>57.5381778786716</v>
+      </c>
+      <c r="E79">
+        <v>30.45</v>
+      </c>
+      <c r="F79">
+        <v>50.05</v>
+      </c>
+      <c r="G79">
+        <v>4.77</v>
+      </c>
+      <c r="H79">
+        <v>45.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>12.625</v>
+      </c>
+      <c r="K79">
+        <v>3.25</v>
+      </c>
+      <c r="L79">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M79">
+        <v>3.048045000000001</v>
+      </c>
+      <c r="N79">
+        <v>6.326954999999998</v>
+      </c>
+      <c r="O79">
+        <v>0.9490432499999997</v>
+      </c>
+      <c r="P79">
+        <v>5.377911749999998</v>
+      </c>
+      <c r="Q79">
+        <v>8.627911749999999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2193503512134596</v>
+      </c>
+      <c r="T79">
+        <v>3.092873876122598</v>
+      </c>
+      <c r="U79">
+        <v>0.0609</v>
+      </c>
+      <c r="V79">
+        <v>0.15</v>
+      </c>
+      <c r="W79">
+        <v>0.051765</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>3.075741991998149</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.09036885695640645</v>
+      </c>
+      <c r="C80">
+        <v>11.5420960120896</v>
+      </c>
+      <c r="D80">
+        <v>57.4720960120896</v>
+      </c>
+      <c r="E80">
+        <v>31.1</v>
+      </c>
+      <c r="F80">
+        <v>50.7</v>
+      </c>
+      <c r="G80">
+        <v>4.77</v>
+      </c>
+      <c r="H80">
+        <v>45.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>12.625</v>
+      </c>
+      <c r="K80">
+        <v>3.25</v>
+      </c>
+      <c r="L80">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M80">
+        <v>3.08763</v>
+      </c>
+      <c r="N80">
+        <v>6.287369999999997</v>
+      </c>
+      <c r="O80">
+        <v>0.9431054999999996</v>
+      </c>
+      <c r="P80">
+        <v>5.344264499999998</v>
+      </c>
+      <c r="Q80">
+        <v>8.594264499999998</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2272370770745748</v>
+      </c>
+      <c r="T80">
+        <v>3.227975515194708</v>
+      </c>
+      <c r="U80">
+        <v>0.0609</v>
+      </c>
+      <c r="V80">
+        <v>0.15</v>
+      </c>
+      <c r="W80">
+        <v>0.051765</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>3.036309402357147</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.0966730331337172</v>
+      </c>
+      <c r="C81">
+        <v>4.631594377374959</v>
+      </c>
+      <c r="D81">
+        <v>51.21159437737496</v>
+      </c>
+      <c r="E81">
+        <v>31.75</v>
+      </c>
+      <c r="F81">
+        <v>51.35</v>
+      </c>
+      <c r="G81">
+        <v>4.77</v>
+      </c>
+      <c r="H81">
+        <v>45.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>12.625</v>
+      </c>
+      <c r="K81">
+        <v>3.25</v>
+      </c>
+      <c r="L81">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M81">
+        <v>3.60477</v>
+      </c>
+      <c r="N81">
+        <v>5.770229999999998</v>
+      </c>
+      <c r="O81">
+        <v>0.8655344999999997</v>
+      </c>
+      <c r="P81">
+        <v>4.904695499999998</v>
+      </c>
+      <c r="Q81">
+        <v>8.154695499999999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2358749196843677</v>
+      </c>
+      <c r="T81">
+        <v>3.375943977035592</v>
+      </c>
+      <c r="U81">
+        <v>0.0702</v>
+      </c>
+      <c r="V81">
+        <v>0.15</v>
+      </c>
+      <c r="W81">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>2.600720711723632</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.09681130931102795</v>
+      </c>
+      <c r="C82">
+        <v>3.859526049861003</v>
+      </c>
+      <c r="D82">
+        <v>51.089526049861</v>
+      </c>
+      <c r="E82">
+        <v>32.4</v>
+      </c>
+      <c r="F82">
+        <v>52</v>
+      </c>
+      <c r="G82">
+        <v>4.77</v>
+      </c>
+      <c r="H82">
+        <v>45.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>12.625</v>
+      </c>
+      <c r="K82">
+        <v>3.25</v>
+      </c>
+      <c r="L82">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M82">
+        <v>3.6504</v>
+      </c>
+      <c r="N82">
+        <v>5.724599999999999</v>
+      </c>
+      <c r="O82">
+        <v>0.8586899999999998</v>
+      </c>
+      <c r="P82">
+        <v>4.865909999999999</v>
+      </c>
+      <c r="Q82">
+        <v>8.11591</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2453765465551398</v>
+      </c>
+      <c r="T82">
+        <v>3.538709285060564</v>
+      </c>
+      <c r="U82">
+        <v>0.0702</v>
+      </c>
+      <c r="V82">
+        <v>0.15</v>
+      </c>
+      <c r="W82">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>2.568211702827087</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.09694958548833869</v>
+      </c>
+      <c r="C83">
+        <v>3.088038264462952</v>
+      </c>
+      <c r="D83">
+        <v>50.96803826446295</v>
+      </c>
+      <c r="E83">
+        <v>33.05</v>
+      </c>
+      <c r="F83">
+        <v>52.65000000000001</v>
+      </c>
+      <c r="G83">
+        <v>4.77</v>
+      </c>
+      <c r="H83">
+        <v>45.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>12.625</v>
+      </c>
+      <c r="K83">
+        <v>3.25</v>
+      </c>
+      <c r="L83">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M83">
+        <v>3.69603</v>
+      </c>
+      <c r="N83">
+        <v>5.678969999999998</v>
+      </c>
+      <c r="O83">
+        <v>0.8518454999999997</v>
+      </c>
+      <c r="P83">
+        <v>4.827124499999998</v>
+      </c>
+      <c r="Q83">
+        <v>8.077124499999998</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2558783446754669</v>
+      </c>
+      <c r="T83">
+        <v>3.718607783403955</v>
+      </c>
+      <c r="U83">
+        <v>0.0702</v>
+      </c>
+      <c r="V83">
+        <v>0.15</v>
+      </c>
+      <c r="W83">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>2.536505385508234</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.09708786166564945</v>
+      </c>
+      <c r="C84">
+        <v>2.317126889524125</v>
+      </c>
+      <c r="D84">
+        <v>50.84712688952413</v>
+      </c>
+      <c r="E84">
+        <v>33.7</v>
+      </c>
+      <c r="F84">
+        <v>53.3</v>
+      </c>
+      <c r="G84">
+        <v>4.77</v>
+      </c>
+      <c r="H84">
+        <v>45.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>12.625</v>
+      </c>
+      <c r="K84">
+        <v>3.25</v>
+      </c>
+      <c r="L84">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M84">
+        <v>3.74166</v>
+      </c>
+      <c r="N84">
+        <v>5.633339999999998</v>
+      </c>
+      <c r="O84">
+        <v>0.8450009999999997</v>
+      </c>
+      <c r="P84">
+        <v>4.788338999999998</v>
+      </c>
+      <c r="Q84">
+        <v>8.038338999999997</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2675470092536081</v>
+      </c>
+      <c r="T84">
+        <v>3.9184950037855</v>
+      </c>
+      <c r="U84">
+        <v>0.0702</v>
+      </c>
+      <c r="V84">
+        <v>0.15</v>
+      </c>
+      <c r="W84">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>2.505572393002036</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1005419878429602</v>
+      </c>
+      <c r="C85">
+        <v>-1.177491467708961</v>
+      </c>
+      <c r="D85">
+        <v>48.00250853229104</v>
+      </c>
+      <c r="E85">
+        <v>34.35</v>
+      </c>
+      <c r="F85">
+        <v>53.95</v>
+      </c>
+      <c r="G85">
+        <v>4.77</v>
+      </c>
+      <c r="H85">
+        <v>45.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>12.625</v>
+      </c>
+      <c r="K85">
+        <v>3.25</v>
+      </c>
+      <c r="L85">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M85">
+        <v>4.040855</v>
+      </c>
+      <c r="N85">
+        <v>5.334144999999999</v>
+      </c>
+      <c r="O85">
+        <v>0.8001217499999997</v>
+      </c>
+      <c r="P85">
+        <v>4.534023249999999</v>
+      </c>
+      <c r="Q85">
+        <v>7.784023249999999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2805884578997659</v>
+      </c>
+      <c r="T85">
+        <v>4.141898367741343</v>
+      </c>
+      <c r="U85">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V85">
+        <v>0.15</v>
+      </c>
+      <c r="W85">
+        <v>0.063665</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>2.320053553022813</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.100720214020271</v>
+      </c>
+      <c r="C86">
+        <v>-1.965658037905833</v>
+      </c>
+      <c r="D86">
+        <v>47.86434196209417</v>
+      </c>
+      <c r="E86">
+        <v>35</v>
+      </c>
+      <c r="F86">
+        <v>54.6</v>
+      </c>
+      <c r="G86">
+        <v>4.77</v>
+      </c>
+      <c r="H86">
+        <v>45.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>12.625</v>
+      </c>
+      <c r="K86">
+        <v>3.25</v>
+      </c>
+      <c r="L86">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M86">
+        <v>4.08954</v>
+      </c>
+      <c r="N86">
+        <v>5.285459999999999</v>
+      </c>
+      <c r="O86">
+        <v>0.7928189999999998</v>
+      </c>
+      <c r="P86">
+        <v>4.492640999999999</v>
+      </c>
+      <c r="Q86">
+        <v>7.742640999999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2952600876266934</v>
+      </c>
+      <c r="T86">
+        <v>4.393227152191666</v>
+      </c>
+      <c r="U86">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V86">
+        <v>0.15</v>
+      </c>
+      <c r="W86">
+        <v>0.063665</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>2.292433867867779</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1008984401975817</v>
+      </c>
+      <c r="C87">
+        <v>-2.753031515730015</v>
+      </c>
+      <c r="D87">
+        <v>47.72696848426999</v>
+      </c>
+      <c r="E87">
+        <v>35.65</v>
+      </c>
+      <c r="F87">
+        <v>55.25</v>
+      </c>
+      <c r="G87">
+        <v>4.77</v>
+      </c>
+      <c r="H87">
+        <v>45.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>12.625</v>
+      </c>
+      <c r="K87">
+        <v>3.25</v>
+      </c>
+      <c r="L87">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M87">
+        <v>4.138224999999999</v>
+      </c>
+      <c r="N87">
+        <v>5.236774999999999</v>
+      </c>
+      <c r="O87">
+        <v>0.7855162499999998</v>
+      </c>
+      <c r="P87">
+        <v>4.451258749999999</v>
+      </c>
+      <c r="Q87">
+        <v>7.701258749999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3118879346505446</v>
+      </c>
+      <c r="T87">
+        <v>4.678066441235367</v>
+      </c>
+      <c r="U87">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V87">
+        <v>0.15</v>
+      </c>
+      <c r="W87">
+        <v>0.063665</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>2.26546405765757</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1010766663748924</v>
+      </c>
+      <c r="C88">
+        <v>-3.539618710304232</v>
+      </c>
+      <c r="D88">
+        <v>47.59038128969576</v>
+      </c>
+      <c r="E88">
+        <v>36.3</v>
+      </c>
+      <c r="F88">
+        <v>55.9</v>
+      </c>
+      <c r="G88">
+        <v>4.77</v>
+      </c>
+      <c r="H88">
+        <v>45.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>12.625</v>
+      </c>
+      <c r="K88">
+        <v>3.25</v>
+      </c>
+      <c r="L88">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M88">
+        <v>4.186909999999999</v>
+      </c>
+      <c r="N88">
+        <v>5.188089999999999</v>
+      </c>
+      <c r="O88">
+        <v>0.7782134999999998</v>
+      </c>
+      <c r="P88">
+        <v>4.409876499999999</v>
+      </c>
+      <c r="Q88">
+        <v>7.659876499999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3308911883920888</v>
+      </c>
+      <c r="T88">
+        <v>5.00359705728531</v>
+      </c>
+      <c r="U88">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V88">
+        <v>0.15</v>
+      </c>
+      <c r="W88">
+        <v>0.063665</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>2.239121452335971</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1012548925522032</v>
+      </c>
+      <c r="C89">
+        <v>-4.325426353027083</v>
+      </c>
+      <c r="D89">
+        <v>47.45457364697292</v>
+      </c>
+      <c r="E89">
+        <v>36.95</v>
+      </c>
+      <c r="F89">
+        <v>56.55</v>
+      </c>
+      <c r="G89">
+        <v>4.77</v>
+      </c>
+      <c r="H89">
+        <v>45.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>12.625</v>
+      </c>
+      <c r="K89">
+        <v>3.25</v>
+      </c>
+      <c r="L89">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M89">
+        <v>4.235594999999999</v>
+      </c>
+      <c r="N89">
+        <v>5.139404999999999</v>
+      </c>
+      <c r="O89">
+        <v>0.7709107499999999</v>
+      </c>
+      <c r="P89">
+        <v>4.368494249999999</v>
+      </c>
+      <c r="Q89">
+        <v>7.618494249999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3528180196323322</v>
+      </c>
+      <c r="T89">
+        <v>5.379209306573706</v>
+      </c>
+      <c r="U89">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V89">
+        <v>0.15</v>
+      </c>
+      <c r="W89">
+        <v>0.063665</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>2.213384424148201</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1014331187295139</v>
+      </c>
+      <c r="C90">
+        <v>-5.110461098678769</v>
+      </c>
+      <c r="D90">
+        <v>47.31953890132124</v>
+      </c>
+      <c r="E90">
+        <v>37.6</v>
+      </c>
+      <c r="F90">
+        <v>57.2</v>
+      </c>
+      <c r="G90">
+        <v>4.77</v>
+      </c>
+      <c r="H90">
+        <v>45.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>12.625</v>
+      </c>
+      <c r="K90">
+        <v>3.25</v>
+      </c>
+      <c r="L90">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M90">
+        <v>4.28428</v>
+      </c>
+      <c r="N90">
+        <v>5.090719999999998</v>
+      </c>
+      <c r="O90">
+        <v>0.7636079999999997</v>
+      </c>
+      <c r="P90">
+        <v>4.327111999999999</v>
+      </c>
+      <c r="Q90">
+        <v>7.577111999999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3783993227459495</v>
+      </c>
+      <c r="T90">
+        <v>5.81742359741017</v>
+      </c>
+      <c r="U90">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V90">
+        <v>0.15</v>
+      </c>
+      <c r="W90">
+        <v>0.063665</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>2.188232328419244</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1016113449068247</v>
+      </c>
+      <c r="C91">
+        <v>-5.894729526508179</v>
+      </c>
+      <c r="D91">
+        <v>47.18527047349183</v>
+      </c>
+      <c r="E91">
+        <v>38.25</v>
+      </c>
+      <c r="F91">
+        <v>57.85</v>
+      </c>
+      <c r="G91">
+        <v>4.77</v>
+      </c>
+      <c r="H91">
+        <v>45.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>12.625</v>
+      </c>
+      <c r="K91">
+        <v>3.25</v>
+      </c>
+      <c r="L91">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M91">
+        <v>4.332965</v>
+      </c>
+      <c r="N91">
+        <v>5.042034999999998</v>
+      </c>
+      <c r="O91">
+        <v>0.7563052499999997</v>
+      </c>
+      <c r="P91">
+        <v>4.285729749999999</v>
+      </c>
+      <c r="Q91">
+        <v>7.535729749999999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4086317718802244</v>
+      </c>
+      <c r="T91">
+        <v>6.335313213853262</v>
+      </c>
+      <c r="U91">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V91">
+        <v>0.15</v>
+      </c>
+      <c r="W91">
+        <v>0.063665</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>2.163645448324646</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1017895710841354</v>
+      </c>
+      <c r="C92">
+        <v>-6.678238141301435</v>
+      </c>
+      <c r="D92">
+        <v>47.05176185869857</v>
+      </c>
+      <c r="E92">
+        <v>38.9</v>
+      </c>
+      <c r="F92">
+        <v>58.5</v>
+      </c>
+      <c r="G92">
+        <v>4.77</v>
+      </c>
+      <c r="H92">
+        <v>45.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>12.625</v>
+      </c>
+      <c r="K92">
+        <v>3.25</v>
+      </c>
+      <c r="L92">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M92">
+        <v>4.38165</v>
+      </c>
+      <c r="N92">
+        <v>4.993349999999999</v>
+      </c>
+      <c r="O92">
+        <v>0.7490024999999998</v>
+      </c>
+      <c r="P92">
+        <v>4.244347499999999</v>
+      </c>
+      <c r="Q92">
+        <v>7.494347499999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4449107108413544</v>
+      </c>
+      <c r="T92">
+        <v>6.956780753584974</v>
+      </c>
+      <c r="U92">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V92">
+        <v>0.15</v>
+      </c>
+      <c r="W92">
+        <v>0.063665</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>2.139604943343261</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1019677972614462</v>
+      </c>
+      <c r="C93">
+        <v>-7.460993374432356</v>
+      </c>
+      <c r="D93">
+        <v>46.91900662556765</v>
+      </c>
+      <c r="E93">
+        <v>39.55</v>
+      </c>
+      <c r="F93">
+        <v>59.15</v>
+      </c>
+      <c r="G93">
+        <v>4.77</v>
+      </c>
+      <c r="H93">
+        <v>45.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>12.625</v>
+      </c>
+      <c r="K93">
+        <v>3.25</v>
+      </c>
+      <c r="L93">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M93">
+        <v>4.430334999999999</v>
+      </c>
+      <c r="N93">
+        <v>4.944664999999999</v>
+      </c>
+      <c r="O93">
+        <v>0.7416997499999998</v>
+      </c>
+      <c r="P93">
+        <v>4.202965249999999</v>
+      </c>
+      <c r="Q93">
+        <v>7.452965249999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.489251636238291</v>
+      </c>
+      <c r="T93">
+        <v>7.716352191034843</v>
+      </c>
+      <c r="U93">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V93">
+        <v>0.15</v>
+      </c>
+      <c r="W93">
+        <v>0.063665</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>2.11609280110872</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1021460234387569</v>
+      </c>
+      <c r="C94">
+        <v>-8.243001584895303</v>
+      </c>
+      <c r="D94">
+        <v>46.7869984151047</v>
+      </c>
+      <c r="E94">
+        <v>40.2</v>
+      </c>
+      <c r="F94">
+        <v>59.8</v>
+      </c>
+      <c r="G94">
+        <v>4.77</v>
+      </c>
+      <c r="H94">
+        <v>45.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>12.625</v>
+      </c>
+      <c r="K94">
+        <v>3.25</v>
+      </c>
+      <c r="L94">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M94">
+        <v>4.47902</v>
+      </c>
+      <c r="N94">
+        <v>4.895979999999998</v>
+      </c>
+      <c r="O94">
+        <v>0.7343969999999996</v>
+      </c>
+      <c r="P94">
+        <v>4.161582999999998</v>
+      </c>
+      <c r="Q94">
+        <v>7.411582999999998</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.544677792984462</v>
+      </c>
+      <c r="T94">
+        <v>8.665816487847181</v>
+      </c>
+      <c r="U94">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V94">
+        <v>0.15</v>
+      </c>
+      <c r="W94">
+        <v>0.063665</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>2.093091792401016</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1023242496160677</v>
+      </c>
+      <c r="C95">
+        <v>-9.024269060320279</v>
+      </c>
+      <c r="D95">
+        <v>46.65573093967973</v>
+      </c>
+      <c r="E95">
+        <v>40.85</v>
+      </c>
+      <c r="F95">
+        <v>60.45</v>
+      </c>
+      <c r="G95">
+        <v>4.77</v>
+      </c>
+      <c r="H95">
+        <v>45.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>12.625</v>
+      </c>
+      <c r="K95">
+        <v>3.25</v>
+      </c>
+      <c r="L95">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M95">
+        <v>4.527705</v>
+      </c>
+      <c r="N95">
+        <v>4.847294999999998</v>
+      </c>
+      <c r="O95">
+        <v>0.7270942499999997</v>
+      </c>
+      <c r="P95">
+        <v>4.120200749999999</v>
+      </c>
+      <c r="Q95">
+        <v>7.370200749999999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6159399945152528</v>
+      </c>
+      <c r="T95">
+        <v>9.886556298034472</v>
+      </c>
+      <c r="U95">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V95">
+        <v>0.15</v>
+      </c>
+      <c r="W95">
+        <v>0.063665</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>2.070585429041865</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1025024757933784</v>
+      </c>
+      <c r="C96">
+        <v>-9.804802017971546</v>
+      </c>
+      <c r="D96">
+        <v>46.52519798202845</v>
+      </c>
+      <c r="E96">
+        <v>41.5</v>
+      </c>
+      <c r="F96">
+        <v>61.1</v>
+      </c>
+      <c r="G96">
+        <v>4.77</v>
+      </c>
+      <c r="H96">
+        <v>45.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>12.625</v>
+      </c>
+      <c r="K96">
+        <v>3.25</v>
+      </c>
+      <c r="L96">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M96">
+        <v>4.57639</v>
+      </c>
+      <c r="N96">
+        <v>4.798609999999998</v>
+      </c>
+      <c r="O96">
+        <v>0.7197914999999997</v>
+      </c>
+      <c r="P96">
+        <v>4.078818499999999</v>
+      </c>
+      <c r="Q96">
+        <v>7.328818499999999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7109562632229742</v>
+      </c>
+      <c r="T96">
+        <v>11.51420937828419</v>
+      </c>
+      <c r="U96">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V96">
+        <v>0.15</v>
+      </c>
+      <c r="W96">
+        <v>0.063665</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>2.04855792447759</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1026807019706892</v>
+      </c>
+      <c r="C97">
+        <v>-10.58460660572901</v>
+      </c>
+      <c r="D97">
+        <v>46.395393394271</v>
+      </c>
+      <c r="E97">
+        <v>42.15000000000001</v>
+      </c>
+      <c r="F97">
+        <v>61.75000000000001</v>
+      </c>
+      <c r="G97">
+        <v>4.77</v>
+      </c>
+      <c r="H97">
+        <v>45.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>12.625</v>
+      </c>
+      <c r="K97">
+        <v>3.25</v>
+      </c>
+      <c r="L97">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M97">
+        <v>4.625075</v>
+      </c>
+      <c r="N97">
+        <v>4.749924999999998</v>
+      </c>
+      <c r="O97">
+        <v>0.7124887499999998</v>
+      </c>
+      <c r="P97">
+        <v>4.037436249999999</v>
+      </c>
+      <c r="Q97">
+        <v>7.287436249999999</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8439790394137845</v>
+      </c>
+      <c r="T97">
+        <v>13.79292369063381</v>
+      </c>
+      <c r="U97">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V97">
+        <v>0.15</v>
+      </c>
+      <c r="W97">
+        <v>0.063665</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>2.02699415685151</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1028589281479999</v>
+      </c>
+      <c r="C98">
+        <v>-11.36368890305351</v>
+      </c>
+      <c r="D98">
+        <v>46.2663110969465</v>
+      </c>
+      <c r="E98">
+        <v>42.8</v>
+      </c>
+      <c r="F98">
+        <v>62.4</v>
+      </c>
+      <c r="G98">
+        <v>4.77</v>
+      </c>
+      <c r="H98">
+        <v>45.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>12.625</v>
+      </c>
+      <c r="K98">
+        <v>3.25</v>
+      </c>
+      <c r="L98">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M98">
+        <v>4.67376</v>
+      </c>
+      <c r="N98">
+        <v>4.701239999999999</v>
+      </c>
+      <c r="O98">
+        <v>0.7051859999999998</v>
+      </c>
+      <c r="P98">
+        <v>3.996053999999999</v>
+      </c>
+      <c r="Q98">
+        <v>7.246053999999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.043513203699997</v>
+      </c>
+      <c r="T98">
+        <v>17.21099515915818</v>
+      </c>
+      <c r="U98">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V98">
+        <v>0.15</v>
+      </c>
+      <c r="W98">
+        <v>0.063665</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>2.005879634384307</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1164765043253107</v>
+      </c>
+      <c r="C99">
+        <v>-20.12470035082964</v>
+      </c>
+      <c r="D99">
+        <v>38.15529964917036</v>
+      </c>
+      <c r="E99">
+        <v>43.45</v>
+      </c>
+      <c r="F99">
+        <v>63.05</v>
+      </c>
+      <c r="G99">
+        <v>4.77</v>
+      </c>
+      <c r="H99">
+        <v>45.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>12.625</v>
+      </c>
+      <c r="K99">
+        <v>3.25</v>
+      </c>
+      <c r="L99">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M99">
+        <v>5.75016</v>
+      </c>
+      <c r="N99">
+        <v>3.624839999999998</v>
+      </c>
+      <c r="O99">
+        <v>0.5437259999999997</v>
+      </c>
+      <c r="P99">
+        <v>3.081113999999999</v>
+      </c>
+      <c r="Q99">
+        <v>6.331113999999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.376070144177021</v>
+      </c>
+      <c r="T99">
+        <v>22.90778094003219</v>
+      </c>
+      <c r="U99">
+        <v>0.0912</v>
+      </c>
+      <c r="V99">
+        <v>0.15</v>
+      </c>
+      <c r="W99">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>1.630389415251054</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1167932805026214</v>
+      </c>
+      <c r="C100">
+        <v>-20.92967126485093</v>
+      </c>
+      <c r="D100">
+        <v>38.00032873514907</v>
+      </c>
+      <c r="E100">
+        <v>44.09999999999999</v>
+      </c>
+      <c r="F100">
+        <v>63.7</v>
+      </c>
+      <c r="G100">
+        <v>4.77</v>
+      </c>
+      <c r="H100">
+        <v>45.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>12.625</v>
+      </c>
+      <c r="K100">
+        <v>3.25</v>
+      </c>
+      <c r="L100">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M100">
+        <v>5.809439999999999</v>
+      </c>
+      <c r="N100">
+        <v>3.565559999999999</v>
+      </c>
+      <c r="O100">
+        <v>0.5348339999999998</v>
+      </c>
+      <c r="P100">
+        <v>3.030725999999999</v>
+      </c>
+      <c r="Q100">
+        <v>6.280725999999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.041184025131069</v>
+      </c>
+      <c r="T100">
+        <v>34.30135250178021</v>
+      </c>
+      <c r="U100">
+        <v>0.0912</v>
+      </c>
+      <c r="V100">
+        <v>0.15</v>
+      </c>
+      <c r="W100">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>1.613752788564819</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1171100566799322</v>
+      </c>
+      <c r="C101">
+        <v>-21.73338841669097</v>
+      </c>
+      <c r="D101">
+        <v>37.84661158330902</v>
+      </c>
+      <c r="E101">
+        <v>44.74999999999999</v>
+      </c>
+      <c r="F101">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="G101">
+        <v>4.77</v>
+      </c>
+      <c r="H101">
+        <v>45.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>12.625</v>
+      </c>
+      <c r="K101">
+        <v>3.25</v>
+      </c>
+      <c r="L101">
+        <v>9.374999999999998</v>
+      </c>
+      <c r="M101">
+        <v>5.86872</v>
+      </c>
+      <c r="N101">
+        <v>3.506279999999999</v>
+      </c>
+      <c r="O101">
+        <v>0.5259419999999998</v>
+      </c>
+      <c r="P101">
+        <v>2.980337999999999</v>
+      </c>
+      <c r="Q101">
+        <v>6.230337999999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.036525667993212</v>
+      </c>
+      <c r="T101">
+        <v>68.48206718702426</v>
+      </c>
+      <c r="U101">
+        <v>0.0912</v>
+      </c>
+      <c r="V101">
+        <v>0.15</v>
+      </c>
+      <c r="W101">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>1.597452255346992</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/lithuania/lithuania_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_environmental_waste_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08971136714200728</v>
+        <v>0.08961505009129428</v>
       </c>
       <c r="C2">
-        <v>66.5946541812863</v>
+        <v>65.98563854497552</v>
       </c>
       <c r="D2">
-        <v>59.2346541812863</v>
+        <v>59.28463854497552</v>
       </c>
       <c r="E2">
-        <v>-23.1</v>
+        <v>-22.441</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.659</v>
       </c>
       <c r="G2">
         <v>7.36</v>
@@ -1451,28 +1451,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0331477</v>
       </c>
       <c r="N2">
-        <v>9.220000000000001</v>
+        <v>9.1868523</v>
       </c>
       <c r="O2">
-        <v>1.383</v>
+        <v>1.378027845</v>
       </c>
       <c r="P2">
-        <v>7.837000000000001</v>
+        <v>7.808824455</v>
       </c>
       <c r="Q2">
-        <v>8.577000000000002</v>
+        <v>8.548824455</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08971136714200728</v>
+        <v>0.09008838393060029</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410372</v>
+        <v>0.8111573051269449</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>278.1490118469758</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08961505009129428</v>
+        <v>0.08951873304058126</v>
       </c>
       <c r="C3">
-        <v>65.98563854497552</v>
+        <v>65.37670733717036</v>
       </c>
       <c r="D3">
-        <v>59.28463854497552</v>
+        <v>59.33470733717036</v>
       </c>
       <c r="E3">
-        <v>-22.441</v>
+        <v>-21.782</v>
       </c>
       <c r="F3">
-        <v>0.659</v>
+        <v>1.318</v>
       </c>
       <c r="G3">
         <v>7.36</v>
@@ -1533,28 +1533,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0331477</v>
+        <v>0.0662954</v>
       </c>
       <c r="N3">
-        <v>9.1868523</v>
+        <v>9.153704600000001</v>
       </c>
       <c r="O3">
-        <v>1.378027845</v>
+        <v>1.37305569</v>
       </c>
       <c r="P3">
-        <v>7.808824455</v>
+        <v>7.780648910000001</v>
       </c>
       <c r="Q3">
-        <v>8.548824455</v>
+        <v>8.520648910000002</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09008838393060029</v>
+        <v>0.09047309493936864</v>
       </c>
       <c r="T3">
-        <v>0.8111573051269449</v>
+        <v>0.8182034223574634</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>278.1490118469758</v>
+        <v>139.0745059234879</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08951873304058126</v>
+        <v>0.08942241598986825</v>
       </c>
       <c r="C4">
-        <v>65.37670733717036</v>
+        <v>64.76786077196367</v>
       </c>
       <c r="D4">
-        <v>59.33470733717036</v>
+        <v>59.38486077196367</v>
       </c>
       <c r="E4">
-        <v>-21.782</v>
+        <v>-21.123</v>
       </c>
       <c r="F4">
-        <v>1.318</v>
+        <v>1.977</v>
       </c>
       <c r="G4">
         <v>7.36</v>
@@ -1615,28 +1615,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M4">
-        <v>0.0662954</v>
+        <v>0.09944310000000001</v>
       </c>
       <c r="N4">
-        <v>9.153704600000001</v>
+        <v>9.1205569</v>
       </c>
       <c r="O4">
-        <v>1.37305569</v>
+        <v>1.368083535</v>
       </c>
       <c r="P4">
-        <v>7.780648910000001</v>
+        <v>7.752473365</v>
       </c>
       <c r="Q4">
-        <v>8.520648910000002</v>
+        <v>8.492473365</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09047309493936864</v>
+        <v>0.09086573813388479</v>
       </c>
       <c r="T4">
-        <v>0.8182034223574634</v>
+        <v>0.8253948203556211</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>139.0745059234879</v>
+        <v>92.71633728232527</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08942241598986825</v>
+        <v>0.08932609893915523</v>
       </c>
       <c r="C5">
-        <v>64.76786077196367</v>
+        <v>64.15909906417284</v>
       </c>
       <c r="D5">
-        <v>59.38486077196367</v>
+        <v>59.43509906417283</v>
       </c>
       <c r="E5">
-        <v>-21.123</v>
+        <v>-20.464</v>
       </c>
       <c r="F5">
-        <v>1.977</v>
+        <v>2.636</v>
       </c>
       <c r="G5">
         <v>7.36</v>
@@ -1697,28 +1697,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M5">
-        <v>0.09944310000000001</v>
+        <v>0.1325908</v>
       </c>
       <c r="N5">
-        <v>9.1205569</v>
+        <v>9.0874092</v>
       </c>
       <c r="O5">
-        <v>1.368083535</v>
+        <v>1.36311138</v>
       </c>
       <c r="P5">
-        <v>7.752473365</v>
+        <v>7.72429782</v>
       </c>
       <c r="Q5">
-        <v>8.492473365</v>
+        <v>8.464297820000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09086573813388479</v>
+        <v>0.09126656139495337</v>
       </c>
       <c r="T5">
-        <v>0.8253948203556211</v>
+        <v>0.8327360391454072</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>92.71633728232527</v>
+        <v>69.53725296174395</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08932609893915523</v>
+        <v>0.08922978188844223</v>
       </c>
       <c r="C6">
-        <v>64.15909906417284</v>
+        <v>63.5504224293427</v>
       </c>
       <c r="D6">
-        <v>59.43509906417283</v>
+        <v>59.4854224293427</v>
       </c>
       <c r="E6">
-        <v>-20.464</v>
+        <v>-19.805</v>
       </c>
       <c r="F6">
-        <v>2.636</v>
+        <v>3.295</v>
       </c>
       <c r="G6">
         <v>7.36</v>
@@ -1779,28 +1779,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M6">
-        <v>0.1325908</v>
+        <v>0.1657385</v>
       </c>
       <c r="N6">
-        <v>9.0874092</v>
+        <v>9.054261500000001</v>
       </c>
       <c r="O6">
-        <v>1.36311138</v>
+        <v>1.358139225</v>
       </c>
       <c r="P6">
-        <v>7.72429782</v>
+        <v>7.696122275</v>
       </c>
       <c r="Q6">
-        <v>8.464297820000001</v>
+        <v>8.436122275000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09126656139495337</v>
+        <v>0.09167582304046551</v>
       </c>
       <c r="T6">
-        <v>0.8327360391454072</v>
+        <v>0.8402318099097151</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.53725296174395</v>
+        <v>55.62980236939516</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08922978188844223</v>
+        <v>0.08913346483772923</v>
       </c>
       <c r="C7">
-        <v>63.5504224293427</v>
+        <v>62.94183108374883</v>
       </c>
       <c r="D7">
-        <v>59.4854224293427</v>
+        <v>59.53583108374882</v>
       </c>
       <c r="E7">
-        <v>-19.805</v>
+        <v>-19.146</v>
       </c>
       <c r="F7">
-        <v>3.295</v>
+        <v>3.954000000000001</v>
       </c>
       <c r="G7">
         <v>7.36</v>
@@ -1861,28 +1861,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M7">
-        <v>0.1657385</v>
+        <v>0.1988862</v>
       </c>
       <c r="N7">
-        <v>9.054261500000001</v>
+        <v>9.0211138</v>
       </c>
       <c r="O7">
-        <v>1.358139225</v>
+        <v>1.35316707</v>
       </c>
       <c r="P7">
-        <v>7.696122275</v>
+        <v>7.667946730000001</v>
       </c>
       <c r="Q7">
-        <v>8.436122275000001</v>
+        <v>8.407946730000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09167582304046551</v>
+        <v>0.09209379238056301</v>
       </c>
       <c r="T7">
-        <v>0.8402318099097151</v>
+        <v>0.84788706515837</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.62980236939516</v>
+        <v>46.35816864116264</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08913346483772921</v>
+        <v>0.08903714778701623</v>
       </c>
       <c r="C8">
-        <v>62.94183108374883</v>
+        <v>62.33332524440043</v>
       </c>
       <c r="D8">
-        <v>59.53583108374882</v>
+        <v>59.58632524440042</v>
       </c>
       <c r="E8">
-        <v>-19.146</v>
+        <v>-18.487</v>
       </c>
       <c r="F8">
-        <v>3.954</v>
+        <v>4.613</v>
       </c>
       <c r="G8">
         <v>7.36</v>
@@ -1943,28 +1943,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M8">
-        <v>0.1988862</v>
+        <v>0.2320339</v>
       </c>
       <c r="N8">
-        <v>9.0211138</v>
+        <v>8.987966100000001</v>
       </c>
       <c r="O8">
-        <v>1.35316707</v>
+        <v>1.348194915</v>
       </c>
       <c r="P8">
-        <v>7.667946730000001</v>
+        <v>7.639771185000001</v>
       </c>
       <c r="Q8">
-        <v>8.407946730000001</v>
+        <v>8.379771185000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09209379238056301</v>
+        <v>0.09252075030861959</v>
       </c>
       <c r="T8">
-        <v>0.84788706515837</v>
+        <v>0.8557069495521573</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.35816864116264</v>
+        <v>39.73557312099656</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08903714778701621</v>
+        <v>0.08894083073630321</v>
       </c>
       <c r="C9">
-        <v>62.33332524440044</v>
+        <v>61.7249051290436</v>
       </c>
       <c r="D9">
-        <v>59.58632524440043</v>
+        <v>59.63690512904359</v>
       </c>
       <c r="E9">
-        <v>-18.487</v>
+        <v>-17.828</v>
       </c>
       <c r="F9">
-        <v>4.613</v>
+        <v>5.272</v>
       </c>
       <c r="G9">
         <v>7.36</v>
@@ -2025,28 +2025,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M9">
-        <v>0.2320339</v>
+        <v>0.2651816</v>
       </c>
       <c r="N9">
-        <v>8.987966100000001</v>
+        <v>8.954818400000001</v>
       </c>
       <c r="O9">
-        <v>1.348194915</v>
+        <v>1.34322276</v>
       </c>
       <c r="P9">
-        <v>7.639771185000001</v>
+        <v>7.611595640000001</v>
       </c>
       <c r="Q9">
-        <v>8.379771185000001</v>
+        <v>8.351595640000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09252075030861959</v>
+        <v>0.09295698993076434</v>
       </c>
       <c r="T9">
-        <v>0.8557069495521573</v>
+        <v>0.863696831432766</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.73557312099655</v>
+        <v>34.76862648087197</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08894083073630321</v>
+        <v>0.0888445136855902</v>
       </c>
       <c r="C10">
-        <v>61.7249051290436</v>
+        <v>61.11657095616434</v>
       </c>
       <c r="D10">
-        <v>59.63690512904359</v>
+        <v>59.68757095616433</v>
       </c>
       <c r="E10">
-        <v>-17.828</v>
+        <v>-17.169</v>
       </c>
       <c r="F10">
-        <v>5.272</v>
+        <v>5.931</v>
       </c>
       <c r="G10">
         <v>7.36</v>
@@ -2107,28 +2107,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M10">
-        <v>0.2651816</v>
+        <v>0.2983293</v>
       </c>
       <c r="N10">
-        <v>8.954818400000001</v>
+        <v>8.9216707</v>
       </c>
       <c r="O10">
-        <v>1.34322276</v>
+        <v>1.338250605</v>
       </c>
       <c r="P10">
-        <v>7.611595640000001</v>
+        <v>7.583420095</v>
       </c>
       <c r="Q10">
-        <v>8.351595640000001</v>
+        <v>8.323420094999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09295698993076434</v>
+        <v>0.09340281723691229</v>
       </c>
       <c r="T10">
-        <v>0.863696831432766</v>
+        <v>0.8718623151129484</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.76862648087197</v>
+        <v>30.90544576077509</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0888445136855902</v>
+        <v>0.08874819663487719</v>
       </c>
       <c r="C11">
-        <v>61.11657095616434</v>
+        <v>60.50832294499179</v>
       </c>
       <c r="D11">
-        <v>59.68757095616433</v>
+        <v>59.73832294499179</v>
       </c>
       <c r="E11">
-        <v>-17.169</v>
+        <v>-16.51</v>
       </c>
       <c r="F11">
-        <v>5.931</v>
+        <v>6.59</v>
       </c>
       <c r="G11">
         <v>7.36</v>
@@ -2189,28 +2189,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M11">
-        <v>0.2983293</v>
+        <v>0.331477</v>
       </c>
       <c r="N11">
-        <v>8.9216707</v>
+        <v>8.888523000000001</v>
       </c>
       <c r="O11">
-        <v>1.338250605</v>
+        <v>1.33327845</v>
       </c>
       <c r="P11">
-        <v>7.583420095</v>
+        <v>7.555244550000001</v>
       </c>
       <c r="Q11">
-        <v>8.323420094999999</v>
+        <v>8.295244550000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09340281723691229</v>
+        <v>0.09385855181653022</v>
       </c>
       <c r="T11">
-        <v>0.8718623151129484</v>
+        <v>0.8802092539860241</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.90544576077509</v>
+        <v>27.81490118469759</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08874819663487719</v>
+        <v>0.08865187958416416</v>
       </c>
       <c r="C12">
-        <v>60.50832294499179</v>
+        <v>59.90016131550141</v>
       </c>
       <c r="D12">
-        <v>59.73832294499179</v>
+        <v>59.78916131550141</v>
       </c>
       <c r="E12">
-        <v>-16.51</v>
+        <v>-15.851</v>
       </c>
       <c r="F12">
-        <v>6.590000000000001</v>
+        <v>7.249000000000001</v>
       </c>
       <c r="G12">
         <v>7.36</v>
@@ -2271,28 +2271,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M12">
-        <v>0.331477</v>
+        <v>0.3646247</v>
       </c>
       <c r="N12">
-        <v>8.888523000000001</v>
+        <v>8.8553753</v>
       </c>
       <c r="O12">
-        <v>1.33327845</v>
+        <v>1.328306295</v>
       </c>
       <c r="P12">
-        <v>7.555244550000001</v>
+        <v>7.527069005</v>
       </c>
       <c r="Q12">
-        <v>8.295244550000001</v>
+        <v>8.267069005</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09385855181653022</v>
+        <v>0.09432452762265636</v>
       </c>
       <c r="T12">
-        <v>0.8802092539860241</v>
+        <v>0.8887437645191686</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.81490118469758</v>
+        <v>25.28627380427053</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08865187958416416</v>
+        <v>0.08855556253345116</v>
       </c>
       <c r="C13">
-        <v>59.90016131550141</v>
+        <v>59.29208628841802</v>
       </c>
       <c r="D13">
-        <v>59.78916131550141</v>
+        <v>59.84008628841801</v>
       </c>
       <c r="E13">
-        <v>-15.851</v>
+        <v>-15.192</v>
       </c>
       <c r="F13">
-        <v>7.249000000000001</v>
+        <v>7.908</v>
       </c>
       <c r="G13">
         <v>7.36</v>
@@ -2353,28 +2353,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M13">
-        <v>0.3646247</v>
+        <v>0.3977724</v>
       </c>
       <c r="N13">
-        <v>8.8553753</v>
+        <v>8.822227600000002</v>
       </c>
       <c r="O13">
-        <v>1.328306295</v>
+        <v>1.32333414</v>
       </c>
       <c r="P13">
-        <v>7.527069005</v>
+        <v>7.498893460000001</v>
       </c>
       <c r="Q13">
-        <v>8.267069005</v>
+        <v>8.238893460000002</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09432452762265636</v>
+        <v>0.09480109378801269</v>
       </c>
       <c r="T13">
-        <v>0.8887437645191686</v>
+        <v>0.8974722412007938</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.28627380427053</v>
+        <v>23.17908432058132</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08855556253345116</v>
+        <v>0.08845924548273815</v>
       </c>
       <c r="C14">
-        <v>59.29208628841802</v>
+        <v>58.68409808521914</v>
       </c>
       <c r="D14">
-        <v>59.84008628841801</v>
+        <v>59.89109808521914</v>
       </c>
       <c r="E14">
-        <v>-15.192</v>
+        <v>-14.533</v>
       </c>
       <c r="F14">
-        <v>7.908</v>
+        <v>8.567</v>
       </c>
       <c r="G14">
         <v>7.36</v>
@@ -2435,28 +2435,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M14">
-        <v>0.3977724</v>
+        <v>0.4309201</v>
       </c>
       <c r="N14">
-        <v>8.822227600000002</v>
+        <v>8.789079900000001</v>
       </c>
       <c r="O14">
-        <v>1.32333414</v>
+        <v>1.318361985</v>
       </c>
       <c r="P14">
-        <v>7.498893460000001</v>
+        <v>7.470717915000001</v>
       </c>
       <c r="Q14">
-        <v>8.238893460000002</v>
+        <v>8.210717915</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09480109378801269</v>
+        <v>0.09528861549740017</v>
       </c>
       <c r="T14">
-        <v>0.8974722412007938</v>
+        <v>0.9064013725187781</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.17908432058132</v>
+        <v>21.39607783438276</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08845924548273815</v>
+        <v>0.08836292843202513</v>
       </c>
       <c r="C15">
-        <v>58.68409808521914</v>
+        <v>58.07619692813815</v>
       </c>
       <c r="D15">
-        <v>59.89109808521914</v>
+        <v>59.94219692813814</v>
       </c>
       <c r="E15">
-        <v>-14.533</v>
+        <v>-13.874</v>
       </c>
       <c r="F15">
-        <v>8.567</v>
+        <v>9.226000000000001</v>
       </c>
       <c r="G15">
         <v>7.36</v>
@@ -2517,28 +2517,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M15">
-        <v>0.4309201</v>
+        <v>0.4640678</v>
       </c>
       <c r="N15">
-        <v>8.789079900000001</v>
+        <v>8.7559322</v>
       </c>
       <c r="O15">
-        <v>1.318361985</v>
+        <v>1.31338983</v>
       </c>
       <c r="P15">
-        <v>7.470717915000001</v>
+        <v>7.44254237</v>
       </c>
       <c r="Q15">
-        <v>8.210717915</v>
+        <v>8.18254237</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09528861549740017</v>
+        <v>0.09578747492095946</v>
       </c>
       <c r="T15">
-        <v>0.9064013725187781</v>
+        <v>0.9155381580534596</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.39607783438276</v>
+        <v>19.86778656049827</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08836292843202513</v>
+        <v>0.08826661138131212</v>
       </c>
       <c r="C16">
-        <v>58.07619692813815</v>
+        <v>57.46838304016745</v>
       </c>
       <c r="D16">
-        <v>59.94219692813814</v>
+        <v>59.99338304016746</v>
       </c>
       <c r="E16">
-        <v>-13.874</v>
+        <v>-13.215</v>
       </c>
       <c r="F16">
-        <v>9.226000000000001</v>
+        <v>9.885000000000002</v>
       </c>
       <c r="G16">
         <v>7.36</v>
@@ -2599,28 +2599,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M16">
-        <v>0.4640678</v>
+        <v>0.4972155</v>
       </c>
       <c r="N16">
-        <v>8.7559322</v>
+        <v>8.722784500000001</v>
       </c>
       <c r="O16">
-        <v>1.31338983</v>
+        <v>1.308417675</v>
       </c>
       <c r="P16">
-        <v>7.44254237</v>
+        <v>7.414366825000001</v>
       </c>
       <c r="Q16">
-        <v>8.18254237</v>
+        <v>8.154366825</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09578747492095946</v>
+        <v>0.09629807221330838</v>
       </c>
       <c r="T16">
-        <v>0.9155381580534596</v>
+        <v>0.9248899267771926</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.86778656049827</v>
+        <v>18.54326745646506</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08826661138131212</v>
+        <v>0.0881702943305991</v>
       </c>
       <c r="C17">
-        <v>57.46838304016746</v>
+        <v>56.86065664506188</v>
       </c>
       <c r="D17">
-        <v>59.99338304016746</v>
+        <v>60.04465664506187</v>
       </c>
       <c r="E17">
-        <v>-13.215</v>
+        <v>-12.556</v>
       </c>
       <c r="F17">
-        <v>9.885</v>
+        <v>10.544</v>
       </c>
       <c r="G17">
         <v>7.36</v>
@@ -2681,28 +2681,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M17">
-        <v>0.4972155</v>
+        <v>0.5303632</v>
       </c>
       <c r="N17">
-        <v>8.722784500000001</v>
+        <v>8.689636800000001</v>
       </c>
       <c r="O17">
-        <v>1.308417675</v>
+        <v>1.30344552</v>
       </c>
       <c r="P17">
-        <v>7.414366825000001</v>
+        <v>7.38619128</v>
       </c>
       <c r="Q17">
-        <v>8.154366825</v>
+        <v>8.12619128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09629807221330838</v>
+        <v>0.09682082658404656</v>
       </c>
       <c r="T17">
-        <v>0.9248899267771926</v>
+        <v>0.9344643566610147</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.54326745646506</v>
+        <v>17.38431324043599</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0881702943305991</v>
+        <v>0.08807397727988608</v>
       </c>
       <c r="C18">
-        <v>56.86065664506188</v>
+        <v>56.25301796734173</v>
       </c>
       <c r="D18">
-        <v>60.04465664506187</v>
+        <v>60.09601796734173</v>
       </c>
       <c r="E18">
-        <v>-12.556</v>
+        <v>-11.897</v>
       </c>
       <c r="F18">
-        <v>10.544</v>
+        <v>11.203</v>
       </c>
       <c r="G18">
         <v>7.36</v>
@@ -2763,28 +2763,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M18">
-        <v>0.5303632</v>
+        <v>0.5635109</v>
       </c>
       <c r="N18">
-        <v>8.689636800000001</v>
+        <v>8.6564891</v>
       </c>
       <c r="O18">
-        <v>1.30344552</v>
+        <v>1.298473365</v>
       </c>
       <c r="P18">
-        <v>7.38619128</v>
+        <v>7.358015735</v>
       </c>
       <c r="Q18">
-        <v>8.12619128</v>
+        <v>8.098015735000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09682082658404656</v>
+        <v>0.0973561774456459</v>
       </c>
       <c r="T18">
-        <v>0.9344643566610147</v>
+        <v>0.9442694956986635</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.38431324043599</v>
+        <v>16.36170657923387</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08807397727988608</v>
+        <v>0.0879776602291731</v>
       </c>
       <c r="C19">
-        <v>56.25301796734173</v>
+        <v>55.64546723229622</v>
       </c>
       <c r="D19">
-        <v>60.09601796734173</v>
+        <v>60.14746723229622</v>
       </c>
       <c r="E19">
-        <v>-11.897</v>
+        <v>-11.238</v>
       </c>
       <c r="F19">
-        <v>11.203</v>
+        <v>11.862</v>
       </c>
       <c r="G19">
         <v>7.36</v>
@@ -2845,28 +2845,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M19">
-        <v>0.5635109</v>
+        <v>0.5966586</v>
       </c>
       <c r="N19">
-        <v>8.6564891</v>
+        <v>8.623341400000001</v>
       </c>
       <c r="O19">
-        <v>1.298473365</v>
+        <v>1.29350121</v>
       </c>
       <c r="P19">
-        <v>7.358015735</v>
+        <v>7.329840190000001</v>
       </c>
       <c r="Q19">
-        <v>8.098015735000001</v>
+        <v>8.069840190000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0973561774456459</v>
+        <v>0.09790458564533304</v>
       </c>
       <c r="T19">
-        <v>0.9442694956986635</v>
+        <v>0.954313784468938</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.36170657923387</v>
+        <v>15.45272288038755</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08797766022917311</v>
+        <v>0.08788134317846008</v>
       </c>
       <c r="C20">
-        <v>55.64546723229622</v>
+        <v>55.03800466598678</v>
       </c>
       <c r="D20">
-        <v>60.14746723229622</v>
+        <v>60.19900466598678</v>
       </c>
       <c r="E20">
-        <v>-11.238</v>
+        <v>-10.579</v>
       </c>
       <c r="F20">
-        <v>11.862</v>
+        <v>12.521</v>
       </c>
       <c r="G20">
         <v>7.36</v>
@@ -2927,28 +2927,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M20">
-        <v>0.5966585999999999</v>
+        <v>0.6298063</v>
       </c>
       <c r="N20">
-        <v>8.623341400000001</v>
+        <v>8.5901937</v>
       </c>
       <c r="O20">
-        <v>1.29350121</v>
+        <v>1.288529055</v>
       </c>
       <c r="P20">
-        <v>7.329840190000001</v>
+        <v>7.301664645000001</v>
       </c>
       <c r="Q20">
-        <v>8.069840190000001</v>
+        <v>8.041664645000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09790458564533304</v>
+        <v>0.09846653478822232</v>
       </c>
       <c r="T20">
-        <v>0.954313784468938</v>
+        <v>0.9646060803693426</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.45272288038755</v>
+        <v>14.63942167615662</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08788134317846008</v>
+        <v>0.08778502612774707</v>
       </c>
       <c r="C21">
-        <v>55.03800466598678</v>
+        <v>54.43063049525025</v>
       </c>
       <c r="D21">
-        <v>60.19900466598678</v>
+        <v>60.25063049525024</v>
       </c>
       <c r="E21">
-        <v>-10.579</v>
+        <v>-9.92</v>
       </c>
       <c r="F21">
-        <v>12.521</v>
+        <v>13.18</v>
       </c>
       <c r="G21">
         <v>7.36</v>
@@ -3009,28 +3009,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M21">
-        <v>0.6298063</v>
+        <v>0.662954</v>
       </c>
       <c r="N21">
-        <v>8.5901937</v>
+        <v>8.557046</v>
       </c>
       <c r="O21">
-        <v>1.288529055</v>
+        <v>1.2835569</v>
       </c>
       <c r="P21">
-        <v>7.301664645000001</v>
+        <v>7.2734891</v>
       </c>
       <c r="Q21">
-        <v>8.041664645000001</v>
+        <v>8.013489100000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09846653478822232</v>
+        <v>0.09904253265968382</v>
       </c>
       <c r="T21">
-        <v>0.9646060803693426</v>
+        <v>0.9751556836672575</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.63942167615662</v>
+        <v>13.90745059234879</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08778502612774707</v>
+        <v>0.08768870907703408</v>
       </c>
       <c r="C22">
-        <v>54.43063049525025</v>
+        <v>53.8233449477022</v>
       </c>
       <c r="D22">
-        <v>60.25063049525024</v>
+        <v>60.3023449477022</v>
       </c>
       <c r="E22">
-        <v>-9.92</v>
+        <v>-9.260999999999999</v>
       </c>
       <c r="F22">
-        <v>13.18</v>
+        <v>13.839</v>
       </c>
       <c r="G22">
         <v>7.36</v>
@@ -3091,28 +3091,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M22">
-        <v>0.662954</v>
+        <v>0.6961017</v>
       </c>
       <c r="N22">
-        <v>8.557046</v>
+        <v>8.523898300000001</v>
       </c>
       <c r="O22">
-        <v>1.2835569</v>
+        <v>1.278584745</v>
       </c>
       <c r="P22">
-        <v>7.2734891</v>
+        <v>7.245313555000001</v>
       </c>
       <c r="Q22">
-        <v>8.013489100000001</v>
+        <v>7.985313555000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09904253265968382</v>
+        <v>0.09963311275573933</v>
       </c>
       <c r="T22">
-        <v>0.9751556836672575</v>
+        <v>0.9859723655296766</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.90745059234879</v>
+        <v>13.24519104033218</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08768870907703406</v>
+        <v>0.08787289202632105</v>
       </c>
       <c r="C23">
-        <v>53.82334494770221</v>
+        <v>53.06553093281421</v>
       </c>
       <c r="D23">
-        <v>60.3023449477022</v>
+        <v>60.20353093281422</v>
       </c>
       <c r="E23">
-        <v>-9.261000000000001</v>
+        <v>-8.602</v>
       </c>
       <c r="F23">
-        <v>13.839</v>
+        <v>14.498</v>
       </c>
       <c r="G23">
         <v>7.36</v>
@@ -3173,45 +3173,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M23">
-        <v>0.6961016999999999</v>
+        <v>0.7509964</v>
       </c>
       <c r="N23">
-        <v>8.523898300000001</v>
+        <v>8.469003600000001</v>
       </c>
       <c r="O23">
-        <v>1.278584745</v>
+        <v>1.27035054</v>
       </c>
       <c r="P23">
-        <v>7.245313555000001</v>
+        <v>7.198653060000001</v>
       </c>
       <c r="Q23">
-        <v>7.985313555000001</v>
+        <v>7.938653060000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09963311275573931</v>
+        <v>0.1002388359311808</v>
       </c>
       <c r="T23">
-        <v>0.9859723655296765</v>
+        <v>0.9970663982090807</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.24519104033218</v>
+        <v>12.27702289917768</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08787289202632105</v>
+        <v>0.08778932497560804</v>
       </c>
       <c r="C24">
-        <v>53.06553093281421</v>
+        <v>52.45132442993901</v>
       </c>
       <c r="D24">
-        <v>60.20353093281422</v>
+        <v>60.24832442993902</v>
       </c>
       <c r="E24">
-        <v>-8.602</v>
+        <v>-7.943</v>
       </c>
       <c r="F24">
-        <v>14.498</v>
+        <v>15.157</v>
       </c>
       <c r="G24">
         <v>7.36</v>
@@ -3255,28 +3255,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M24">
-        <v>0.7509964</v>
+        <v>0.7851326000000001</v>
       </c>
       <c r="N24">
-        <v>8.469003600000001</v>
+        <v>8.4348674</v>
       </c>
       <c r="O24">
-        <v>1.27035054</v>
+        <v>1.26523011</v>
       </c>
       <c r="P24">
-        <v>7.198653060000001</v>
+        <v>7.16963729</v>
       </c>
       <c r="Q24">
-        <v>7.938653060000001</v>
+        <v>7.90963729</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1002388359311808</v>
+        <v>0.1008602921761143</v>
       </c>
       <c r="T24">
-        <v>0.9970663982090807</v>
+        <v>1.008448587581456</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.27702289917768</v>
+        <v>11.7432392948656</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08778932497560804</v>
+        <v>0.08770575792489503</v>
       </c>
       <c r="C25">
-        <v>52.45132442993901</v>
+        <v>51.83718463249915</v>
       </c>
       <c r="D25">
-        <v>60.24832442993902</v>
+        <v>60.29318463249915</v>
       </c>
       <c r="E25">
-        <v>-7.943</v>
+        <v>-7.283999999999999</v>
       </c>
       <c r="F25">
-        <v>15.157</v>
+        <v>15.816</v>
       </c>
       <c r="G25">
         <v>7.36</v>
@@ -3337,28 +3337,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M25">
-        <v>0.7851326000000001</v>
+        <v>0.8192688000000001</v>
       </c>
       <c r="N25">
-        <v>8.4348674</v>
+        <v>8.400731200000001</v>
       </c>
       <c r="O25">
-        <v>1.26523011</v>
+        <v>1.26010968</v>
       </c>
       <c r="P25">
-        <v>7.16963729</v>
+        <v>7.140621520000001</v>
       </c>
       <c r="Q25">
-        <v>7.90963729</v>
+        <v>7.880621520000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1008602921761143</v>
+        <v>0.1014981025327566</v>
       </c>
       <c r="T25">
-        <v>1.008448587581456</v>
+        <v>1.020130308253105</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.7432392948656</v>
+        <v>11.25393765757954</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08770575792489503</v>
+        <v>0.08762219087418201</v>
       </c>
       <c r="C26">
-        <v>51.83718463249915</v>
+        <v>51.22311168960993</v>
       </c>
       <c r="D26">
-        <v>60.29318463249915</v>
+        <v>60.33811168960992</v>
       </c>
       <c r="E26">
-        <v>-7.284000000000001</v>
+        <v>-6.625</v>
       </c>
       <c r="F26">
-        <v>15.816</v>
+        <v>16.475</v>
       </c>
       <c r="G26">
         <v>7.36</v>
@@ -3419,28 +3419,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M26">
-        <v>0.8192688</v>
+        <v>0.8534050000000001</v>
       </c>
       <c r="N26">
-        <v>8.400731200000001</v>
+        <v>8.366595</v>
       </c>
       <c r="O26">
-        <v>1.26010968</v>
+        <v>1.25498925</v>
       </c>
       <c r="P26">
-        <v>7.140621520000001</v>
+        <v>7.111605750000001</v>
       </c>
       <c r="Q26">
-        <v>7.880621520000001</v>
+        <v>7.851605750000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1014981025327566</v>
+        <v>0.102152921165576</v>
       </c>
       <c r="T26">
-        <v>1.020130308253105</v>
+        <v>1.032123541475997</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.25393765757954</v>
+        <v>10.80378015127636</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08762219087418201</v>
+        <v>0.08753862382346903</v>
       </c>
       <c r="C27">
-        <v>51.22311168960993</v>
+        <v>50.60910575083139</v>
       </c>
       <c r="D27">
-        <v>60.33811168960992</v>
+        <v>60.38310575083139</v>
       </c>
       <c r="E27">
-        <v>-6.625</v>
+        <v>-5.966000000000001</v>
       </c>
       <c r="F27">
-        <v>16.475</v>
+        <v>17.134</v>
       </c>
       <c r="G27">
         <v>7.36</v>
@@ -3501,28 +3501,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M27">
-        <v>0.8534050000000001</v>
+        <v>0.8875412</v>
       </c>
       <c r="N27">
-        <v>8.366595</v>
+        <v>8.332458800000001</v>
       </c>
       <c r="O27">
-        <v>1.25498925</v>
+        <v>1.24986882</v>
       </c>
       <c r="P27">
-        <v>7.111605750000001</v>
+        <v>7.082589980000002</v>
       </c>
       <c r="Q27">
-        <v>7.851605750000001</v>
+        <v>7.822589980000002</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.102152921165576</v>
+        <v>0.1028254375992824</v>
       </c>
       <c r="T27">
-        <v>1.032123541475997</v>
+        <v>1.044440916137347</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.80378015127636</v>
+        <v>10.38825014545804</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08753862382346903</v>
+        <v>0.087455056772756</v>
       </c>
       <c r="C28">
-        <v>50.60910575083139</v>
+        <v>49.99516696617012</v>
       </c>
       <c r="D28">
-        <v>60.38310575083139</v>
+        <v>60.42816696617012</v>
       </c>
       <c r="E28">
-        <v>-5.966000000000001</v>
+        <v>-5.306999999999999</v>
       </c>
       <c r="F28">
-        <v>17.134</v>
+        <v>17.793</v>
       </c>
       <c r="G28">
         <v>7.36</v>
@@ -3583,28 +3583,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M28">
-        <v>0.8875412</v>
+        <v>0.9216774000000001</v>
       </c>
       <c r="N28">
-        <v>8.332458800000001</v>
+        <v>8.298322600000001</v>
       </c>
       <c r="O28">
-        <v>1.24986882</v>
+        <v>1.24474839</v>
       </c>
       <c r="P28">
-        <v>7.082589980000002</v>
+        <v>7.053574210000001</v>
       </c>
       <c r="Q28">
-        <v>7.822589980000002</v>
+        <v>7.793574210000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1028254375992824</v>
+        <v>0.1035163791407616</v>
       </c>
       <c r="T28">
-        <v>1.044440916137347</v>
+        <v>1.057095753118185</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.38825014545804</v>
+        <v>10.0035001400707</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.087455056772756</v>
+        <v>0.08777608972204298</v>
       </c>
       <c r="C29">
-        <v>49.99516696617012</v>
+        <v>49.16342488774301</v>
       </c>
       <c r="D29">
-        <v>60.42816696617012</v>
+        <v>60.255424887743</v>
       </c>
       <c r="E29">
-        <v>-5.306999999999999</v>
+        <v>-4.648</v>
       </c>
       <c r="F29">
-        <v>17.793</v>
+        <v>18.452</v>
       </c>
       <c r="G29">
         <v>7.36</v>
@@ -3665,45 +3665,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M29">
-        <v>0.9216774000000001</v>
+        <v>0.9871820000000001</v>
       </c>
       <c r="N29">
-        <v>8.298322600000001</v>
+        <v>8.232818</v>
       </c>
       <c r="O29">
-        <v>1.24474839</v>
+        <v>1.2349227</v>
       </c>
       <c r="P29">
-        <v>7.053574210000001</v>
+        <v>6.9978953</v>
       </c>
       <c r="Q29">
-        <v>7.793574210000001</v>
+        <v>7.7378953</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1035163791407616</v>
+        <v>0.1042265135028375</v>
       </c>
       <c r="T29">
-        <v>1.057095753118185</v>
+        <v>1.070102113348491</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.15</v>
       </c>
       <c r="W29">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>10.0035001400707</v>
+        <v>9.339716485916476</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08777608972204298</v>
+        <v>0.08770697267132997</v>
       </c>
       <c r="C30">
-        <v>49.16342488774301</v>
+        <v>48.54153205764041</v>
       </c>
       <c r="D30">
-        <v>60.255424887743</v>
+        <v>60.29253205764041</v>
       </c>
       <c r="E30">
-        <v>-4.648</v>
+        <v>-3.988999999999997</v>
       </c>
       <c r="F30">
-        <v>18.452</v>
+        <v>19.111</v>
       </c>
       <c r="G30">
         <v>7.36</v>
@@ -3747,28 +3747,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M30">
-        <v>0.9871820000000001</v>
+        <v>1.0224385</v>
       </c>
       <c r="N30">
-        <v>8.232818</v>
+        <v>8.197561500000001</v>
       </c>
       <c r="O30">
-        <v>1.2349227</v>
+        <v>1.229634225</v>
       </c>
       <c r="P30">
-        <v>6.9978953</v>
+        <v>6.967927275000001</v>
       </c>
       <c r="Q30">
-        <v>7.7378953</v>
+        <v>7.707927275000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1042265135028375</v>
+        <v>0.1049566516497605</v>
       </c>
       <c r="T30">
-        <v>1.070102113348491</v>
+        <v>1.083474849923313</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.339716485916476</v>
+        <v>9.017657296746943</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08770697267132997</v>
+        <v>0.08763785562061696</v>
       </c>
       <c r="C31">
-        <v>48.54153205764041</v>
+        <v>47.91968495920587</v>
       </c>
       <c r="D31">
-        <v>60.29253205764041</v>
+        <v>60.32968495920586</v>
       </c>
       <c r="E31">
-        <v>-3.989000000000001</v>
+        <v>-3.330000000000002</v>
       </c>
       <c r="F31">
-        <v>19.111</v>
+        <v>19.77</v>
       </c>
       <c r="G31">
         <v>7.36</v>
@@ -3829,28 +3829,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M31">
-        <v>1.0224385</v>
+        <v>1.057695</v>
       </c>
       <c r="N31">
-        <v>8.197561500000001</v>
+        <v>8.162305</v>
       </c>
       <c r="O31">
-        <v>1.229634225</v>
+        <v>1.22434575</v>
       </c>
       <c r="P31">
-        <v>6.967927275000001</v>
+        <v>6.93795925</v>
       </c>
       <c r="Q31">
-        <v>7.707927275000001</v>
+        <v>7.677959250000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1049566516497605</v>
+        <v>0.1057076508865957</v>
       </c>
       <c r="T31">
-        <v>1.083474849923313</v>
+        <v>1.097229664685986</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.017657296746945</v>
+        <v>8.717068720188712</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08763785562061696</v>
+        <v>0.08756873856990394</v>
       </c>
       <c r="C32">
-        <v>47.91968495920587</v>
+        <v>47.29788367703249</v>
       </c>
       <c r="D32">
-        <v>60.32968495920586</v>
+        <v>60.36688367703249</v>
       </c>
       <c r="E32">
-        <v>-3.330000000000002</v>
+        <v>-2.670999999999999</v>
       </c>
       <c r="F32">
-        <v>19.77</v>
+        <v>20.429</v>
       </c>
       <c r="G32">
         <v>7.36</v>
@@ -3911,28 +3911,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M32">
-        <v>1.057695</v>
+        <v>1.0929515</v>
       </c>
       <c r="N32">
-        <v>8.162305</v>
+        <v>8.127048500000001</v>
       </c>
       <c r="O32">
-        <v>1.22434575</v>
+        <v>1.219057275</v>
       </c>
       <c r="P32">
-        <v>6.93795925</v>
+        <v>6.907991225000001</v>
       </c>
       <c r="Q32">
-        <v>7.677959250000001</v>
+        <v>7.647991225000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1057076508865957</v>
+        <v>0.1064804182172521</v>
       </c>
       <c r="T32">
-        <v>1.097229664685986</v>
+        <v>1.111383169731636</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.717068720188712</v>
+        <v>8.435872955021335</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08756873856990394</v>
+        <v>0.08749962151919093</v>
       </c>
       <c r="C33">
-        <v>47.29788367703249</v>
+        <v>46.67612829592225</v>
       </c>
       <c r="D33">
-        <v>60.36688367703249</v>
+        <v>60.40412829592224</v>
       </c>
       <c r="E33">
-        <v>-2.670999999999999</v>
+        <v>-2.012</v>
       </c>
       <c r="F33">
-        <v>20.429</v>
+        <v>21.088</v>
       </c>
       <c r="G33">
         <v>7.36</v>
@@ -3993,28 +3993,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M33">
-        <v>1.0929515</v>
+        <v>1.128208</v>
       </c>
       <c r="N33">
-        <v>8.127048500000001</v>
+        <v>8.091792</v>
       </c>
       <c r="O33">
-        <v>1.219057275</v>
+        <v>1.2137688</v>
       </c>
       <c r="P33">
-        <v>6.907991225000001</v>
+        <v>6.878023199999999</v>
       </c>
       <c r="Q33">
-        <v>7.647991225000001</v>
+        <v>7.6180232</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1064804182172521</v>
+        <v>0.1072759139988102</v>
       </c>
       <c r="T33">
-        <v>1.111383169731636</v>
+        <v>1.125952954337452</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.435872955021335</v>
+        <v>8.172251925176916</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08749962151919093</v>
+        <v>0.08743050446847792</v>
       </c>
       <c r="C34">
-        <v>46.67612829592225</v>
+        <v>46.05441890088642</v>
       </c>
       <c r="D34">
-        <v>60.40412829592224</v>
+        <v>60.44141890088642</v>
       </c>
       <c r="E34">
-        <v>-2.012</v>
+        <v>-1.352999999999998</v>
       </c>
       <c r="F34">
-        <v>21.088</v>
+        <v>21.747</v>
       </c>
       <c r="G34">
         <v>7.36</v>
@@ -4075,28 +4075,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M34">
-        <v>1.128208</v>
+        <v>1.1634645</v>
       </c>
       <c r="N34">
-        <v>8.091792</v>
+        <v>8.056535500000001</v>
       </c>
       <c r="O34">
-        <v>1.2137688</v>
+        <v>1.208480325</v>
       </c>
       <c r="P34">
-        <v>6.878023199999999</v>
+        <v>6.848055175000001</v>
       </c>
       <c r="Q34">
-        <v>7.6180232</v>
+        <v>7.588055175000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1072759139988102</v>
+        <v>0.1080951559231014</v>
       </c>
       <c r="T34">
-        <v>1.125952954337452</v>
+        <v>1.140957657886725</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.172251925176916</v>
+        <v>7.924607927444284</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08743050446847792</v>
+        <v>0.08736138741776492</v>
       </c>
       <c r="C35">
-        <v>46.05441890088642</v>
+        <v>45.43275557714641</v>
       </c>
       <c r="D35">
-        <v>60.44141890088642</v>
+        <v>60.47875557714642</v>
       </c>
       <c r="E35">
-        <v>-1.352999999999998</v>
+        <v>-0.6939999999999991</v>
       </c>
       <c r="F35">
-        <v>21.747</v>
+        <v>22.406</v>
       </c>
       <c r="G35">
         <v>7.36</v>
@@ -4157,28 +4157,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M35">
-        <v>1.1634645</v>
+        <v>1.198721</v>
       </c>
       <c r="N35">
-        <v>8.056535500000001</v>
+        <v>8.021279</v>
       </c>
       <c r="O35">
-        <v>1.208480325</v>
+        <v>1.20319185</v>
       </c>
       <c r="P35">
-        <v>6.848055175000001</v>
+        <v>6.81808715</v>
       </c>
       <c r="Q35">
-        <v>7.588055175000001</v>
+        <v>7.55808715</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1080951559231014</v>
+        <v>0.1089392233602499</v>
       </c>
       <c r="T35">
-        <v>1.140957657886725</v>
+        <v>1.15641704942234</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.924607927444284</v>
+        <v>7.691531223695922</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08736138741776492</v>
+        <v>0.08753027036705191</v>
       </c>
       <c r="C36">
-        <v>45.43275557714641</v>
+        <v>44.68260709724954</v>
       </c>
       <c r="D36">
-        <v>60.47875557714642</v>
+        <v>60.38760709724954</v>
       </c>
       <c r="E36">
-        <v>-0.6939999999999991</v>
+        <v>-0.03499999999999659</v>
       </c>
       <c r="F36">
-        <v>22.406</v>
+        <v>23.065</v>
       </c>
       <c r="G36">
         <v>7.36</v>
@@ -4239,45 +4239,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M36">
-        <v>1.198721</v>
+        <v>1.2524295</v>
       </c>
       <c r="N36">
-        <v>8.021279</v>
+        <v>7.967570500000001</v>
       </c>
       <c r="O36">
-        <v>1.20319185</v>
+        <v>1.195135575</v>
       </c>
       <c r="P36">
-        <v>6.81808715</v>
+        <v>6.772434925000001</v>
       </c>
       <c r="Q36">
-        <v>7.55808715</v>
+        <v>7.512434925000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1089392233602499</v>
+        <v>0.1098092621031568</v>
       </c>
       <c r="T36">
-        <v>1.15641704942234</v>
+        <v>1.172352114543666</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.691531223695922</v>
+        <v>7.361691815786836</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08753027036705191</v>
+        <v>0.08746795331633889</v>
       </c>
       <c r="C37">
-        <v>44.68260709724954</v>
+        <v>44.05720847442572</v>
       </c>
       <c r="D37">
-        <v>60.38760709724954</v>
+        <v>60.42120847442573</v>
       </c>
       <c r="E37">
-        <v>-0.03499999999999659</v>
+        <v>0.6240000000000023</v>
       </c>
       <c r="F37">
-        <v>23.065</v>
+        <v>23.724</v>
       </c>
       <c r="G37">
         <v>7.36</v>
@@ -4321,28 +4321,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M37">
-        <v>1.2524295</v>
+        <v>1.2882132</v>
       </c>
       <c r="N37">
-        <v>7.967570500000001</v>
+        <v>7.9317868</v>
       </c>
       <c r="O37">
-        <v>1.195135575</v>
+        <v>1.18976802</v>
       </c>
       <c r="P37">
-        <v>6.772434925000001</v>
+        <v>6.74201878</v>
       </c>
       <c r="Q37">
-        <v>7.512434925000001</v>
+        <v>7.482018780000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1098092621031568</v>
+        <v>0.1107064895567795</v>
       </c>
       <c r="T37">
-        <v>1.172352114543666</v>
+        <v>1.188785150450033</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.361691815786836</v>
+        <v>7.157200376459424</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0874679533163389</v>
+        <v>0.08740563626562589</v>
       </c>
       <c r="C38">
-        <v>44.05720847442571</v>
+        <v>43.43184726593868</v>
       </c>
       <c r="D38">
-        <v>60.42120847442571</v>
+        <v>60.45484726593868</v>
       </c>
       <c r="E38">
-        <v>0.6239999999999988</v>
+        <v>1.283000000000001</v>
       </c>
       <c r="F38">
-        <v>23.724</v>
+        <v>24.383</v>
       </c>
       <c r="G38">
         <v>7.36</v>
@@ -4403,28 +4403,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M38">
-        <v>1.2882132</v>
+        <v>1.3239969</v>
       </c>
       <c r="N38">
-        <v>7.931786800000001</v>
+        <v>7.896003100000001</v>
       </c>
       <c r="O38">
-        <v>1.18976802</v>
+        <v>1.184400465</v>
       </c>
       <c r="P38">
-        <v>6.742018780000001</v>
+        <v>6.711602635</v>
       </c>
       <c r="Q38">
-        <v>7.482018780000002</v>
+        <v>7.451602635</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1107064895567795</v>
+        <v>0.1116322004216284</v>
       </c>
       <c r="T38">
-        <v>1.188785150450033</v>
+        <v>1.205739870035968</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.157200376459426</v>
+        <v>6.963762528447007</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08740563626562589</v>
+        <v>0.08734331921491288</v>
       </c>
       <c r="C39">
-        <v>43.43184726593868</v>
+        <v>42.8065235343132</v>
       </c>
       <c r="D39">
-        <v>60.45484726593868</v>
+        <v>60.4885235343132</v>
       </c>
       <c r="E39">
-        <v>1.283000000000001</v>
+        <v>1.942</v>
       </c>
       <c r="F39">
-        <v>24.383</v>
+        <v>25.042</v>
       </c>
       <c r="G39">
         <v>7.36</v>
@@ -4485,28 +4485,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M39">
-        <v>1.3239969</v>
+        <v>1.3597806</v>
       </c>
       <c r="N39">
-        <v>7.896003100000001</v>
+        <v>7.8602194</v>
       </c>
       <c r="O39">
-        <v>1.184400465</v>
+        <v>1.17903291</v>
       </c>
       <c r="P39">
-        <v>6.711602635</v>
+        <v>6.68118649</v>
       </c>
       <c r="Q39">
-        <v>7.451602635</v>
+        <v>7.42118649</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1116322004216284</v>
+        <v>0.1125877729272788</v>
       </c>
       <c r="T39">
-        <v>1.205739870035968</v>
+        <v>1.223241516060158</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.963762528447007</v>
+        <v>6.780505619803665</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08734331921491288</v>
+        <v>0.08728100216419986</v>
       </c>
       <c r="C40">
-        <v>42.8065235343132</v>
+        <v>42.18123734221346</v>
       </c>
       <c r="D40">
-        <v>60.4885235343132</v>
+        <v>60.52223734221347</v>
       </c>
       <c r="E40">
-        <v>1.942</v>
+        <v>2.601000000000003</v>
       </c>
       <c r="F40">
-        <v>25.042</v>
+        <v>25.701</v>
       </c>
       <c r="G40">
         <v>7.36</v>
@@ -4567,28 +4567,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M40">
-        <v>1.3597806</v>
+        <v>1.3955643</v>
       </c>
       <c r="N40">
-        <v>7.8602194</v>
+        <v>7.8244357</v>
       </c>
       <c r="O40">
-        <v>1.17903291</v>
+        <v>1.173665355</v>
       </c>
       <c r="P40">
-        <v>6.68118649</v>
+        <v>6.650770345000001</v>
       </c>
       <c r="Q40">
-        <v>7.42118649</v>
+        <v>7.390770345000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1125877729272788</v>
+        <v>0.1135746756790162</v>
       </c>
       <c r="T40">
-        <v>1.223241516060158</v>
+        <v>1.241316986544158</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.780505619803665</v>
+        <v>6.606646501347161</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08728100216419986</v>
+        <v>0.08721868511348686</v>
       </c>
       <c r="C41">
-        <v>42.18123734221346</v>
+        <v>41.5559887524434</v>
       </c>
       <c r="D41">
-        <v>60.52223734221347</v>
+        <v>60.55598875244339</v>
       </c>
       <c r="E41">
-        <v>2.601000000000003</v>
+        <v>3.260000000000002</v>
       </c>
       <c r="F41">
-        <v>25.701</v>
+        <v>26.36</v>
       </c>
       <c r="G41">
         <v>7.36</v>
@@ -4649,28 +4649,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M41">
-        <v>1.3955643</v>
+        <v>1.431348</v>
       </c>
       <c r="N41">
-        <v>7.8244357</v>
+        <v>7.788652000000001</v>
       </c>
       <c r="O41">
-        <v>1.173665355</v>
+        <v>1.1682978</v>
       </c>
       <c r="P41">
-        <v>6.650770345000001</v>
+        <v>6.6203542</v>
       </c>
       <c r="Q41">
-        <v>7.390770345000001</v>
+        <v>7.360354200000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1135746756790162</v>
+        <v>0.1145944751891448</v>
       </c>
       <c r="T41">
-        <v>1.241316986544158</v>
+        <v>1.259994972710958</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.606646501347161</v>
+        <v>6.441480338813482</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08721868511348686</v>
+        <v>0.08715636806277384</v>
       </c>
       <c r="C42">
-        <v>41.5559887524434</v>
+        <v>40.93077782794715</v>
       </c>
       <c r="D42">
-        <v>60.55598875244339</v>
+        <v>60.58977782794715</v>
       </c>
       <c r="E42">
-        <v>3.260000000000002</v>
+        <v>3.919000000000004</v>
       </c>
       <c r="F42">
-        <v>26.36</v>
+        <v>27.01900000000001</v>
       </c>
       <c r="G42">
         <v>7.36</v>
@@ -4731,28 +4731,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M42">
-        <v>1.431348</v>
+        <v>1.4671317</v>
       </c>
       <c r="N42">
-        <v>7.788652000000001</v>
+        <v>7.7528683</v>
       </c>
       <c r="O42">
-        <v>1.1682978</v>
+        <v>1.162930245</v>
       </c>
       <c r="P42">
-        <v>6.6203542</v>
+        <v>6.589938055</v>
       </c>
       <c r="Q42">
-        <v>7.360354200000001</v>
+        <v>7.329938055</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1145944751891448</v>
+        <v>0.115648844174193</v>
       </c>
       <c r="T42">
-        <v>1.259994972710958</v>
+        <v>1.279306110951209</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.441480338813482</v>
+        <v>6.284371062257055</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08715636806277384</v>
+        <v>0.08709405101206083</v>
       </c>
       <c r="C43">
-        <v>40.93077782794715</v>
+        <v>40.30560463180939</v>
       </c>
       <c r="D43">
-        <v>60.58977782794715</v>
+        <v>60.62360463180939</v>
       </c>
       <c r="E43">
-        <v>3.919000000000004</v>
+        <v>4.578000000000003</v>
       </c>
       <c r="F43">
-        <v>27.01900000000001</v>
+        <v>27.678</v>
       </c>
       <c r="G43">
         <v>7.36</v>
@@ -4813,28 +4813,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M43">
-        <v>1.4671317</v>
+        <v>1.5029154</v>
       </c>
       <c r="N43">
-        <v>7.7528683</v>
+        <v>7.717084600000001</v>
       </c>
       <c r="O43">
-        <v>1.162930245</v>
+        <v>1.15756269</v>
       </c>
       <c r="P43">
-        <v>6.589938055</v>
+        <v>6.559521910000001</v>
       </c>
       <c r="Q43">
-        <v>7.329938055</v>
+        <v>7.299521910000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.115648844174193</v>
+        <v>0.1167395707104497</v>
       </c>
       <c r="T43">
-        <v>1.279306110951209</v>
+        <v>1.299283150510089</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.284371062257055</v>
+        <v>6.134743179822364</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08709405101206084</v>
+        <v>0.08739723396134781</v>
       </c>
       <c r="C44">
-        <v>40.3056046318094</v>
+        <v>39.48238570200422</v>
       </c>
       <c r="D44">
-        <v>60.62360463180939</v>
+        <v>60.45938570200423</v>
       </c>
       <c r="E44">
-        <v>4.577999999999999</v>
+        <v>5.237000000000002</v>
       </c>
       <c r="F44">
-        <v>27.678</v>
+        <v>28.337</v>
       </c>
       <c r="G44">
         <v>7.36</v>
@@ -4895,45 +4895,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M44">
-        <v>1.5029154</v>
+        <v>1.5670361</v>
       </c>
       <c r="N44">
-        <v>7.717084600000001</v>
+        <v>7.6529639</v>
       </c>
       <c r="O44">
-        <v>1.15756269</v>
+        <v>1.147944585</v>
       </c>
       <c r="P44">
-        <v>6.559521910000001</v>
+        <v>6.505019315</v>
       </c>
       <c r="Q44">
-        <v>7.299521910000001</v>
+        <v>7.245019315</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1167395707104497</v>
+        <v>0.1178685683532418</v>
       </c>
       <c r="T44">
-        <v>1.299283150510089</v>
+        <v>1.319961138825421</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.15</v>
       </c>
       <c r="W44">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.134743179822364</v>
+        <v>5.883718951975643</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08739723396134781</v>
+        <v>0.0873434169106348</v>
       </c>
       <c r="C45">
-        <v>39.48238570200422</v>
+        <v>38.85247070997152</v>
       </c>
       <c r="D45">
-        <v>60.45938570200423</v>
+        <v>60.48847070997152</v>
       </c>
       <c r="E45">
-        <v>5.237000000000002</v>
+        <v>5.896000000000001</v>
       </c>
       <c r="F45">
-        <v>28.337</v>
+        <v>28.996</v>
       </c>
       <c r="G45">
         <v>7.36</v>
@@ -4977,28 +4977,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M45">
-        <v>1.5670361</v>
+        <v>1.6034788</v>
       </c>
       <c r="N45">
-        <v>7.6529639</v>
+        <v>7.6165212</v>
       </c>
       <c r="O45">
-        <v>1.147944585</v>
+        <v>1.14247818</v>
       </c>
       <c r="P45">
-        <v>6.505019315</v>
+        <v>6.47404302</v>
       </c>
       <c r="Q45">
-        <v>7.245019315</v>
+        <v>7.21404302</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1178685683532418</v>
+        <v>0.1190378873404193</v>
       </c>
       <c r="T45">
-        <v>1.319961138825421</v>
+        <v>1.341377626723444</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.883718951975643</v>
+        <v>5.749998066703469</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0873434169106348</v>
+        <v>0.0872895998599218</v>
       </c>
       <c r="C46">
-        <v>38.85247070997152</v>
+        <v>38.22258371507532</v>
       </c>
       <c r="D46">
-        <v>60.48847070997152</v>
+        <v>60.51758371507531</v>
       </c>
       <c r="E46">
-        <v>5.896000000000001</v>
+        <v>6.555000000000003</v>
       </c>
       <c r="F46">
-        <v>28.996</v>
+        <v>29.655</v>
       </c>
       <c r="G46">
         <v>7.36</v>
@@ -5059,28 +5059,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M46">
-        <v>1.6034788</v>
+        <v>1.6399215</v>
       </c>
       <c r="N46">
-        <v>7.6165212</v>
+        <v>7.580078500000001</v>
       </c>
       <c r="O46">
-        <v>1.14247818</v>
+        <v>1.137011775</v>
       </c>
       <c r="P46">
-        <v>6.47404302</v>
+        <v>6.443066725</v>
       </c>
       <c r="Q46">
-        <v>7.21404302</v>
+        <v>7.183066725000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1190378873404193</v>
+        <v>0.1202497270180396</v>
       </c>
       <c r="T46">
-        <v>1.341377626723444</v>
+        <v>1.363572895999577</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.749998066703469</v>
+        <v>5.622220331887837</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0872895998599218</v>
+        <v>0.0872357828092088</v>
       </c>
       <c r="C47">
-        <v>38.22258371507532</v>
+        <v>37.59272475776</v>
       </c>
       <c r="D47">
-        <v>60.51758371507531</v>
+        <v>60.54672475776</v>
       </c>
       <c r="E47">
-        <v>6.555000000000003</v>
+        <v>7.214000000000002</v>
       </c>
       <c r="F47">
-        <v>29.655</v>
+        <v>30.314</v>
       </c>
       <c r="G47">
         <v>7.36</v>
@@ -5141,28 +5141,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M47">
-        <v>1.6399215</v>
+        <v>1.6763642</v>
       </c>
       <c r="N47">
-        <v>7.580078500000001</v>
+        <v>7.543635800000001</v>
       </c>
       <c r="O47">
-        <v>1.137011775</v>
+        <v>1.13154537</v>
       </c>
       <c r="P47">
-        <v>6.443066725</v>
+        <v>6.412090430000001</v>
       </c>
       <c r="Q47">
-        <v>7.183066725000001</v>
+        <v>7.152090430000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1202497270180396</v>
+        <v>0.1215064496466829</v>
       </c>
       <c r="T47">
-        <v>1.363572895999577</v>
+        <v>1.386590212285936</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.622220331887837</v>
+        <v>5.499998150759841</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0872357828092088</v>
+        <v>0.08718196575849577</v>
       </c>
       <c r="C48">
-        <v>37.59272475776</v>
+        <v>36.96289387854791</v>
       </c>
       <c r="D48">
-        <v>60.54672475776</v>
+        <v>60.57589387854792</v>
       </c>
       <c r="E48">
-        <v>7.214000000000002</v>
+        <v>7.873000000000005</v>
       </c>
       <c r="F48">
-        <v>30.314</v>
+        <v>30.97300000000001</v>
       </c>
       <c r="G48">
         <v>7.36</v>
@@ -5223,28 +5223,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M48">
-        <v>1.6763642</v>
+        <v>1.7128069</v>
       </c>
       <c r="N48">
-        <v>7.543635800000001</v>
+        <v>7.5071931</v>
       </c>
       <c r="O48">
-        <v>1.13154537</v>
+        <v>1.126078965</v>
       </c>
       <c r="P48">
-        <v>6.412090430000001</v>
+        <v>6.381114135000001</v>
       </c>
       <c r="Q48">
-        <v>7.152090430000001</v>
+        <v>7.121114135000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1215064496466829</v>
+        <v>0.1228105957707467</v>
       </c>
       <c r="T48">
-        <v>1.386590212285936</v>
+        <v>1.410476106545366</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.499998150759841</v>
+        <v>5.382976913509631</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08718196575849577</v>
+        <v>0.08712814870778277</v>
       </c>
       <c r="C49">
-        <v>36.96289387854791</v>
+        <v>36.3330911180395</v>
       </c>
       <c r="D49">
-        <v>60.57589387854792</v>
+        <v>60.60509111803951</v>
       </c>
       <c r="E49">
-        <v>7.873000000000005</v>
+        <v>8.532000000000004</v>
       </c>
       <c r="F49">
-        <v>30.97300000000001</v>
+        <v>31.63200000000001</v>
       </c>
       <c r="G49">
         <v>7.36</v>
@@ -5305,28 +5305,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M49">
-        <v>1.7128069</v>
+        <v>1.7492496</v>
       </c>
       <c r="N49">
-        <v>7.5071931</v>
+        <v>7.4707504</v>
       </c>
       <c r="O49">
-        <v>1.126078965</v>
+        <v>1.12061256</v>
       </c>
       <c r="P49">
-        <v>6.381114135000001</v>
+        <v>6.35013784</v>
       </c>
       <c r="Q49">
-        <v>7.121114135000001</v>
+        <v>7.090137840000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1228105957707467</v>
+        <v>0.1241649013611207</v>
       </c>
       <c r="T49">
-        <v>1.410476106545366</v>
+        <v>1.435280689045543</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.382976913509631</v>
+        <v>5.270831561144846</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08712814870778277</v>
+        <v>0.08707433165706974</v>
       </c>
       <c r="C50">
-        <v>36.3330911180395</v>
+        <v>35.7033165169136</v>
       </c>
       <c r="D50">
-        <v>60.60509111803951</v>
+        <v>60.6343165169136</v>
       </c>
       <c r="E50">
-        <v>8.532</v>
+        <v>9.191000000000003</v>
       </c>
       <c r="F50">
-        <v>31.632</v>
+        <v>32.291</v>
       </c>
       <c r="G50">
         <v>7.36</v>
@@ -5387,28 +5387,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M50">
-        <v>1.7492496</v>
+        <v>1.7856923</v>
       </c>
       <c r="N50">
-        <v>7.4707504</v>
+        <v>7.434307700000001</v>
       </c>
       <c r="O50">
-        <v>1.12061256</v>
+        <v>1.115146155</v>
       </c>
       <c r="P50">
-        <v>6.35013784</v>
+        <v>6.319161545</v>
       </c>
       <c r="Q50">
-        <v>7.090137840000001</v>
+        <v>7.059161545</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1241649013611207</v>
+        <v>0.1255723169746465</v>
       </c>
       <c r="T50">
-        <v>1.435280689045543</v>
+        <v>1.461058000271217</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.270831561144847</v>
+        <v>5.163263570101075</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08707433165706974</v>
+        <v>0.08702051460635674</v>
       </c>
       <c r="C51">
-        <v>35.7033165169136</v>
+        <v>35.07357011592742</v>
       </c>
       <c r="D51">
-        <v>60.6343165169136</v>
+        <v>60.66357011592742</v>
       </c>
       <c r="E51">
-        <v>9.191000000000003</v>
+        <v>9.850000000000001</v>
       </c>
       <c r="F51">
-        <v>32.291</v>
+        <v>32.95</v>
       </c>
       <c r="G51">
         <v>7.36</v>
@@ -5469,28 +5469,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M51">
-        <v>1.7856923</v>
+        <v>1.822135</v>
       </c>
       <c r="N51">
-        <v>7.434307700000001</v>
+        <v>7.397865</v>
       </c>
       <c r="O51">
-        <v>1.115146155</v>
+        <v>1.10967975</v>
       </c>
       <c r="P51">
-        <v>6.319161545</v>
+        <v>6.288185250000001</v>
       </c>
       <c r="Q51">
-        <v>7.059161545</v>
+        <v>7.028185250000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1255723169746465</v>
+        <v>0.1270360292127135</v>
       </c>
       <c r="T51">
-        <v>1.461058000271217</v>
+        <v>1.487866403945919</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.163263570101075</v>
+        <v>5.059998298699053</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08702051460635674</v>
+        <v>0.08696669755564372</v>
       </c>
       <c r="C52">
-        <v>35.07357011592742</v>
+        <v>34.44385195591696</v>
       </c>
       <c r="D52">
-        <v>60.66357011592742</v>
+        <v>60.69285195591696</v>
       </c>
       <c r="E52">
-        <v>9.850000000000001</v>
+        <v>10.509</v>
       </c>
       <c r="F52">
-        <v>32.95</v>
+        <v>33.609</v>
       </c>
       <c r="G52">
         <v>7.36</v>
@@ -5551,28 +5551,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M52">
-        <v>1.822135</v>
+        <v>1.8585777</v>
       </c>
       <c r="N52">
-        <v>7.397865</v>
+        <v>7.361422300000001</v>
       </c>
       <c r="O52">
-        <v>1.10967975</v>
+        <v>1.104213345</v>
       </c>
       <c r="P52">
-        <v>6.288185250000001</v>
+        <v>6.257208955000001</v>
       </c>
       <c r="Q52">
-        <v>7.028185250000001</v>
+        <v>6.997208955000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1270360292127135</v>
+        <v>0.1285594848074362</v>
       </c>
       <c r="T52">
-        <v>1.487866403945919</v>
+        <v>1.515769028178771</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.059998298699053</v>
+        <v>4.960782645783386</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08696669755564372</v>
+        <v>0.08691288050493072</v>
       </c>
       <c r="C53">
-        <v>34.44385195591696</v>
+        <v>33.81416207779709</v>
       </c>
       <c r="D53">
-        <v>60.69285195591696</v>
+        <v>60.72216207779709</v>
       </c>
       <c r="E53">
-        <v>10.509</v>
+        <v>11.168</v>
       </c>
       <c r="F53">
-        <v>33.609</v>
+        <v>34.268</v>
       </c>
       <c r="G53">
         <v>7.36</v>
@@ -5633,28 +5633,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M53">
-        <v>1.8585777</v>
+        <v>1.8950204</v>
       </c>
       <c r="N53">
-        <v>7.361422300000001</v>
+        <v>7.324979600000001</v>
       </c>
       <c r="O53">
-        <v>1.104213345</v>
+        <v>1.09874694</v>
       </c>
       <c r="P53">
-        <v>6.257208955000001</v>
+        <v>6.226232660000001</v>
       </c>
       <c r="Q53">
-        <v>6.997208955000001</v>
+        <v>6.966232660000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1285594848074362</v>
+        <v>0.1301464177186057</v>
       </c>
       <c r="T53">
-        <v>1.515769028178771</v>
+        <v>1.544834261754659</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.960782645783386</v>
+        <v>4.865382979518321</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08691288050493072</v>
+        <v>0.08685906345421771</v>
       </c>
       <c r="C54">
-        <v>33.81416207779709</v>
+        <v>33.18450052256171</v>
       </c>
       <c r="D54">
-        <v>60.72216207779709</v>
+        <v>60.75150052256171</v>
       </c>
       <c r="E54">
-        <v>11.168</v>
+        <v>11.82700000000001</v>
       </c>
       <c r="F54">
-        <v>34.268</v>
+        <v>34.92700000000001</v>
       </c>
       <c r="G54">
         <v>7.36</v>
@@ -5715,28 +5715,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M54">
-        <v>1.8950204</v>
+        <v>1.9314631</v>
       </c>
       <c r="N54">
-        <v>7.324979600000001</v>
+        <v>7.2885369</v>
       </c>
       <c r="O54">
-        <v>1.09874694</v>
+        <v>1.093280535</v>
       </c>
       <c r="P54">
-        <v>6.226232660000001</v>
+        <v>6.195256365000001</v>
       </c>
       <c r="Q54">
-        <v>6.966232660000001</v>
+        <v>6.935256365000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1301464177186057</v>
+        <v>0.1318008796898249</v>
       </c>
       <c r="T54">
-        <v>1.544834261754659</v>
+        <v>1.575136313780584</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.865382979518321</v>
+        <v>4.773583300659483</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08685906345421771</v>
+        <v>0.0868052464035047</v>
       </c>
       <c r="C55">
-        <v>33.18450052256171</v>
+        <v>32.55486733128404</v>
       </c>
       <c r="D55">
-        <v>60.75150052256171</v>
+        <v>60.78086733128404</v>
       </c>
       <c r="E55">
-        <v>11.82700000000001</v>
+        <v>12.486</v>
       </c>
       <c r="F55">
-        <v>34.92700000000001</v>
+        <v>35.58600000000001</v>
       </c>
       <c r="G55">
         <v>7.36</v>
@@ -5797,28 +5797,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M55">
-        <v>1.9314631</v>
+        <v>1.9679058</v>
       </c>
       <c r="N55">
-        <v>7.2885369</v>
+        <v>7.2520942</v>
       </c>
       <c r="O55">
-        <v>1.093280535</v>
+        <v>1.08781413</v>
       </c>
       <c r="P55">
-        <v>6.195256365000001</v>
+        <v>6.16428007</v>
       </c>
       <c r="Q55">
-        <v>6.935256365000001</v>
+        <v>6.90428007</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1318008796898249</v>
+        <v>0.1335272747902276</v>
       </c>
       <c r="T55">
-        <v>1.575136313780584</v>
+        <v>1.606755846329377</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.773583300659483</v>
+        <v>4.685183609906531</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0868052464035047</v>
+        <v>0.08675142935279169</v>
       </c>
       <c r="C56">
-        <v>32.55486733128404</v>
+        <v>31.92526254511674</v>
       </c>
       <c r="D56">
-        <v>60.78086733128404</v>
+        <v>60.81026254511674</v>
       </c>
       <c r="E56">
-        <v>12.486</v>
+        <v>13.145</v>
       </c>
       <c r="F56">
-        <v>35.58600000000001</v>
+        <v>36.245</v>
       </c>
       <c r="G56">
         <v>7.36</v>
@@ -5879,28 +5879,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M56">
-        <v>1.9679058</v>
+        <v>2.0043485</v>
       </c>
       <c r="N56">
-        <v>7.2520942</v>
+        <v>7.2156515</v>
       </c>
       <c r="O56">
-        <v>1.08781413</v>
+        <v>1.082347725</v>
       </c>
       <c r="P56">
-        <v>6.16428007</v>
+        <v>6.133303775</v>
       </c>
       <c r="Q56">
-        <v>6.90428007</v>
+        <v>6.873303775</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1335272747902276</v>
+        <v>0.1353303985617593</v>
       </c>
       <c r="T56">
-        <v>1.606755846329377</v>
+        <v>1.639780691435893</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.685183609906531</v>
+        <v>4.599998453362776</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08675142935279169</v>
+        <v>0.08669761230207867</v>
       </c>
       <c r="C57">
-        <v>31.92526254511674</v>
+        <v>31.29568620529209</v>
       </c>
       <c r="D57">
-        <v>60.81026254511674</v>
+        <v>60.83968620529209</v>
       </c>
       <c r="E57">
-        <v>13.145</v>
+        <v>13.804</v>
       </c>
       <c r="F57">
-        <v>36.245</v>
+        <v>36.904</v>
       </c>
       <c r="G57">
         <v>7.36</v>
@@ -5961,28 +5961,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M57">
-        <v>2.0043485</v>
+        <v>2.0407912</v>
       </c>
       <c r="N57">
-        <v>7.2156515</v>
+        <v>7.179208800000001</v>
       </c>
       <c r="O57">
-        <v>1.082347725</v>
+        <v>1.07688132</v>
       </c>
       <c r="P57">
-        <v>6.133303775</v>
+        <v>6.10232748</v>
       </c>
       <c r="Q57">
-        <v>6.873303775</v>
+        <v>6.842327480000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1353303985617593</v>
+        <v>0.1372154825047243</v>
       </c>
       <c r="T57">
-        <v>1.639780691435893</v>
+        <v>1.674306665865432</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.599998453362776</v>
+        <v>4.517855623838441</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08669761230207867</v>
+        <v>0.08785504525136567</v>
       </c>
       <c r="C58">
-        <v>31.29568620529209</v>
+        <v>30.01009154264487</v>
       </c>
       <c r="D58">
-        <v>60.83968620529209</v>
+        <v>60.21309154264487</v>
       </c>
       <c r="E58">
-        <v>13.804</v>
+        <v>14.46300000000001</v>
       </c>
       <c r="F58">
-        <v>36.904</v>
+        <v>37.56300000000001</v>
       </c>
       <c r="G58">
         <v>7.36</v>
@@ -6043,45 +6043,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M58">
-        <v>2.0407912</v>
+        <v>2.171141400000001</v>
       </c>
       <c r="N58">
-        <v>7.179208800000001</v>
+        <v>7.0488586</v>
       </c>
       <c r="O58">
-        <v>1.07688132</v>
+        <v>1.05732879</v>
       </c>
       <c r="P58">
-        <v>6.10232748</v>
+        <v>5.99152981</v>
       </c>
       <c r="Q58">
-        <v>6.842327480000001</v>
+        <v>6.731529810000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1372154825047243</v>
+        <v>0.1391882447706178</v>
       </c>
       <c r="T58">
-        <v>1.674306665865432</v>
+        <v>1.710438499570764</v>
       </c>
       <c r="U58">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.517855623838441</v>
+        <v>4.246614246313021</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08785504525136567</v>
+        <v>0.08782247820065264</v>
       </c>
       <c r="C59">
-        <v>30.01009154264487</v>
+        <v>29.36854570907609</v>
       </c>
       <c r="D59">
-        <v>60.21309154264487</v>
+        <v>60.23054570907609</v>
       </c>
       <c r="E59">
-        <v>14.46300000000001</v>
+        <v>15.12200000000001</v>
       </c>
       <c r="F59">
-        <v>37.56300000000001</v>
+        <v>38.22200000000001</v>
       </c>
       <c r="G59">
         <v>7.36</v>
@@ -6125,28 +6125,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M59">
-        <v>2.171141400000001</v>
+        <v>2.209231600000001</v>
       </c>
       <c r="N59">
-        <v>7.0488586</v>
+        <v>7.0107684</v>
       </c>
       <c r="O59">
-        <v>1.05732879</v>
+        <v>1.05161526</v>
       </c>
       <c r="P59">
-        <v>5.99152981</v>
+        <v>5.95915314</v>
       </c>
       <c r="Q59">
-        <v>6.731529810000001</v>
+        <v>6.69915314</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1391882447706178</v>
+        <v>0.141254948096792</v>
       </c>
       <c r="T59">
-        <v>1.710438499570764</v>
+        <v>1.748290896785874</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.246614246313021</v>
+        <v>4.173396759307624</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08782247820065266</v>
+        <v>0.08778991114993964</v>
       </c>
       <c r="C60">
-        <v>29.36854570907608</v>
+        <v>28.72700999743437</v>
       </c>
       <c r="D60">
-        <v>60.23054570907608</v>
+        <v>60.24800999743436</v>
       </c>
       <c r="E60">
-        <v>15.122</v>
+        <v>15.781</v>
       </c>
       <c r="F60">
-        <v>38.222</v>
+        <v>38.881</v>
       </c>
       <c r="G60">
         <v>7.36</v>
@@ -6207,28 +6207,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M60">
-        <v>2.2092316</v>
+        <v>2.2473218</v>
       </c>
       <c r="N60">
-        <v>7.0107684</v>
+        <v>6.972678200000001</v>
       </c>
       <c r="O60">
-        <v>1.05161526</v>
+        <v>1.04590173</v>
       </c>
       <c r="P60">
-        <v>5.95915314</v>
+        <v>5.926776470000001</v>
       </c>
       <c r="Q60">
-        <v>6.69915314</v>
+        <v>6.666776470000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.141254948096792</v>
+        <v>0.143422466219365</v>
       </c>
       <c r="T60">
-        <v>1.748290896785873</v>
+        <v>1.78798975240172</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.173396759307625</v>
+        <v>4.102661221014276</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08778991114993964</v>
+        <v>0.08775734409922663</v>
       </c>
       <c r="C61">
-        <v>28.72700999743437</v>
+        <v>28.08548441652704</v>
       </c>
       <c r="D61">
-        <v>60.24800999743436</v>
+        <v>60.26548441652704</v>
       </c>
       <c r="E61">
-        <v>15.781</v>
+        <v>16.44</v>
       </c>
       <c r="F61">
-        <v>38.881</v>
+        <v>39.54</v>
       </c>
       <c r="G61">
         <v>7.36</v>
@@ -6289,28 +6289,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M61">
-        <v>2.2473218</v>
+        <v>2.285412</v>
       </c>
       <c r="N61">
-        <v>6.972678200000001</v>
+        <v>6.934588000000001</v>
       </c>
       <c r="O61">
-        <v>1.04590173</v>
+        <v>1.0401882</v>
       </c>
       <c r="P61">
-        <v>5.926776470000001</v>
+        <v>5.8943998</v>
       </c>
       <c r="Q61">
-        <v>6.666776470000001</v>
+        <v>6.634399800000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.143422466219365</v>
+        <v>0.1456983602480666</v>
       </c>
       <c r="T61">
-        <v>1.78798975240172</v>
+        <v>1.829673550798359</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.102661221014276</v>
+        <v>4.034283533997371</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08775734409922663</v>
+        <v>0.08953952704851362</v>
       </c>
       <c r="C62">
-        <v>28.08548441652704</v>
+        <v>26.48489076643158</v>
       </c>
       <c r="D62">
-        <v>60.26548441652704</v>
+        <v>59.32389076643158</v>
       </c>
       <c r="E62">
-        <v>16.44</v>
+        <v>17.099</v>
       </c>
       <c r="F62">
-        <v>39.54</v>
+        <v>40.19900000000001</v>
       </c>
       <c r="G62">
         <v>7.36</v>
@@ -6371,45 +6371,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M62">
-        <v>2.285412</v>
+        <v>2.4641987</v>
       </c>
       <c r="N62">
-        <v>6.934588000000001</v>
+        <v>6.7558013</v>
       </c>
       <c r="O62">
-        <v>1.0401882</v>
+        <v>1.013370195</v>
       </c>
       <c r="P62">
-        <v>5.8943998</v>
+        <v>5.742431105</v>
       </c>
       <c r="Q62">
-        <v>6.634399800000001</v>
+        <v>6.482431105</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1456983602480666</v>
+        <v>0.1480909667910606</v>
       </c>
       <c r="T62">
-        <v>1.829673550798359</v>
+        <v>1.873494979882006</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.15</v>
       </c>
       <c r="W62">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.034283533997371</v>
+        <v>3.741581391143498</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08953952704851362</v>
+        <v>0.08953670999780061</v>
       </c>
       <c r="C63">
-        <v>26.48489076643158</v>
+        <v>25.82735590129455</v>
       </c>
       <c r="D63">
-        <v>59.32389076643158</v>
+        <v>59.32535590129455</v>
       </c>
       <c r="E63">
-        <v>17.099</v>
+        <v>17.758</v>
       </c>
       <c r="F63">
-        <v>40.19900000000001</v>
+        <v>40.858</v>
       </c>
       <c r="G63">
         <v>7.36</v>
@@ -6453,28 +6453,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M63">
-        <v>2.4641987</v>
+        <v>2.5045954</v>
       </c>
       <c r="N63">
-        <v>6.7558013</v>
+        <v>6.7154046</v>
       </c>
       <c r="O63">
-        <v>1.013370195</v>
+        <v>1.00731069</v>
       </c>
       <c r="P63">
-        <v>5.742431105</v>
+        <v>5.708093910000001</v>
       </c>
       <c r="Q63">
-        <v>6.482431105</v>
+        <v>6.448093910000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1480909667910606</v>
+        <v>0.1506094999942121</v>
       </c>
       <c r="T63">
-        <v>1.873494979882006</v>
+        <v>1.919622799970054</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.741581391143498</v>
+        <v>3.681233304189571</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08953670999780061</v>
+        <v>0.08953389294708761</v>
       </c>
       <c r="C64">
-        <v>25.82735590129455</v>
+        <v>25.1698211085288</v>
       </c>
       <c r="D64">
-        <v>59.32535590129455</v>
+        <v>59.3268211085288</v>
       </c>
       <c r="E64">
-        <v>17.758</v>
+        <v>18.417</v>
       </c>
       <c r="F64">
-        <v>40.858</v>
+        <v>41.517</v>
       </c>
       <c r="G64">
         <v>7.36</v>
@@ -6535,28 +6535,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M64">
-        <v>2.5045954</v>
+        <v>2.5449921</v>
       </c>
       <c r="N64">
-        <v>6.7154046</v>
+        <v>6.675007900000001</v>
       </c>
       <c r="O64">
-        <v>1.00731069</v>
+        <v>1.001251185</v>
       </c>
       <c r="P64">
-        <v>5.708093910000001</v>
+        <v>5.673756715000001</v>
       </c>
       <c r="Q64">
-        <v>6.448093910000001</v>
+        <v>6.413756715000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1506094999942121</v>
+        <v>0.1532641701272638</v>
       </c>
       <c r="T64">
-        <v>1.919622799970054</v>
+        <v>1.968244015738538</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.681233304189571</v>
+        <v>3.622801029519895</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08953389294708761</v>
+        <v>0.08953107589637457</v>
       </c>
       <c r="C65">
-        <v>25.1698211085288</v>
+        <v>24.51228638813974</v>
       </c>
       <c r="D65">
-        <v>59.3268211085288</v>
+        <v>59.32828638813974</v>
       </c>
       <c r="E65">
-        <v>18.417</v>
+        <v>19.076</v>
       </c>
       <c r="F65">
-        <v>41.517</v>
+        <v>42.176</v>
       </c>
       <c r="G65">
         <v>7.36</v>
@@ -6617,28 +6617,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M65">
-        <v>2.5449921</v>
+        <v>2.5853888</v>
       </c>
       <c r="N65">
-        <v>6.675007900000001</v>
+        <v>6.6346112</v>
       </c>
       <c r="O65">
-        <v>1.001251185</v>
+        <v>0.99519168</v>
       </c>
       <c r="P65">
-        <v>5.673756715000001</v>
+        <v>5.639419520000001</v>
       </c>
       <c r="Q65">
-        <v>6.413756715000001</v>
+        <v>6.379419520000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1532641701272638</v>
+        <v>0.1560663219343738</v>
       </c>
       <c r="T65">
-        <v>1.968244015738538</v>
+        <v>2.019566410160826</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.622801029519895</v>
+        <v>3.566194763433647</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08953107589637457</v>
+        <v>0.08952825884566158</v>
       </c>
       <c r="C66">
-        <v>24.51228638813974</v>
+        <v>23.85475174013263</v>
       </c>
       <c r="D66">
-        <v>59.32828638813974</v>
+        <v>59.32975174013264</v>
       </c>
       <c r="E66">
-        <v>19.076</v>
+        <v>19.73500000000001</v>
       </c>
       <c r="F66">
-        <v>42.176</v>
+        <v>42.83500000000001</v>
       </c>
       <c r="G66">
         <v>7.36</v>
@@ -6699,28 +6699,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M66">
-        <v>2.5853888</v>
+        <v>2.625785500000001</v>
       </c>
       <c r="N66">
-        <v>6.6346112</v>
+        <v>6.5942145</v>
       </c>
       <c r="O66">
-        <v>0.99519168</v>
+        <v>0.9891321749999999</v>
       </c>
       <c r="P66">
-        <v>5.639419520000001</v>
+        <v>5.605082325</v>
       </c>
       <c r="Q66">
-        <v>6.379419520000001</v>
+        <v>6.345082325</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1560663219343738</v>
+        <v>0.1590285967018902</v>
       </c>
       <c r="T66">
-        <v>2.019566410160826</v>
+        <v>2.073821512835818</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.566194763433647</v>
+        <v>3.51133022861159</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08952825884566158</v>
+        <v>0.09109624179494857</v>
       </c>
       <c r="C67">
-        <v>23.85475174013263</v>
+        <v>22.39117121167038</v>
       </c>
       <c r="D67">
-        <v>59.32975174013264</v>
+        <v>58.52517121167038</v>
       </c>
       <c r="E67">
-        <v>19.73500000000001</v>
+        <v>20.39400000000001</v>
       </c>
       <c r="F67">
-        <v>42.83500000000001</v>
+        <v>43.49400000000001</v>
       </c>
       <c r="G67">
         <v>7.36</v>
@@ -6781,45 +6781,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M67">
-        <v>2.625785500000001</v>
+        <v>2.7879654</v>
       </c>
       <c r="N67">
-        <v>6.5942145</v>
+        <v>6.4320346</v>
       </c>
       <c r="O67">
-        <v>0.9891321749999999</v>
+        <v>0.9648051899999999</v>
       </c>
       <c r="P67">
-        <v>5.605082325</v>
+        <v>5.46722941</v>
       </c>
       <c r="Q67">
-        <v>6.345082325</v>
+        <v>6.20722941</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1590285967018902</v>
+        <v>0.1621651229263193</v>
       </c>
       <c r="T67">
-        <v>2.073821512835818</v>
+        <v>2.131268092138749</v>
       </c>
       <c r="U67">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.15</v>
       </c>
       <c r="W67">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.51133022861159</v>
+        <v>3.307071170969338</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09109624179494857</v>
+        <v>0.09111722474423556</v>
       </c>
       <c r="C68">
-        <v>22.39117121167038</v>
+        <v>21.72155215184031</v>
       </c>
       <c r="D68">
-        <v>58.52517121167038</v>
+        <v>58.51455215184032</v>
       </c>
       <c r="E68">
-        <v>20.39400000000001</v>
+        <v>21.053</v>
       </c>
       <c r="F68">
-        <v>43.49400000000001</v>
+        <v>44.15300000000001</v>
       </c>
       <c r="G68">
         <v>7.36</v>
@@ -6863,28 +6863,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M68">
-        <v>2.7879654</v>
+        <v>2.830207300000001</v>
       </c>
       <c r="N68">
-        <v>6.4320346</v>
+        <v>6.3897927</v>
       </c>
       <c r="O68">
-        <v>0.9648051899999999</v>
+        <v>0.9584689049999999</v>
       </c>
       <c r="P68">
-        <v>5.46722941</v>
+        <v>5.431323795</v>
       </c>
       <c r="Q68">
-        <v>6.20722941</v>
+        <v>6.171323795</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1621651229263193</v>
+        <v>0.1654917416491987</v>
       </c>
       <c r="T68">
-        <v>2.131268092138749</v>
+        <v>2.192196282308524</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.307071170969338</v>
+        <v>3.257711899760841</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09111722474423556</v>
+        <v>0.09113820769352254</v>
       </c>
       <c r="C69">
-        <v>21.72155215184031</v>
+        <v>21.05193694484733</v>
       </c>
       <c r="D69">
-        <v>58.51455215184032</v>
+        <v>58.50393694484734</v>
       </c>
       <c r="E69">
-        <v>21.053</v>
+        <v>21.712</v>
       </c>
       <c r="F69">
-        <v>44.15300000000001</v>
+        <v>44.812</v>
       </c>
       <c r="G69">
         <v>7.36</v>
@@ -6945,28 +6945,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M69">
-        <v>2.830207300000001</v>
+        <v>2.872449200000001</v>
       </c>
       <c r="N69">
-        <v>6.3897927</v>
+        <v>6.3475508</v>
       </c>
       <c r="O69">
-        <v>0.9584689049999999</v>
+        <v>0.95213262</v>
       </c>
       <c r="P69">
-        <v>5.431323795</v>
+        <v>5.39541818</v>
       </c>
       <c r="Q69">
-        <v>6.171323795</v>
+        <v>6.13541818</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1654917416491987</v>
+        <v>0.169026274042258</v>
       </c>
       <c r="T69">
-        <v>2.192196282308524</v>
+        <v>2.256932484363911</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.257711899760841</v>
+        <v>3.209804371823181</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09113820769352254</v>
+        <v>0.09115919064280953</v>
       </c>
       <c r="C70">
-        <v>21.05193694484733</v>
+        <v>20.38232558859497</v>
       </c>
       <c r="D70">
-        <v>58.50393694484734</v>
+        <v>58.49332558859498</v>
       </c>
       <c r="E70">
-        <v>21.712</v>
+        <v>22.37100000000001</v>
       </c>
       <c r="F70">
-        <v>44.812</v>
+        <v>45.47100000000001</v>
       </c>
       <c r="G70">
         <v>7.36</v>
@@ -7027,28 +7027,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M70">
-        <v>2.872449200000001</v>
+        <v>2.914691100000001</v>
       </c>
       <c r="N70">
-        <v>6.3475508</v>
+        <v>6.3053089</v>
       </c>
       <c r="O70">
-        <v>0.95213262</v>
+        <v>0.9457963349999999</v>
       </c>
       <c r="P70">
-        <v>5.39541818</v>
+        <v>5.359512565</v>
       </c>
       <c r="Q70">
-        <v>6.13541818</v>
+        <v>6.099512565</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.169026274042258</v>
+        <v>0.1727888407832566</v>
       </c>
       <c r="T70">
-        <v>2.256932484363911</v>
+        <v>2.325845215584161</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.209804371823181</v>
+        <v>3.163285467883714</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09115919064280953</v>
+        <v>0.09118017359209651</v>
       </c>
       <c r="C71">
-        <v>20.38232558859497</v>
+        <v>19.71271808098828</v>
       </c>
       <c r="D71">
-        <v>58.49332558859498</v>
+        <v>58.48271808098828</v>
       </c>
       <c r="E71">
-        <v>22.37100000000001</v>
+        <v>23.03000000000001</v>
       </c>
       <c r="F71">
-        <v>45.47100000000001</v>
+        <v>46.13000000000001</v>
       </c>
       <c r="G71">
         <v>7.36</v>
@@ -7109,28 +7109,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M71">
-        <v>2.914691100000001</v>
+        <v>2.956933000000001</v>
       </c>
       <c r="N71">
-        <v>6.3053089</v>
+        <v>6.263066999999999</v>
       </c>
       <c r="O71">
-        <v>0.9457963349999999</v>
+        <v>0.9394600499999999</v>
       </c>
       <c r="P71">
-        <v>5.359512565</v>
+        <v>5.323606949999999</v>
       </c>
       <c r="Q71">
-        <v>6.099512565</v>
+        <v>6.06360695</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1727888407832566</v>
+        <v>0.1768022453069884</v>
       </c>
       <c r="T71">
-        <v>2.325845215584161</v>
+        <v>2.399352128885761</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.163285467883714</v>
+        <v>3.118095675485375</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09118017359209651</v>
+        <v>0.09120115654138353</v>
       </c>
       <c r="C72">
-        <v>19.71271808098828</v>
+        <v>19.04311441993382</v>
       </c>
       <c r="D72">
-        <v>58.48271808098828</v>
+        <v>58.47211441993382</v>
       </c>
       <c r="E72">
-        <v>23.03000000000001</v>
+        <v>23.68900000000001</v>
       </c>
       <c r="F72">
-        <v>46.13000000000001</v>
+        <v>46.78900000000001</v>
       </c>
       <c r="G72">
         <v>7.36</v>
@@ -7191,28 +7191,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M72">
-        <v>2.956933000000001</v>
+        <v>2.999174900000001</v>
       </c>
       <c r="N72">
-        <v>6.263066999999999</v>
+        <v>6.2208251</v>
       </c>
       <c r="O72">
-        <v>0.9394600499999999</v>
+        <v>0.9331237649999999</v>
       </c>
       <c r="P72">
-        <v>5.323606949999999</v>
+        <v>5.287701335</v>
       </c>
       <c r="Q72">
-        <v>6.06360695</v>
+        <v>6.027701335</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1768022453069884</v>
+        <v>0.1810924363495984</v>
       </c>
       <c r="T72">
-        <v>2.399352128885761</v>
+        <v>2.477928484484024</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.118095675485375</v>
+        <v>3.074178834985581</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09120115654138353</v>
+        <v>0.09122213949067051</v>
       </c>
       <c r="C73">
-        <v>19.04311441993383</v>
+        <v>18.37351460333972</v>
       </c>
       <c r="D73">
-        <v>58.47211441993382</v>
+        <v>58.46151460333972</v>
       </c>
       <c r="E73">
-        <v>23.689</v>
+        <v>24.348</v>
       </c>
       <c r="F73">
-        <v>46.789</v>
+        <v>47.448</v>
       </c>
       <c r="G73">
         <v>7.36</v>
@@ -7273,28 +7273,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M73">
-        <v>2.9991749</v>
+        <v>3.0414168</v>
       </c>
       <c r="N73">
-        <v>6.220825100000001</v>
+        <v>6.1785832</v>
       </c>
       <c r="O73">
-        <v>0.933123765</v>
+        <v>0.92678748</v>
       </c>
       <c r="P73">
-        <v>5.287701335</v>
+        <v>5.251795720000001</v>
       </c>
       <c r="Q73">
-        <v>6.027701335000001</v>
+        <v>5.991795720000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1810924363495983</v>
+        <v>0.1856890696095375</v>
       </c>
       <c r="T73">
-        <v>2.477928484484023</v>
+        <v>2.562117436910733</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.074178834985582</v>
+        <v>3.031481906721893</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09122213949067051</v>
+        <v>0.09608302243995749</v>
       </c>
       <c r="C74">
-        <v>18.37351460333972</v>
+        <v>15.35836648868043</v>
       </c>
       <c r="D74">
-        <v>58.46151460333972</v>
+        <v>56.10536648868044</v>
       </c>
       <c r="E74">
-        <v>24.348</v>
+        <v>25.00700000000001</v>
       </c>
       <c r="F74">
-        <v>47.448</v>
+        <v>48.10700000000001</v>
       </c>
       <c r="G74">
         <v>7.36</v>
@@ -7355,45 +7355,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M74">
-        <v>3.0414168</v>
+        <v>3.458893300000001</v>
       </c>
       <c r="N74">
-        <v>6.1785832</v>
+        <v>5.7611067</v>
       </c>
       <c r="O74">
-        <v>0.92678748</v>
+        <v>0.864166005</v>
       </c>
       <c r="P74">
-        <v>5.251795720000001</v>
+        <v>4.896940695</v>
       </c>
       <c r="Q74">
-        <v>5.991795720000001</v>
+        <v>5.636940695</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1856890696095375</v>
+        <v>0.1906261942220648</v>
       </c>
       <c r="T74">
-        <v>2.562117436910733</v>
+        <v>2.652542608035717</v>
       </c>
       <c r="U74">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.15</v>
       </c>
       <c r="W74">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.031481906721893</v>
+        <v>2.665592488788249</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09608302243995749</v>
+        <v>0.09617030538924448</v>
       </c>
       <c r="C75">
-        <v>15.35836648868043</v>
+        <v>14.65879349984373</v>
       </c>
       <c r="D75">
-        <v>56.10536648868044</v>
+        <v>56.06479349984374</v>
       </c>
       <c r="E75">
-        <v>25.00700000000001</v>
+        <v>25.666</v>
       </c>
       <c r="F75">
-        <v>48.10700000000001</v>
+        <v>48.76600000000001</v>
       </c>
       <c r="G75">
         <v>7.36</v>
@@ -7437,28 +7437,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M75">
-        <v>3.458893300000001</v>
+        <v>3.506275400000001</v>
       </c>
       <c r="N75">
-        <v>5.7611067</v>
+        <v>5.7137246</v>
       </c>
       <c r="O75">
-        <v>0.864166005</v>
+        <v>0.85705869</v>
       </c>
       <c r="P75">
-        <v>4.896940695</v>
+        <v>4.85666591</v>
       </c>
       <c r="Q75">
-        <v>5.636940695</v>
+        <v>5.59666591</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1906261942220648</v>
+        <v>0.1959430976509403</v>
       </c>
       <c r="T75">
-        <v>2.652542608035717</v>
+        <v>2.749923561554931</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.665592488788249</v>
+        <v>2.629570968669489</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09617030538924448</v>
+        <v>0.09625758833853147</v>
       </c>
       <c r="C76">
-        <v>14.65879349984373</v>
+        <v>13.95927914988416</v>
       </c>
       <c r="D76">
-        <v>56.06479349984374</v>
+        <v>56.02427914988417</v>
       </c>
       <c r="E76">
-        <v>25.666</v>
+        <v>26.325</v>
       </c>
       <c r="F76">
-        <v>48.76600000000001</v>
+        <v>49.425</v>
       </c>
       <c r="G76">
         <v>7.36</v>
@@ -7519,28 +7519,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M76">
-        <v>3.506275400000001</v>
+        <v>3.553657500000001</v>
       </c>
       <c r="N76">
-        <v>5.7137246</v>
+        <v>5.6663425</v>
       </c>
       <c r="O76">
-        <v>0.85705869</v>
+        <v>0.849951375</v>
       </c>
       <c r="P76">
-        <v>4.85666591</v>
+        <v>4.816391125</v>
       </c>
       <c r="Q76">
-        <v>5.59666591</v>
+        <v>5.556391125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1959430976509403</v>
+        <v>0.2016853533541259</v>
       </c>
       <c r="T76">
-        <v>2.749923561554931</v>
+        <v>2.855094991355682</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.629570968669489</v>
+        <v>2.594510022420562</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09625758833853147</v>
+        <v>0.09634487128781846</v>
       </c>
       <c r="C77">
-        <v>13.95927914988416</v>
+        <v>13.2598233117701</v>
       </c>
       <c r="D77">
-        <v>56.02427914988417</v>
+        <v>55.9838233117701</v>
       </c>
       <c r="E77">
-        <v>26.325</v>
+        <v>26.984</v>
       </c>
       <c r="F77">
-        <v>49.425</v>
+        <v>50.084</v>
       </c>
       <c r="G77">
         <v>7.36</v>
@@ -7601,28 +7601,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M77">
-        <v>3.553657500000001</v>
+        <v>3.6010396</v>
       </c>
       <c r="N77">
-        <v>5.6663425</v>
+        <v>5.618960400000001</v>
       </c>
       <c r="O77">
-        <v>0.849951375</v>
+        <v>0.8428440600000001</v>
       </c>
       <c r="P77">
-        <v>4.816391125</v>
+        <v>4.776116340000001</v>
       </c>
       <c r="Q77">
-        <v>5.556391125</v>
+        <v>5.516116340000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2016853533541259</v>
+        <v>0.2079061303659103</v>
       </c>
       <c r="T77">
-        <v>2.855094991355682</v>
+        <v>2.969030706973162</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.594510022420562</v>
+        <v>2.560371732651871</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09634487128781846</v>
+        <v>0.09643215423710545</v>
       </c>
       <c r="C78">
-        <v>13.2598233117701</v>
+        <v>12.5604258588366</v>
       </c>
       <c r="D78">
-        <v>55.9838233117701</v>
+        <v>55.9434258588366</v>
       </c>
       <c r="E78">
-        <v>26.984</v>
+        <v>27.643</v>
       </c>
       <c r="F78">
-        <v>50.084</v>
+        <v>50.743</v>
       </c>
       <c r="G78">
         <v>7.36</v>
@@ -7683,28 +7683,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M78">
-        <v>3.6010396</v>
+        <v>3.648421700000001</v>
       </c>
       <c r="N78">
-        <v>5.618960400000001</v>
+        <v>5.571578300000001</v>
       </c>
       <c r="O78">
-        <v>0.8428440600000001</v>
+        <v>0.8357367450000001</v>
       </c>
       <c r="P78">
-        <v>4.776116340000001</v>
+        <v>4.735841555</v>
       </c>
       <c r="Q78">
-        <v>5.516116340000001</v>
+        <v>5.475841555000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2079061303659103</v>
+        <v>0.2146678445091541</v>
       </c>
       <c r="T78">
-        <v>2.969030706973162</v>
+        <v>3.092873876122597</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.560371732651871</v>
+        <v>2.52712015170834</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09643215423710545</v>
+        <v>0.09910513718639244</v>
       </c>
       <c r="C79">
-        <v>12.5604258588366</v>
+        <v>10.69190152142193</v>
       </c>
       <c r="D79">
-        <v>55.9434258588366</v>
+        <v>54.73390152142194</v>
       </c>
       <c r="E79">
-        <v>27.643</v>
+        <v>28.30200000000001</v>
       </c>
       <c r="F79">
-        <v>50.743</v>
+        <v>51.40200000000001</v>
       </c>
       <c r="G79">
         <v>7.36</v>
@@ -7765,45 +7765,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M79">
-        <v>3.648421700000001</v>
+        <v>3.896271600000001</v>
       </c>
       <c r="N79">
-        <v>5.571578300000001</v>
+        <v>5.3237284</v>
       </c>
       <c r="O79">
-        <v>0.8357367450000001</v>
+        <v>0.79855926</v>
       </c>
       <c r="P79">
-        <v>4.735841555</v>
+        <v>4.52516914</v>
       </c>
       <c r="Q79">
-        <v>5.475841555000001</v>
+        <v>5.26516914</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2146678445091541</v>
+        <v>0.2220442599381474</v>
       </c>
       <c r="T79">
-        <v>3.092873876122597</v>
+        <v>3.227975515194708</v>
       </c>
       <c r="U79">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.15</v>
       </c>
       <c r="W79">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.52712015170834</v>
+        <v>2.366364808859834</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09910513718639244</v>
+        <v>0.09922557013567943</v>
       </c>
       <c r="C80">
-        <v>10.69190152142193</v>
+        <v>9.979635747425966</v>
       </c>
       <c r="D80">
-        <v>54.73390152142194</v>
+        <v>54.68063574742597</v>
       </c>
       <c r="E80">
-        <v>28.30200000000001</v>
+        <v>28.96100000000001</v>
       </c>
       <c r="F80">
-        <v>51.40200000000001</v>
+        <v>52.06100000000001</v>
       </c>
       <c r="G80">
         <v>7.36</v>
@@ -7847,28 +7847,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M80">
-        <v>3.896271600000001</v>
+        <v>3.946223800000001</v>
       </c>
       <c r="N80">
-        <v>5.3237284</v>
+        <v>5.2737762</v>
       </c>
       <c r="O80">
-        <v>0.79855926</v>
+        <v>0.79106643</v>
       </c>
       <c r="P80">
-        <v>4.52516914</v>
+        <v>4.48270977</v>
       </c>
       <c r="Q80">
-        <v>5.26516914</v>
+        <v>5.222709770000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2220442599381474</v>
+        <v>0.230123191122283</v>
       </c>
       <c r="T80">
-        <v>3.227975515194708</v>
+        <v>3.375943977035592</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.366364808859834</v>
+        <v>2.336410823937558</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09922557013567943</v>
+        <v>0.09934600308496641</v>
       </c>
       <c r="C81">
-        <v>9.979635747425966</v>
+        <v>9.267473546686993</v>
       </c>
       <c r="D81">
-        <v>54.68063574742597</v>
+        <v>54.627473546687</v>
       </c>
       <c r="E81">
-        <v>28.96100000000001</v>
+        <v>29.62</v>
       </c>
       <c r="F81">
-        <v>52.06100000000001</v>
+        <v>52.72000000000001</v>
       </c>
       <c r="G81">
         <v>7.36</v>
@@ -7929,28 +7929,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M81">
-        <v>3.946223800000001</v>
+        <v>3.996176000000001</v>
       </c>
       <c r="N81">
-        <v>5.2737762</v>
+        <v>5.223824</v>
       </c>
       <c r="O81">
-        <v>0.79106643</v>
+        <v>0.7835736000000001</v>
       </c>
       <c r="P81">
-        <v>4.48270977</v>
+        <v>4.4402504</v>
       </c>
       <c r="Q81">
-        <v>5.222709770000001</v>
+        <v>5.1802504</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.230123191122283</v>
+        <v>0.2390100154248321</v>
       </c>
       <c r="T81">
-        <v>3.375943977035592</v>
+        <v>3.538709285060564</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.336410823937558</v>
+        <v>2.307205688638338</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09934600308496641</v>
+        <v>0.09946643603425341</v>
       </c>
       <c r="C82">
-        <v>9.267473546686993</v>
+        <v>8.555414617407102</v>
       </c>
       <c r="D82">
-        <v>54.627473546687</v>
+        <v>54.57441461740711</v>
       </c>
       <c r="E82">
-        <v>29.62</v>
+        <v>30.279</v>
       </c>
       <c r="F82">
-        <v>52.72000000000001</v>
+        <v>53.379</v>
       </c>
       <c r="G82">
         <v>7.36</v>
@@ -8011,28 +8011,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M82">
-        <v>3.996176000000001</v>
+        <v>4.046128200000001</v>
       </c>
       <c r="N82">
-        <v>5.223824</v>
+        <v>5.1738718</v>
       </c>
       <c r="O82">
-        <v>0.7835736000000001</v>
+        <v>0.77608077</v>
       </c>
       <c r="P82">
-        <v>4.4402504</v>
+        <v>4.39779103</v>
       </c>
       <c r="Q82">
-        <v>5.1802504</v>
+        <v>5.13779103</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2390100154248321</v>
+        <v>0.2488322949171232</v>
       </c>
       <c r="T82">
-        <v>3.538709285060564</v>
+        <v>3.718607783403955</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.307205688638338</v>
+        <v>2.278721667790951</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09946643603425341</v>
+        <v>0.09958686898354038</v>
       </c>
       <c r="C83">
-        <v>8.555414617407102</v>
+        <v>7.84345865895974</v>
       </c>
       <c r="D83">
-        <v>54.57441461740711</v>
+        <v>54.52145865895975</v>
       </c>
       <c r="E83">
-        <v>30.279</v>
+        <v>30.93800000000001</v>
       </c>
       <c r="F83">
-        <v>53.379</v>
+        <v>54.03800000000001</v>
       </c>
       <c r="G83">
         <v>7.36</v>
@@ -8093,28 +8093,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M83">
-        <v>4.046128200000001</v>
+        <v>4.096080400000001</v>
       </c>
       <c r="N83">
-        <v>5.1738718</v>
+        <v>5.1239196</v>
       </c>
       <c r="O83">
-        <v>0.77608077</v>
+        <v>0.76858794</v>
       </c>
       <c r="P83">
-        <v>4.39779103</v>
+        <v>4.35533166</v>
       </c>
       <c r="Q83">
-        <v>5.13779103</v>
+        <v>5.09533166</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2488322949171232</v>
+        <v>0.2597459387974467</v>
       </c>
       <c r="T83">
-        <v>3.718607783403955</v>
+        <v>3.918495003785499</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.278721667790951</v>
+        <v>2.250932379159354</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09958686898354038</v>
+        <v>0.0997073019328274</v>
       </c>
       <c r="C84">
-        <v>7.84345865895974</v>
+        <v>7.131605371884092</v>
       </c>
       <c r="D84">
-        <v>54.52145865895975</v>
+        <v>54.4686053718841</v>
       </c>
       <c r="E84">
-        <v>30.93800000000001</v>
+        <v>31.59700000000001</v>
       </c>
       <c r="F84">
-        <v>54.03800000000001</v>
+        <v>54.69700000000001</v>
       </c>
       <c r="G84">
         <v>7.36</v>
@@ -8175,28 +8175,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M84">
-        <v>4.096080400000001</v>
+        <v>4.146032600000001</v>
       </c>
       <c r="N84">
-        <v>5.1239196</v>
+        <v>5.0739674</v>
       </c>
       <c r="O84">
-        <v>0.76858794</v>
+        <v>0.76109511</v>
       </c>
       <c r="P84">
-        <v>4.35533166</v>
+        <v>4.31287229</v>
       </c>
       <c r="Q84">
-        <v>5.09533166</v>
+        <v>5.05287229</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2597459387974467</v>
+        <v>0.2719435407813376</v>
       </c>
       <c r="T84">
-        <v>3.918495003785499</v>
+        <v>4.141898367741343</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.250932379159354</v>
+        <v>2.223812711940567</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0997073019328274</v>
+        <v>0.09982773488211437</v>
       </c>
       <c r="C85">
-        <v>7.131605371884092</v>
+        <v>6.419854457879417</v>
       </c>
       <c r="D85">
-        <v>54.4686053718841</v>
+        <v>54.41585445787943</v>
       </c>
       <c r="E85">
-        <v>31.59700000000001</v>
+        <v>32.25600000000001</v>
       </c>
       <c r="F85">
-        <v>54.69700000000001</v>
+        <v>55.35600000000001</v>
       </c>
       <c r="G85">
         <v>7.36</v>
@@ -8257,28 +8257,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M85">
-        <v>4.146032600000001</v>
+        <v>4.195984800000001</v>
       </c>
       <c r="N85">
-        <v>5.0739674</v>
+        <v>5.0240152</v>
       </c>
       <c r="O85">
-        <v>0.76109511</v>
+        <v>0.75360228</v>
       </c>
       <c r="P85">
-        <v>4.31287229</v>
+        <v>4.27041292</v>
       </c>
       <c r="Q85">
-        <v>5.05287229</v>
+        <v>5.01041292</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2719435407813376</v>
+        <v>0.2856658430132149</v>
       </c>
       <c r="T85">
-        <v>4.141898367741343</v>
+        <v>4.393227152191668</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.223812711940567</v>
+        <v>2.197338751084132</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09982773488211438</v>
+        <v>0.09994816783140137</v>
       </c>
       <c r="C86">
-        <v>6.419854457879417</v>
+        <v>5.708205619799401</v>
       </c>
       <c r="D86">
-        <v>54.41585445787942</v>
+        <v>54.3632056197994</v>
       </c>
       <c r="E86">
-        <v>32.256</v>
+        <v>32.915</v>
       </c>
       <c r="F86">
-        <v>55.356</v>
+        <v>56.015</v>
       </c>
       <c r="G86">
         <v>7.36</v>
@@ -8339,28 +8339,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M86">
-        <v>4.195984800000001</v>
+        <v>4.245937000000001</v>
       </c>
       <c r="N86">
-        <v>5.0240152</v>
+        <v>4.974063</v>
       </c>
       <c r="O86">
-        <v>0.75360228</v>
+        <v>0.74610945</v>
       </c>
       <c r="P86">
-        <v>4.27041292</v>
+        <v>4.227953550000001</v>
       </c>
       <c r="Q86">
-        <v>5.01041292</v>
+        <v>4.967953550000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2856658430132148</v>
+        <v>0.3012177855426757</v>
       </c>
       <c r="T86">
-        <v>4.393227152191665</v>
+        <v>4.678066441235366</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.197338751084132</v>
+        <v>2.17148770695373</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09994816783140137</v>
+        <v>0.1000686007806884</v>
       </c>
       <c r="C87">
-        <v>5.708205619799401</v>
+        <v>4.996658561646605</v>
       </c>
       <c r="D87">
-        <v>54.3632056197994</v>
+        <v>54.31065856164661</v>
       </c>
       <c r="E87">
-        <v>32.915</v>
+        <v>33.57400000000001</v>
       </c>
       <c r="F87">
-        <v>56.015</v>
+        <v>56.67400000000001</v>
       </c>
       <c r="G87">
         <v>7.36</v>
@@ -8421,28 +8421,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M87">
-        <v>4.245937000000001</v>
+        <v>4.295889200000001</v>
       </c>
       <c r="N87">
-        <v>4.974063</v>
+        <v>4.924110799999999</v>
       </c>
       <c r="O87">
-        <v>0.74610945</v>
+        <v>0.7386166199999998</v>
       </c>
       <c r="P87">
-        <v>4.227953550000001</v>
+        <v>4.185494179999999</v>
       </c>
       <c r="Q87">
-        <v>4.967953550000001</v>
+        <v>4.925494179999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3012177855426757</v>
+        <v>0.3189914341477739</v>
       </c>
       <c r="T87">
-        <v>4.678066441235366</v>
+        <v>5.003597057285309</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.17148770695373</v>
+        <v>2.146237849896128</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1000686007806884</v>
+        <v>0.1001890337299753</v>
       </c>
       <c r="C88">
-        <v>4.996658561646605</v>
+        <v>4.285212988566983</v>
       </c>
       <c r="D88">
-        <v>54.31065856164661</v>
+        <v>54.25821298856699</v>
       </c>
       <c r="E88">
-        <v>33.57400000000001</v>
+        <v>34.233</v>
       </c>
       <c r="F88">
-        <v>56.67400000000001</v>
+        <v>57.33300000000001</v>
       </c>
       <c r="G88">
         <v>7.36</v>
@@ -8503,28 +8503,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M88">
-        <v>4.295889200000001</v>
+        <v>4.345841400000001</v>
       </c>
       <c r="N88">
-        <v>4.924110799999999</v>
+        <v>4.874158599999999</v>
       </c>
       <c r="O88">
-        <v>0.7386166199999998</v>
+        <v>0.7311237899999999</v>
       </c>
       <c r="P88">
-        <v>4.185494179999999</v>
+        <v>4.14303481</v>
       </c>
       <c r="Q88">
-        <v>4.925494179999999</v>
+        <v>4.88303481</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3189914341477739</v>
+        <v>0.3394994902305795</v>
       </c>
       <c r="T88">
-        <v>5.003597057285309</v>
+        <v>5.379209306573705</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.146237849896128</v>
+        <v>2.121568449322609</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1001890337299753</v>
+        <v>0.1003094666792623</v>
       </c>
       <c r="C89">
-        <v>4.285212988566983</v>
+        <v>3.573868606844229</v>
       </c>
       <c r="D89">
-        <v>54.25821298856699</v>
+        <v>54.20586860684423</v>
       </c>
       <c r="E89">
-        <v>34.233</v>
+        <v>34.892</v>
       </c>
       <c r="F89">
-        <v>57.33300000000001</v>
+        <v>57.992</v>
       </c>
       <c r="G89">
         <v>7.36</v>
@@ -8585,28 +8585,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M89">
-        <v>4.345841400000001</v>
+        <v>4.395793600000001</v>
       </c>
       <c r="N89">
-        <v>4.874158599999999</v>
+        <v>4.8242064</v>
       </c>
       <c r="O89">
-        <v>0.7311237899999999</v>
+        <v>0.7236309599999999</v>
       </c>
       <c r="P89">
-        <v>4.14303481</v>
+        <v>4.10057544</v>
       </c>
       <c r="Q89">
-        <v>4.88303481</v>
+        <v>4.84057544</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3394994902305795</v>
+        <v>0.3634255556605194</v>
       </c>
       <c r="T89">
-        <v>5.379209306573705</v>
+        <v>5.817423597410169</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.121568449322609</v>
+        <v>2.097459716943944</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1003094666792623</v>
+        <v>0.1004298996285493</v>
       </c>
       <c r="C90">
-        <v>3.573868606844229</v>
+        <v>2.862625123894404</v>
       </c>
       <c r="D90">
-        <v>54.20586860684423</v>
+        <v>54.15362512389441</v>
       </c>
       <c r="E90">
-        <v>34.892</v>
+        <v>35.551</v>
       </c>
       <c r="F90">
-        <v>57.992</v>
+        <v>58.651</v>
       </c>
       <c r="G90">
         <v>7.36</v>
@@ -8667,28 +8667,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M90">
-        <v>4.395793600000001</v>
+        <v>4.445745800000001</v>
       </c>
       <c r="N90">
-        <v>4.8242064</v>
+        <v>4.7742542</v>
       </c>
       <c r="O90">
-        <v>0.7236309599999999</v>
+        <v>0.7161381299999999</v>
       </c>
       <c r="P90">
-        <v>4.10057544</v>
+        <v>4.05811607</v>
       </c>
       <c r="Q90">
-        <v>4.84057544</v>
+        <v>4.79811607</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3634255556605194</v>
+        <v>0.3917018148049938</v>
       </c>
       <c r="T90">
-        <v>5.817423597410169</v>
+        <v>6.335313213853262</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.097459716943944</v>
+        <v>2.073892753832214</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1004298996285493</v>
+        <v>0.1005503325778363</v>
       </c>
       <c r="C91">
-        <v>2.862625123894404</v>
+        <v>2.151482248260429</v>
       </c>
       <c r="D91">
-        <v>54.15362512389441</v>
+        <v>54.10148224826044</v>
       </c>
       <c r="E91">
-        <v>35.551</v>
+        <v>36.21000000000001</v>
       </c>
       <c r="F91">
-        <v>58.651</v>
+        <v>59.31000000000001</v>
       </c>
       <c r="G91">
         <v>7.36</v>
@@ -8749,28 +8749,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M91">
-        <v>4.445745800000001</v>
+        <v>4.495698000000001</v>
       </c>
       <c r="N91">
-        <v>4.7742542</v>
+        <v>4.724302</v>
       </c>
       <c r="O91">
-        <v>0.7161381299999999</v>
+        <v>0.7086452999999999</v>
       </c>
       <c r="P91">
-        <v>4.05811607</v>
+        <v>4.0156567</v>
       </c>
       <c r="Q91">
-        <v>4.79811607</v>
+        <v>4.7556567</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3917018148049938</v>
+        <v>0.4256333257783632</v>
       </c>
       <c r="T91">
-        <v>6.335313213853262</v>
+        <v>6.956780753584973</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.073892753832214</v>
+        <v>2.050849501011856</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1005503325778363</v>
+        <v>0.1006707655271233</v>
       </c>
       <c r="C92">
-        <v>2.151482248260429</v>
+        <v>1.440439689606741</v>
       </c>
       <c r="D92">
-        <v>54.10148224826044</v>
+        <v>54.04943968960675</v>
       </c>
       <c r="E92">
-        <v>36.21000000000001</v>
+        <v>36.86900000000001</v>
       </c>
       <c r="F92">
-        <v>59.31000000000001</v>
+        <v>59.96900000000001</v>
       </c>
       <c r="G92">
         <v>7.36</v>
@@ -8831,28 +8831,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M92">
-        <v>4.495698000000001</v>
+        <v>4.545650200000001</v>
       </c>
       <c r="N92">
-        <v>4.724302</v>
+        <v>4.6743498</v>
       </c>
       <c r="O92">
-        <v>0.7086452999999999</v>
+        <v>0.7011524699999999</v>
       </c>
       <c r="P92">
-        <v>4.0156567</v>
+        <v>3.97319733</v>
       </c>
       <c r="Q92">
-        <v>4.7556567</v>
+        <v>4.71319733</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4256333257783632</v>
+        <v>0.4671051725235923</v>
       </c>
       <c r="T92">
-        <v>6.956780753584973</v>
+        <v>7.716352191034842</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.050849501011856</v>
+        <v>2.028312693308429</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1006707655271233</v>
+        <v>0.1007911984764103</v>
       </c>
       <c r="C93">
-        <v>1.440439689606741</v>
+        <v>0.7294971587137979</v>
       </c>
       <c r="D93">
-        <v>54.04943968960675</v>
+        <v>53.99749715871381</v>
       </c>
       <c r="E93">
-        <v>36.86900000000001</v>
+        <v>37.52800000000001</v>
       </c>
       <c r="F93">
-        <v>59.96900000000001</v>
+        <v>60.62800000000001</v>
       </c>
       <c r="G93">
         <v>7.36</v>
@@ -8913,28 +8913,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M93">
-        <v>4.545650200000001</v>
+        <v>4.595602400000001</v>
       </c>
       <c r="N93">
-        <v>4.6743498</v>
+        <v>4.6243976</v>
       </c>
       <c r="O93">
-        <v>0.7011524699999999</v>
+        <v>0.69365964</v>
       </c>
       <c r="P93">
-        <v>3.97319733</v>
+        <v>3.93073796</v>
       </c>
       <c r="Q93">
-        <v>4.71319733</v>
+        <v>4.67073796</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4671051725235923</v>
+        <v>0.5189449809551288</v>
       </c>
       <c r="T93">
-        <v>7.716352191034842</v>
+        <v>8.665816487847179</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.028312693308429</v>
+        <v>2.00626581620725</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1007911984764103</v>
+        <v>0.1121367314256973</v>
       </c>
       <c r="C94">
-        <v>0.7294971587137979</v>
+        <v>-4.412267384980368</v>
       </c>
       <c r="D94">
-        <v>53.99749715871381</v>
+        <v>49.51473261501964</v>
       </c>
       <c r="E94">
-        <v>37.52800000000001</v>
+        <v>38.187</v>
       </c>
       <c r="F94">
-        <v>60.62800000000001</v>
+        <v>61.28700000000001</v>
       </c>
       <c r="G94">
         <v>7.36</v>
@@ -8995,45 +8995,45 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M94">
-        <v>4.595602400000001</v>
+        <v>5.51583</v>
       </c>
       <c r="N94">
-        <v>4.6243976</v>
+        <v>3.70417</v>
       </c>
       <c r="O94">
-        <v>0.69365964</v>
+        <v>0.5556255</v>
       </c>
       <c r="P94">
-        <v>3.93073796</v>
+        <v>3.1485445</v>
       </c>
       <c r="Q94">
-        <v>4.67073796</v>
+        <v>3.888544500000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5189449809551288</v>
+        <v>0.585596163224247</v>
       </c>
       <c r="T94">
-        <v>8.665816487847179</v>
+        <v>9.886556298034471</v>
       </c>
       <c r="U94">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V94">
         <v>0.15</v>
       </c>
       <c r="W94">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.00626581620725</v>
+        <v>1.671552604050524</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1121367314256973</v>
+        <v>0.1123778643749843</v>
       </c>
       <c r="C95">
-        <v>-4.412267384980368</v>
+        <v>-5.158478690262619</v>
       </c>
       <c r="D95">
-        <v>49.51473261501964</v>
+        <v>49.42752130973739</v>
       </c>
       <c r="E95">
-        <v>38.187</v>
+        <v>38.84600000000001</v>
       </c>
       <c r="F95">
-        <v>61.28700000000001</v>
+        <v>61.94600000000001</v>
       </c>
       <c r="G95">
         <v>7.36</v>
@@ -9077,28 +9077,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M95">
-        <v>5.51583</v>
+        <v>5.575140000000001</v>
       </c>
       <c r="N95">
-        <v>3.70417</v>
+        <v>3.64486</v>
       </c>
       <c r="O95">
-        <v>0.5556255</v>
+        <v>0.5467289999999999</v>
       </c>
       <c r="P95">
-        <v>3.1485445</v>
+        <v>3.098131</v>
       </c>
       <c r="Q95">
-        <v>3.888544500000001</v>
+        <v>3.838131</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.585596163224247</v>
+        <v>0.6744644062497382</v>
       </c>
       <c r="T95">
-        <v>9.886556298034471</v>
+        <v>11.51420937828419</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.671552604050524</v>
+        <v>1.653770129539348</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1123778643749843</v>
+        <v>0.1126189973242712</v>
       </c>
       <c r="C96">
-        <v>-5.158478690262619</v>
+        <v>-5.904383321605586</v>
       </c>
       <c r="D96">
-        <v>49.42752130973739</v>
+        <v>49.34061667839443</v>
       </c>
       <c r="E96">
-        <v>38.84600000000001</v>
+        <v>39.50500000000001</v>
       </c>
       <c r="F96">
-        <v>61.94600000000001</v>
+        <v>62.60500000000001</v>
       </c>
       <c r="G96">
         <v>7.36</v>
@@ -9159,28 +9159,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M96">
-        <v>5.575140000000001</v>
+        <v>5.634450000000001</v>
       </c>
       <c r="N96">
-        <v>3.64486</v>
+        <v>3.58555</v>
       </c>
       <c r="O96">
-        <v>0.5467289999999999</v>
+        <v>0.5378324999999999</v>
       </c>
       <c r="P96">
-        <v>3.098131</v>
+        <v>3.0477175</v>
       </c>
       <c r="Q96">
-        <v>3.838131</v>
+        <v>3.7877175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6744644062497382</v>
+        <v>0.798879946485426</v>
       </c>
       <c r="T96">
-        <v>11.51420937828419</v>
+        <v>13.79292369063381</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.653770129539348</v>
+        <v>1.636362022912618</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1126189973242712</v>
+        <v>0.1128601302735582</v>
       </c>
       <c r="C97">
-        <v>-5.904383321605586</v>
+        <v>-6.649982893774165</v>
       </c>
       <c r="D97">
-        <v>49.34061667839443</v>
+        <v>49.25401710622585</v>
       </c>
       <c r="E97">
-        <v>39.50500000000001</v>
+        <v>40.16400000000001</v>
       </c>
       <c r="F97">
-        <v>62.60500000000001</v>
+        <v>63.26400000000001</v>
       </c>
       <c r="G97">
         <v>7.36</v>
@@ -9241,28 +9241,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M97">
-        <v>5.634450000000001</v>
+        <v>5.693760000000001</v>
       </c>
       <c r="N97">
-        <v>3.58555</v>
+        <v>3.52624</v>
       </c>
       <c r="O97">
-        <v>0.5378324999999999</v>
+        <v>0.528936</v>
       </c>
       <c r="P97">
-        <v>3.0477175</v>
+        <v>2.997304</v>
       </c>
       <c r="Q97">
-        <v>3.7877175</v>
+        <v>3.737304</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.798879946485426</v>
+        <v>0.9855032568389577</v>
       </c>
       <c r="T97">
-        <v>13.79292369063381</v>
+        <v>17.21099515915823</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.636362022912618</v>
+        <v>1.619316585173945</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1128601302735582</v>
+        <v>0.1131012632228452</v>
       </c>
       <c r="C98">
-        <v>-6.649982893774158</v>
+        <v>-7.395279010216584</v>
       </c>
       <c r="D98">
-        <v>49.25401710622585</v>
+        <v>49.16772098978342</v>
       </c>
       <c r="E98">
-        <v>40.164</v>
+        <v>40.823</v>
       </c>
       <c r="F98">
-        <v>63.264</v>
+        <v>63.923</v>
       </c>
       <c r="G98">
         <v>7.36</v>
@@ -9323,28 +9323,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M98">
-        <v>5.69376</v>
+        <v>5.75307</v>
       </c>
       <c r="N98">
-        <v>3.52624</v>
+        <v>3.466930000000001</v>
       </c>
       <c r="O98">
-        <v>0.5289360000000001</v>
+        <v>0.5200395000000001</v>
       </c>
       <c r="P98">
-        <v>2.997304000000001</v>
+        <v>2.9468905</v>
       </c>
       <c r="Q98">
-        <v>3.737304000000001</v>
+        <v>3.686890500000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9855032568389551</v>
+        <v>1.296542107428173</v>
       </c>
       <c r="T98">
-        <v>17.21099515915818</v>
+        <v>22.90778094003219</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.619316585173945</v>
+        <v>1.60262259975978</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1131012632228452</v>
+        <v>0.1133423961721322</v>
       </c>
       <c r="C99">
-        <v>-7.395279010216584</v>
+        <v>-8.140273263163351</v>
       </c>
       <c r="D99">
-        <v>49.16772098978342</v>
+        <v>49.08172673683666</v>
       </c>
       <c r="E99">
-        <v>40.823</v>
+        <v>41.48200000000001</v>
       </c>
       <c r="F99">
-        <v>63.923</v>
+        <v>64.58200000000001</v>
       </c>
       <c r="G99">
         <v>7.36</v>
@@ -9405,28 +9405,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M99">
-        <v>5.75307</v>
+        <v>5.81238</v>
       </c>
       <c r="N99">
-        <v>3.466930000000001</v>
+        <v>3.407620000000001</v>
       </c>
       <c r="O99">
-        <v>0.5200395000000001</v>
+        <v>0.511143</v>
       </c>
       <c r="P99">
-        <v>2.9468905</v>
+        <v>2.896477</v>
       </c>
       <c r="Q99">
-        <v>3.686890500000001</v>
+        <v>3.636477000000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.296542107428173</v>
+        <v>1.91861980860661</v>
       </c>
       <c r="T99">
-        <v>22.90778094003219</v>
+        <v>34.30135250178021</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.60262259975978</v>
+        <v>1.586269307925497</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1133423961721322</v>
+        <v>0.1135835291214192</v>
       </c>
       <c r="C100">
-        <v>-8.140273263163351</v>
+        <v>-8.884967233725177</v>
       </c>
       <c r="D100">
-        <v>49.08172673683666</v>
+        <v>48.99603276627482</v>
       </c>
       <c r="E100">
-        <v>41.48200000000001</v>
+        <v>42.141</v>
       </c>
       <c r="F100">
-        <v>64.58200000000001</v>
+        <v>65.241</v>
       </c>
       <c r="G100">
         <v>7.36</v>
@@ -9487,28 +9487,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="M100">
-        <v>5.81238</v>
+        <v>5.87169</v>
       </c>
       <c r="N100">
-        <v>3.407620000000001</v>
+        <v>3.348310000000001</v>
       </c>
       <c r="O100">
-        <v>0.511143</v>
+        <v>0.5022465</v>
       </c>
       <c r="P100">
-        <v>2.896477</v>
+        <v>2.846063500000001</v>
       </c>
       <c r="Q100">
-        <v>3.636477000000001</v>
+        <v>3.586063500000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.91861980860661</v>
+        <v>3.784852912141917</v>
       </c>
       <c r="T100">
-        <v>34.30135250178021</v>
+        <v>68.48206718702426</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.586269307925497</v>
+        <v>1.570246385623219</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1135835291214192</v>
-      </c>
-      <c r="C101">
-        <v>-8.884967233725177</v>
-      </c>
-      <c r="D101">
-        <v>48.99603276627482</v>
-      </c>
-      <c r="E101">
-        <v>42.141</v>
-      </c>
-      <c r="F101">
-        <v>65.241</v>
-      </c>
-      <c r="G101">
-        <v>7.36</v>
-      </c>
-      <c r="H101">
-        <v>42.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="K101">
-        <v>0.7400000000000002</v>
-      </c>
-      <c r="L101">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="M101">
-        <v>5.87169</v>
-      </c>
-      <c r="N101">
-        <v>3.348310000000001</v>
-      </c>
-      <c r="O101">
-        <v>0.5022465</v>
-      </c>
-      <c r="P101">
-        <v>2.846063500000001</v>
-      </c>
-      <c r="Q101">
-        <v>3.586063500000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.784852912141917</v>
-      </c>
-      <c r="T101">
-        <v>68.48206718702426</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.0765</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.570246385623219</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
